--- a/Alpha Set List.xlsx
+++ b/Alpha Set List.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\apoke\Desktop\Advance!Tactics\Advance-Tactics-Tcgarena\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8BC321B-5883-4883-B90F-72F2A57CB59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{47DCAE94-7B1A-49FD-BF75-7ADC8598953D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="1" xr2:uid="{CA094A51-376D-41C2-95CA-6278B694BA34}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Extended Set List'!$A$69:$K$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Set1 - Alpha'!$A$69:$K$69</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,14 +44,26 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="434">
   <si>
     <t>Card Name</t>
   </si>
   <si>
+    <t>Align</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Spd</t>
+  </si>
+  <si>
     <t>Cost</t>
   </si>
   <si>
+    <t>Num/Ft</t>
+  </si>
+  <si>
     <t>Race</t>
   </si>
   <si>
@@ -64,254 +76,523 @@
     <t>Def</t>
   </si>
   <si>
-    <t>Goblin Vanguard</t>
+    <t>Effects</t>
+  </si>
+  <si>
+    <t>Rarity</t>
+  </si>
+  <si>
+    <t>Art Status</t>
+  </si>
+  <si>
+    <t>Artist</t>
+  </si>
+  <si>
+    <t>Ancient Knowledge</t>
+  </si>
+  <si>
+    <t>Command</t>
+  </si>
+  <si>
+    <t>Quick</t>
+  </si>
+  <si>
+    <t>IAA</t>
+  </si>
+  <si>
+    <t>Spell</t>
+  </si>
+  <si>
+    <t>Draw 4 cards.</t>
+  </si>
+  <si>
+    <t>Uncommon</t>
+  </si>
+  <si>
+    <t>Ants Insatiable</t>
+  </si>
+  <si>
+    <t>Ruthless</t>
+  </si>
+  <si>
+    <t>Army</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>FFF</t>
+  </si>
+  <si>
+    <t>Insect</t>
+  </si>
+  <si>
+    <t>Warriors</t>
+  </si>
+  <si>
+    <t>Static: When this unit deals undefended damage, put that many +1Pow counters on it.</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>Architect's Guild</t>
+  </si>
+  <si>
+    <t>Structure</t>
+  </si>
+  <si>
+    <t>SSWW</t>
+  </si>
+  <si>
+    <t>Building</t>
+  </si>
+  <si>
+    <t>Activate(WW/SS): Put a Building from your hand onto the field in any tile you could normally play one.</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>Architects of Palador</t>
+  </si>
+  <si>
+    <t>SWF</t>
+  </si>
+  <si>
+    <t>Human</t>
+  </si>
+  <si>
+    <t>Architects</t>
+  </si>
+  <si>
+    <t>Enter: Excavate for a Building card. Put that card into your hand.</t>
+  </si>
+  <si>
+    <t>Army of Mandibles</t>
+  </si>
+  <si>
+    <t>SF</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Static: This unit's power is equal to half its numbers, rounded down.</t>
+  </si>
+  <si>
+    <t>Ball of Fire</t>
+  </si>
+  <si>
+    <t>Rapid</t>
+  </si>
+  <si>
+    <t>WA</t>
+  </si>
+  <si>
+    <t>Deal 6 true damage to each unit on a chosen tile. Deal 4 true damage to each unit on each tile one orthoginal tile away  from the chosen tile.</t>
+  </si>
+  <si>
+    <t>Black Colony Guards</t>
+  </si>
+  <si>
+    <t>WF</t>
+  </si>
+  <si>
+    <t>Static: This unit's power is equal the number of your combatants on the field.</t>
+  </si>
+  <si>
+    <t>Callous Kobolds</t>
+  </si>
+  <si>
+    <t>Kobold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Static: This unit can advance while engaged. </t>
+  </si>
+  <si>
+    <t>Castle of New Beginnings</t>
+  </si>
+  <si>
+    <t>Castle</t>
+  </si>
+  <si>
+    <t>Crafty Kobolds</t>
+  </si>
+  <si>
+    <t>Cunning</t>
+  </si>
+  <si>
+    <t>SWI</t>
+  </si>
+  <si>
+    <t>Static: Your other armies within 1 orthoginal tile of this card have +3 Power and +1 Defense.</t>
+  </si>
+  <si>
+    <t>Crooked Coinswipes</t>
   </si>
   <si>
     <t>Chaotic</t>
   </si>
   <si>
-    <t>Army</t>
-  </si>
-  <si>
-    <t>Quick</t>
-  </si>
-  <si>
-    <t>SF</t>
+    <t>F</t>
   </si>
   <si>
     <t>Goblin</t>
   </si>
   <si>
-    <t>Warriors</t>
-  </si>
-  <si>
-    <t>Effects</t>
-  </si>
-  <si>
-    <t>Ramshackle Cavalry</t>
-  </si>
-  <si>
-    <t>Rudimentry Archers</t>
-  </si>
-  <si>
-    <t>Normal</t>
-  </si>
-  <si>
-    <t>Goblin Giants</t>
+    <t>Criminals</t>
+  </si>
+  <si>
+    <t>Post-Battle: One random resource in your opponent's reserves decays. Produce a resource of the same type.</t>
+  </si>
+  <si>
+    <t>Dark Cultists</t>
+  </si>
+  <si>
+    <t>IA</t>
+  </si>
+  <si>
+    <t>Mages</t>
+  </si>
+  <si>
+    <t>Activate(Sacrifice an Army): This unit gets +1 Power</t>
+  </si>
+  <si>
+    <t>Dig Deeper</t>
+  </si>
+  <si>
+    <t>Produce a resource that shares a type with a resource tile you control.</t>
+  </si>
+  <si>
+    <t>Dung-Beetle Scavengers</t>
+  </si>
+  <si>
+    <t>Scavengers</t>
+  </si>
+  <si>
+    <t>Produce(You have no other units): Two Food</t>
+  </si>
+  <si>
+    <t>Earthquake</t>
+  </si>
+  <si>
+    <t>AA</t>
+  </si>
+  <si>
+    <t>A chosen structure falls.</t>
+  </si>
+  <si>
+    <t>Elaizha, Petromancer</t>
+  </si>
+  <si>
+    <t>Champion</t>
+  </si>
+  <si>
+    <t>SSA</t>
+  </si>
+  <si>
+    <t>Elaizha</t>
+  </si>
+  <si>
+    <t>Command(S): Deal damage to target unit equal to this unit's power.
+Command(S): This unit has +10Def until end of turn. You can only activate this ability once per turn.</t>
+  </si>
+  <si>
+    <t>Secret Rare</t>
+  </si>
+  <si>
+    <t>Enhanced Managolems</t>
+  </si>
+  <si>
+    <t>SCA</t>
+  </si>
+  <si>
+    <t>Golem</t>
+  </si>
+  <si>
+    <t>Finished</t>
+  </si>
+  <si>
+    <t>Chuck Carr</t>
+  </si>
+  <si>
+    <t>Espionage</t>
+  </si>
+  <si>
+    <t>FI</t>
+  </si>
+  <si>
+    <t>Choose an opponent and look at their hand. They discard 1 chosen card.</t>
+  </si>
+  <si>
+    <t>Evhan of the Kobold Legion</t>
+  </si>
+  <si>
+    <t>SWMM</t>
+  </si>
+  <si>
+    <t>Evhan</t>
+  </si>
+  <si>
+    <t>Command(Destroy a Kobold): Deal true damage equal to the destroyed Kobold's power to all units on it's previously occupied tile and all castles it was on the backlines of.</t>
+  </si>
+  <si>
+    <t>Evhan's Wall of Panic</t>
+  </si>
+  <si>
+    <t>SMA</t>
+  </si>
+  <si>
+    <t>Defenses</t>
+  </si>
+  <si>
+    <t>Trigger: Flip 2 coins. If either are tails, triggering unit moves backwards 1 tile.</t>
+  </si>
+  <si>
+    <t>Outlined</t>
+  </si>
+  <si>
+    <t>Exhaustive Research</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>Discard a card, then draw 2 cards.</t>
+  </si>
+  <si>
+    <t>Factory Units</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Clanker</t>
+  </si>
+  <si>
+    <t>Workers</t>
+  </si>
+  <si>
+    <t>Produce: One Metal</t>
+  </si>
+  <si>
+    <t>Farm</t>
   </si>
   <si>
     <t>WI</t>
   </si>
   <si>
-    <t>SWI</t>
-  </si>
-  <si>
-    <t>Goblin Prospectors</t>
-  </si>
-  <si>
-    <t>Peasants</t>
-  </si>
-  <si>
-    <t>Static: The tile occupied by this card is a Stone Resource tile.</t>
+    <t>Produce: One Food
+Static: Occupied tile is a Food resource tile.
+Cannot be built on your backlines.</t>
+  </si>
+  <si>
+    <t>Gnawing Valkyries</t>
+  </si>
+  <si>
+    <t>WIF</t>
+  </si>
+  <si>
+    <t>Static: Cannot be engaged by units on the occupied tile.</t>
   </si>
   <si>
     <t>Goblin Chief Bucas</t>
   </si>
   <si>
-    <t>Champion</t>
-  </si>
-  <si>
     <t>SFM</t>
   </si>
   <si>
-    <t>Num/Ft</t>
-  </si>
-  <si>
-    <t>Evhan of the Kobold Legion</t>
-  </si>
-  <si>
-    <t>Cunning</t>
-  </si>
-  <si>
-    <t>SWM</t>
-  </si>
-  <si>
-    <t>Kobold</t>
-  </si>
-  <si>
-    <t>Sculptor Konor</t>
-  </si>
-  <si>
-    <t>Golem</t>
-  </si>
-  <si>
-    <t>SSC</t>
+    <t>Bucas</t>
   </si>
   <si>
     <t>Static: Once per turn, when one of your Goblins advances, you may have it advance again.
 Static: The first time one of your Goblins would take damage each turn, it instead moves one lane to the right or left, chosen at random.</t>
   </si>
   <si>
-    <t>Scavenging Kobolds</t>
-  </si>
-  <si>
-    <t>WF</t>
-  </si>
-  <si>
-    <t>Scouts</t>
-  </si>
-  <si>
-    <t>Crafty Kobolds</t>
-  </si>
-  <si>
-    <t>Reckless Arsonists</t>
-  </si>
-  <si>
-    <t>Human</t>
-  </si>
-  <si>
-    <t>Static: Tiles within 1 orthoginal tile of this card have no resource type.</t>
+    <t>Goblin Giants</t>
+  </si>
+  <si>
+    <t>SIF</t>
+  </si>
+  <si>
+    <t>Goblin Prospectors</t>
+  </si>
+  <si>
+    <t>Peasants</t>
+  </si>
+  <si>
+    <t>Static: The tile occupied by this card is a Stone Resource tile.</t>
+  </si>
+  <si>
+    <t>Goblin Vanguard</t>
+  </si>
+  <si>
+    <t>Static: Your other goblin units have +1 power.</t>
+  </si>
+  <si>
+    <t>Harbinger of Death</t>
+  </si>
+  <si>
+    <t>ICCAA</t>
+  </si>
+  <si>
+    <t>God</t>
+  </si>
+  <si>
+    <t>Harbinger</t>
+  </si>
+  <si>
+    <t>End: Each other unit within one tile of this unit loses 5kNum/5Ftt.</t>
+  </si>
+  <si>
+    <t>Heroic Battalion</t>
+  </si>
+  <si>
+    <t>Righteous</t>
+  </si>
+  <si>
+    <t>SFFF</t>
+  </si>
+  <si>
+    <t>Static: If this unit is engaging a Ruthless unit, it has +1 Power.</t>
+  </si>
+  <si>
+    <t>John Kaboom</t>
+  </si>
+  <si>
+    <t>WWII</t>
+  </si>
+  <si>
+    <t>Kaboom</t>
+  </si>
+  <si>
+    <t>Post-Battle: Deal 6 damage to each other unit within 1 orthoginal tile and each unit with a Bomb counter on it. Remove all Bomb counters from all units.
+Activate: Put a Bomb counter on a unit on the occupied tile.</t>
+  </si>
+  <si>
+    <t>King of the Pride</t>
+  </si>
+  <si>
+    <t>IIF</t>
+  </si>
+  <si>
+    <t>Feline</t>
+  </si>
+  <si>
+    <t>Static: Your Felines have +2Pow if they advanced this turn.
+End: If it's your turn, you may have up to 2 Felines advance.</t>
+  </si>
+  <si>
+    <t>Kobold Contraptionists</t>
+  </si>
+  <si>
+    <t>Activate(W): Create a Structure with 1Ft/0Def named Trebuchet on this tile with "Command: One combatant on this tile moves up to 2 tiles forward."</t>
+  </si>
+  <si>
+    <t>Chuck Carr, Evan Hirt</t>
+  </si>
+  <si>
+    <t>Lioness Errica</t>
+  </si>
+  <si>
+    <t>IFFA</t>
+  </si>
+  <si>
+    <t>Errica</t>
+  </si>
+  <si>
+    <t>Strafe (This unit can advance horizontally)
+Static: Your other Felines have Strafe.</t>
+  </si>
+  <si>
+    <t>Josh Carr</t>
+  </si>
+  <si>
+    <t>Loot the Bodies</t>
+  </si>
+  <si>
+    <t>Can only be played after the combat step.
+If any of your units felled a combatant this turn, draw two cards.</t>
+  </si>
+  <si>
+    <t>Mages of Palador</t>
+  </si>
+  <si>
+    <t>Range 1
+Static: Has +1 Power and +1 Defense for each Mana in your Reserves.</t>
+  </si>
+  <si>
+    <t>Mana Well</t>
+  </si>
+  <si>
+    <t>SW</t>
+  </si>
+  <si>
+    <t>Produce: One mana if there are no combatants on this tile. Otherwise, Two Mana</t>
+  </si>
+  <si>
+    <t>Mud-Spitters</t>
+  </si>
+  <si>
+    <t>SFF</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Range 2</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Ryan Chalmers</t>
+  </si>
+  <si>
+    <t>Obscured in Smog</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>A chosen unit gets -3Pow/-1Def until end of turn.</t>
+  </si>
+  <si>
+    <t>Palador Elites</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normal </t>
+  </si>
+  <si>
+    <t>IFM</t>
+  </si>
+  <si>
+    <t>Palador Frontliners</t>
+  </si>
+  <si>
+    <t>Static: If this unit is behind another friendly combatant, this unit advances.</t>
   </si>
   <si>
     <t xml:space="preserve">Palador Knights </t>
   </si>
   <si>
-    <t>Righteous</t>
-  </si>
-  <si>
-    <t>FI</t>
-  </si>
-  <si>
-    <t>Palador Elites</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Normal </t>
-  </si>
-  <si>
-    <t>Palador Frontliners</t>
-  </si>
-  <si>
-    <t>Static: If this unit is behind another friendly combatant, this unit advances.</t>
-  </si>
-  <si>
-    <t>Mages of Palador</t>
-  </si>
-  <si>
-    <t>Mages</t>
-  </si>
-  <si>
-    <t>Crooked Coinswipes</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>Criminals</t>
-  </si>
-  <si>
-    <t>Post-Battle: One random resource in your opponent's reserves decays. Produce a resource of the same type.</t>
-  </si>
-  <si>
-    <t>Kobold Contraptionists</t>
-  </si>
-  <si>
-    <t>Architects</t>
-  </si>
-  <si>
-    <t>Stone Legion</t>
-  </si>
-  <si>
-    <t>SS</t>
-  </si>
-  <si>
-    <t>Enhanced Managolems</t>
-  </si>
-  <si>
-    <t>Align</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Spd</t>
-  </si>
-  <si>
-    <t>Sawmill</t>
-  </si>
-  <si>
-    <t>Structure</t>
-  </si>
-  <si>
-    <t>Building</t>
-  </si>
-  <si>
-    <t>Farm</t>
-  </si>
-  <si>
-    <t>SCA</t>
-  </si>
-  <si>
-    <t>WA</t>
-  </si>
-  <si>
-    <t>Mana Well</t>
-  </si>
-  <si>
-    <t>SW</t>
-  </si>
-  <si>
-    <t>Heroic Battalion</t>
-  </si>
-  <si>
-    <t>SFFF</t>
-  </si>
-  <si>
-    <t>Static: If this unit is engaging a Ruthless unit, it has +1 Power.</t>
-  </si>
-  <si>
-    <t>Callous Kobolds</t>
-  </si>
-  <si>
-    <t>Ruthless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Static: This unit can advance while engaged. </t>
-  </si>
-  <si>
-    <t>Retreat</t>
-  </si>
-  <si>
-    <t>Command</t>
-  </si>
-  <si>
-    <t>Rapid</t>
-  </si>
-  <si>
-    <t>Tactical Roll</t>
-  </si>
-  <si>
-    <t>All of your combatants move back 1 tile.</t>
-  </si>
-  <si>
-    <t>Loot the Bodies</t>
-  </si>
-  <si>
-    <t>Move one of your combatants one tile horizontally.</t>
-  </si>
-  <si>
-    <t>AA</t>
-  </si>
-  <si>
-    <t>A chosen structure falls.</t>
-  </si>
-  <si>
-    <t>Teleportation</t>
+    <t>IF</t>
+  </si>
+  <si>
+    <t>Palador Library</t>
+  </si>
+  <si>
+    <t>WII</t>
+  </si>
+  <si>
+    <t>Activate: Draw 1 card.</t>
   </si>
   <si>
     <t>Palador Mage Guild</t>
   </si>
   <si>
-    <t>Activate: If unengaged, this unit advances.</t>
+    <t>SWFC</t>
   </si>
   <si>
     <t>Produce: One Mana
@@ -319,483 +600,253 @@
 Activate: One of your mage units gains 2k numbers.</t>
   </si>
   <si>
-    <t>Palador Library</t>
-  </si>
-  <si>
-    <t>WII</t>
-  </si>
-  <si>
-    <t>Activate: Draw 1 card.</t>
-  </si>
-  <si>
-    <t>Castle of New Beginnings</t>
-  </si>
-  <si>
-    <t>Castle</t>
+    <t>Pillars of Flame</t>
+  </si>
+  <si>
+    <t>WAA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Choose a lane. Deal 8 damage to each unit in that lane. </t>
+  </si>
+  <si>
+    <t>Ramshackle Cavalry</t>
+  </si>
+  <si>
+    <t>Activate: If unengaged, this unit advances.</t>
+  </si>
+  <si>
+    <t>Reckless Arsonists</t>
+  </si>
+  <si>
+    <t>Static: Tiles within 1 orthoginal tile of this card have no resource type.</t>
+  </si>
+  <si>
+    <t>Recyclists of the Muck</t>
+  </si>
+  <si>
+    <t>Activate(?): Produce a resource of any basic resource type.</t>
+  </si>
+  <si>
+    <t>Repurposed Battering Ram</t>
+  </si>
+  <si>
+    <t>Trap</t>
+  </si>
+  <si>
+    <t>Hidden
+Trigger: Flip this card face up. Deal 6 damage to each combatant within 2 tiles forward. Produce a Wood, then this unit falls.</t>
+  </si>
+  <si>
+    <t>Retreat</t>
+  </si>
+  <si>
+    <t>All of your combatants move back 1 tile.</t>
+  </si>
+  <si>
+    <t>Rhyan, Loyal to the Mound</t>
+  </si>
+  <si>
+    <t>SWFF</t>
+  </si>
+  <si>
+    <t>Rhyan</t>
+  </si>
+  <si>
+    <t>Command(F): Create a Insect Army summon with 5kNum/XPow/2Def and "This unit's power is equal to the number of your Insects on the field" on a horizontally adjacent tile.</t>
+  </si>
+  <si>
+    <t>Ritual of Annihilation</t>
+  </si>
+  <si>
+    <t>CFAAAA</t>
+  </si>
+  <si>
+    <t>Ritual</t>
+  </si>
+  <si>
+    <t>Enter: Put 3 Time counters on this unit.
+End(This unit has no time counters on it): For each unit, deal damage equal to their attack to any target, then deal 5 damage to each castle.</t>
+  </si>
+  <si>
+    <t>Rudimentry Archers</t>
+  </si>
+  <si>
+    <t>Range 1</t>
+  </si>
+  <si>
+    <t>Savannah Cheetahs</t>
+  </si>
+  <si>
+    <t>Static: The first time this unit advances, it advances 2 more times, then put 3 Time counters on this unit. This unit can't advance while it has Time counters on it.</t>
+  </si>
+  <si>
+    <t>Sawmill</t>
+  </si>
+  <si>
+    <t>Produce: One Wood
+Produce(Occupied tile has a Wood resource type):One Wood</t>
+  </si>
+  <si>
+    <t>Scavenging Kobolds</t>
+  </si>
+  <si>
+    <t>Produce: One resource of a type of occupied tile.</t>
+  </si>
+  <si>
+    <t>Sculptor Konor</t>
+  </si>
+  <si>
+    <t>SSC</t>
+  </si>
+  <si>
+    <t>Konor</t>
+  </si>
+  <si>
+    <t>Activate: Create a Golem Army summon with 1kNum/3Pow/7Def on this tile.</t>
+  </si>
+  <si>
+    <t>Sensitive Spike Shooter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hidden
+Trigger: Flip this card face up. Deal 7 damage to each combatant in an othoganally adjacent tile. </t>
+  </si>
+  <si>
+    <t>Shaloom of the Shroom</t>
+  </si>
+  <si>
+    <t>FA</t>
+  </si>
+  <si>
+    <t>Fungus</t>
+  </si>
+  <si>
+    <t>Shaloom</t>
+  </si>
+  <si>
+    <t>Pre-Battle: Roll a d4. Your castle loses that much fortitude and you produce that much Food.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calum </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smoke Spirit Atascha </t>
+  </si>
+  <si>
+    <t>WW</t>
+  </si>
+  <si>
+    <t>Elemental</t>
+  </si>
+  <si>
+    <t>Atascha</t>
+  </si>
+  <si>
+    <t>Strafe
+Static: Other units on this tile have -2 Power and -2 Defense</t>
+  </si>
+  <si>
+    <t>Stash Mound</t>
+  </si>
+  <si>
+    <t>Enter: Put a Time counter on Stash Mound.
+Activate(Destroy Stash Mound, No time counters on Stash Mound): Produce 2 Food.</t>
   </si>
   <si>
     <t>Stone Barricades</t>
   </si>
   <si>
-    <t>Defenses</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Elemental</t>
-  </si>
-  <si>
-    <t>Dark Cultists</t>
-  </si>
-  <si>
-    <t>IA</t>
-  </si>
-  <si>
-    <t>Ball of Fire</t>
-  </si>
-  <si>
-    <t>Spell</t>
-  </si>
-  <si>
-    <t>Earthquake</t>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>Static: Enemy combatants cannot advance forward while on the occupied tile.</t>
+  </si>
+  <si>
+    <t>Stone Legion</t>
+  </si>
+  <si>
+    <t>Stone-Age Clankers</t>
+  </si>
+  <si>
+    <t>Tactical Roll</t>
+  </si>
+  <si>
+    <t>Move one of your combatants one tile horizontally.</t>
+  </si>
+  <si>
+    <t>Taunting Dopes</t>
+  </si>
+  <si>
+    <t>Scouts</t>
+  </si>
+  <si>
+    <t>Static: When this unit advances, combatants within one orthogonal tile move to the occupied tile.</t>
+  </si>
+  <si>
+    <t>Teleportation</t>
   </si>
   <si>
     <t>If this command targets a structure, it costs an additional A.
 One chosen unit moves up to 2 tiles orthoganally.</t>
   </si>
   <si>
-    <t>Exhaustive Research</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>Discard a card, then draw 2 cards.</t>
-  </si>
-  <si>
-    <t>SSA</t>
-  </si>
-  <si>
-    <t>Command(S): Deal damage to target unit equal to this unit's power.
-Command(S): This unit has +10Def until end of turn. You can only activate this ability once per turn.</t>
-  </si>
-  <si>
-    <t>Static: When this unit advances, combatants within one orthogonal tile move to the occupied tile.</t>
-  </si>
-  <si>
-    <t>Static: Your other armies within 1 orthoginal tile of this card have +3 Power and +1 Defense.</t>
-  </si>
-  <si>
-    <t>SWF</t>
-  </si>
-  <si>
-    <t>Enter: Excavate for a Building card. Put that card into your hand.</t>
-  </si>
-  <si>
-    <t>Architects of Palador</t>
-  </si>
-  <si>
-    <t>Evhan's Wall of Panic</t>
-  </si>
-  <si>
-    <t>Trigger: Flip 2 coins. If either are tails, triggering unit moves backwards 1 tile.</t>
-  </si>
-  <si>
-    <t>Espionage</t>
-  </si>
-  <si>
-    <t>Choose an opponent and look at their hand. They discard 1 chosen card.</t>
-  </si>
-  <si>
-    <t>Pillar of Flame</t>
-  </si>
-  <si>
-    <t>WAA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Choose a lane. Deal 8 damage to each unit in that lane. </t>
-  </si>
-  <si>
-    <t>Trap</t>
-  </si>
-  <si>
-    <t>Sensitive Spike Shooter</t>
-  </si>
-  <si>
-    <t>Bucas</t>
-  </si>
-  <si>
-    <t>Evhan</t>
-  </si>
-  <si>
-    <t>Konor</t>
-  </si>
-  <si>
-    <t>Elaizha</t>
-  </si>
-  <si>
-    <t>Elaizha, Petromancer</t>
-  </si>
-  <si>
-    <t>God</t>
-  </si>
-  <si>
-    <t>Harbinger</t>
-  </si>
-  <si>
-    <t>Harbinger of Death</t>
-  </si>
-  <si>
-    <t>ICCAA</t>
-  </si>
-  <si>
-    <t>Static: Enemy combatants cannot advance forward while on the occupied tile.</t>
-  </si>
-  <si>
-    <t>Can only be played after the combat step.
-If any of your units felled a combatant this turn, draw two cards.</t>
-  </si>
-  <si>
-    <t>Recyclists of the Muck</t>
-  </si>
-  <si>
-    <t>Architect's Guild</t>
-  </si>
-  <si>
-    <t>SSWW</t>
-  </si>
-  <si>
-    <t>Ritual of Annihilation</t>
-  </si>
-  <si>
-    <t>CFAAAA</t>
-  </si>
-  <si>
-    <t>Ritual</t>
-  </si>
-  <si>
-    <t>End: Each other unit within one tile of this unit loses 5kNum/5Ftt.</t>
-  </si>
-  <si>
-    <t>Activate(WW/SS): Put a Building from your hand onto the field in any tile you could normally play one.</t>
-  </si>
-  <si>
-    <t>Ancient Knowledge</t>
-  </si>
-  <si>
-    <t>IAA</t>
-  </si>
-  <si>
-    <t>Draw 4 cards.</t>
-  </si>
-  <si>
-    <t>John Kaboom</t>
-  </si>
-  <si>
-    <t>WWII</t>
-  </si>
-  <si>
-    <t>Kaboom</t>
-  </si>
-  <si>
-    <t>Produce: One Food
-Static: Occupied tile is a Food resource tile.
-Cannot be built on your backlines.</t>
-  </si>
-  <si>
-    <t>Insect</t>
-  </si>
-  <si>
-    <t>Black Colony Guards</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>Static: This unit's power is equal the number of your combatants on the field.</t>
-  </si>
-  <si>
-    <t>Army of Mandibles</t>
-  </si>
-  <si>
-    <t>Static: This unit's power is equal to half its numbers, rounded down.</t>
-  </si>
-  <si>
-    <t>Ants Insatiable</t>
-  </si>
-  <si>
-    <t>FFF</t>
-  </si>
-  <si>
-    <t>Gnawing Valkyries</t>
-  </si>
-  <si>
-    <t>Mud-Spitters</t>
-  </si>
-  <si>
-    <t>SFF</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Static: Cannot be engaged by units on the occupied tile.</t>
-  </si>
-  <si>
-    <t>Rhyan, Loyal to the Mound</t>
-  </si>
-  <si>
-    <t>Rhyan</t>
-  </si>
-  <si>
-    <t>Taunting Dopes</t>
+    <t>Tin Can Clankers</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>Static: When one or more of your opponent's resources decay, produce one Metal.</t>
   </si>
   <si>
     <t>Walls of Wind</t>
   </si>
   <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>Walls</t>
-  </si>
-  <si>
-    <t>SWFF</t>
-  </si>
-  <si>
-    <t>Command(F): Create a Insect Army summon with 5kNum/XPow/2Def and "This unit's power is equal to the number of your Insects on the field" on a horizontally adjacent tile.</t>
-  </si>
-  <si>
-    <t>Deal 6 true damage to each unit on a chosen tile. Deal 4 true damage to each unit on each tile one orthoginal tile away  from the chosen tile.</t>
-  </si>
-  <si>
-    <t>Stash Mound</t>
-  </si>
-  <si>
-    <t>Range 2</t>
-  </si>
-  <si>
-    <t>Shaloom of the Shroom</t>
-  </si>
-  <si>
-    <t>Shaloom</t>
-  </si>
-  <si>
-    <t>Errica</t>
-  </si>
-  <si>
-    <t>Lioness Errica</t>
-  </si>
-  <si>
-    <t>Feline</t>
-  </si>
-  <si>
-    <t>Range 1</t>
-  </si>
-  <si>
-    <t>Dig Deeper</t>
-  </si>
-  <si>
-    <t>Produce a resource that shares a type with a resource tile you control.</t>
-  </si>
-  <si>
-    <t>Clanker</t>
-  </si>
-  <si>
-    <t>MMM</t>
-  </si>
-  <si>
-    <t>Factory Units</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>Workers</t>
-  </si>
-  <si>
-    <t>Produce: One Metal</t>
-  </si>
-  <si>
-    <t>Savannah Cheetahs</t>
-  </si>
-  <si>
-    <t>Static: The first time this unit advances, it advances 2 more times, then put 3 Time counters on this unit. This unit can't advance while it has Time counters on it.</t>
-  </si>
-  <si>
-    <t>Zh'Aedin</t>
-  </si>
-  <si>
-    <t>Zh'Aedin, in Billowing Smog</t>
-  </si>
-  <si>
-    <t>Tin Can Clankers</t>
-  </si>
-  <si>
-    <t>SM</t>
-  </si>
-  <si>
-    <t>Static: When one or more of your opponent's resources decay, produce one Metal.</t>
-  </si>
-  <si>
-    <t>Range 1
-Static: Has +1 Power and +1 Defense for each Mana in your Reserves.</t>
-  </si>
-  <si>
-    <t>King of the Pride</t>
-  </si>
-  <si>
-    <t>Static: Your Felines have +2Pow if they advanced this turn.
-End: If it's your turn, you may have up to 2 Felines advance.</t>
-  </si>
-  <si>
-    <t>Young Hunters</t>
-  </si>
-  <si>
-    <t>White Stalkers</t>
-  </si>
-  <si>
-    <t>Static: Enemy combatants within 1 tile of this unit don't advance during their owner's advance step.</t>
-  </si>
-  <si>
-    <t>Stone-Age Clankers</t>
-  </si>
-  <si>
-    <t>Dung-Beetle Scavengers</t>
-  </si>
-  <si>
-    <t>Scavengers</t>
-  </si>
-  <si>
-    <t>Enter: Put 3 Time counters on this unit.
-End(This unit has no time counters on it): For each unit, deal damage equal to their attack to any target, then deal 5 damage to each castle.</t>
-  </si>
-  <si>
-    <t>Repurposed Battering Ram</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hidden
-Trigger: Flip this card face up. Deal 7 damage to each combatant in an othoganally adjacent tile. </t>
-  </si>
-  <si>
-    <t>Hidden
-Trigger: Flip this card face up. Deal 6 damage to each combatant within 2 tiles forward. Produce a Wood, then this unit falls.</t>
-  </si>
-  <si>
-    <t>Produce: One Wood
-Produce(Occupied tile has a Wood resource type):One Wood</t>
-  </si>
-  <si>
-    <t>SMA</t>
-  </si>
-  <si>
-    <t>Produce(You have no other units): Two Food</t>
-  </si>
-  <si>
-    <t>Enter: Put a Time counter on Stash Mound.
-Activate(Destroy Stash Mound, No time counters on Stash Mound): Produce 2 Food.</t>
-  </si>
-  <si>
-    <t>Obscured in Smog</t>
-  </si>
-  <si>
-    <t>A chosen unit gets -3Pow/-1Def until end of turn.</t>
-  </si>
-  <si>
-    <t>Factory Defense Sentries</t>
-  </si>
-  <si>
-    <t>Range 1
-This unit cannot advance into a tile on an opponent's field.</t>
-  </si>
-  <si>
-    <t>Rarity</t>
-  </si>
-  <si>
-    <t>Common</t>
-  </si>
-  <si>
-    <t>Uncommon</t>
-  </si>
-  <si>
-    <t>Secret Rare</t>
-  </si>
-  <si>
-    <t>Rare</t>
-  </si>
-  <si>
-    <t>Pre-Battle: Roll a d4. Your castle loses that much fortitude and you produce that much Food.</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>Card</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Precon 1</t>
-  </si>
-  <si>
-    <t>Precon 2</t>
-  </si>
-  <si>
-    <t>Defenders</t>
-  </si>
-  <si>
-    <t>Dung Beetle Scavengers</t>
-  </si>
-  <si>
-    <t>Ants insatiable</t>
-  </si>
-  <si>
-    <t>Static: When this unit deals undefended damage, put that many +1Pow counters on it.</t>
-  </si>
-  <si>
-    <t>Command(Destroy a Kobold): Deal true damage equal to the destroyed Kobold's power to all units on it's previously occupied tile and all castles it was on the backlines of.</t>
-  </si>
-  <si>
-    <t>SWFC</t>
   </si>
   <si>
     <t>Static: This unit can advance while engaged.
 Post-Advance: Any other units on the tile this unit advanced from are moved to the occupied tile.</t>
   </si>
   <si>
-    <t>Activate(Sacrifice an Army): This unit gets +1 Power</t>
-  </si>
-  <si>
-    <t>Static: Your other goblin units have +1 power.</t>
-  </si>
-  <si>
-    <t>Activate(?): Produce a resource of any basic resource type.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smoke Spirit Atascha </t>
-  </si>
-  <si>
-    <t>WW</t>
-  </si>
-  <si>
-    <t>Atascha</t>
-  </si>
-  <si>
-    <t>Strafe
-Static: Other units on this tile have -2 Power and -2 Defense</t>
-  </si>
-  <si>
-    <t>Activate: Create a Golem Army summon with 1kNum/3Pow/7Def on this tile.</t>
-  </si>
-  <si>
-    <t>FA</t>
-  </si>
-  <si>
-    <t>Produce: One mana if there are no combatants on this tile. Otherwise, Two Mana</t>
+    <t>White Stalkers</t>
+  </si>
+  <si>
+    <t>Static: Enemy combatants within 1 tile of this unit don't advance during their owner's advance step.</t>
+  </si>
+  <si>
+    <t>Young Hunters</t>
+  </si>
+  <si>
+    <t>Produce: One Food
+Post-Battle: If this unit felled a unit this turn, it gains +1Pow and +1Def.</t>
+  </si>
+  <si>
+    <t>Zh'Aedinn, in Billowing Smog</t>
+  </si>
+  <si>
+    <t>MMM</t>
+  </si>
+  <si>
+    <t>Zh'Aedinn</t>
+  </si>
+  <si>
+    <t>Produce: One Metal
+Command(M): Each of your Clanker units gain +1Pow and +1Def until end of turn.</t>
+  </si>
+  <si>
+    <t>Lore</t>
   </si>
   <si>
     <t>Freaky Fungi</t>
   </si>
   <si>
+    <t>Static: You can use Food as though it were Mana to pay for cards and card effects.</t>
+  </si>
+  <si>
     <t>The Crooked One</t>
   </si>
   <si>
@@ -803,6 +854,9 @@
   </si>
   <si>
     <t>Crooked One</t>
+  </si>
+  <si>
+    <t>Enter: For each enemy unit, that unit's controller chooses to deal 10 damage to that unit or deal 5 damage to their castle.</t>
   </si>
   <si>
     <t>House-eaters</t>
@@ -836,20 +890,13 @@
     <t>Skittish Kobolds</t>
   </si>
   <si>
-    <t>Strafe (This unit can advance horizontally)
-Static: Your other Felines have Strafe.</t>
+    <t>Trigger: This unit moves to a random orthoginal tile.</t>
   </si>
   <si>
     <t>Bombardier Beetles</t>
   </si>
   <si>
     <t>Bombers</t>
-  </si>
-  <si>
-    <t>Fungus</t>
-  </si>
-  <si>
-    <t>Trigger: This unit moves to a random orthoginal tile.</t>
   </si>
   <si>
     <t>Command(F): This unit deals 5 damage to a chosen enemy unit, then deals 2 damage to each other unit within 1 orthoginal tile of the chosen unit.</t>
@@ -868,22 +915,25 @@
     <t>Bouncer Clankers</t>
   </si>
   <si>
+    <t>Defenders</t>
+  </si>
+  <si>
     <t>Post-Battle: Any units dealt damage by Bouncer Clankers this combat move back 1 tile.</t>
   </si>
   <si>
-    <t>Enter: For each enemy unit, that unit's controller chooses to deal 10 damage to that unit or deal 5 damage to their castle.</t>
-  </si>
-  <si>
     <t>Overflowing Mound</t>
   </si>
   <si>
+    <t>SWIF</t>
+  </si>
+  <si>
+    <t>Start: Create a 3kNum/3Power/3Def Insect army summon on this tile with "Static: This creature always advances when able."</t>
+  </si>
+  <si>
     <t>Assembly Lines</t>
   </si>
   <si>
     <t>WIM</t>
-  </si>
-  <si>
-    <t>Start: Create a 3kNum/3Power/3Def Insect army summon on this tile with "Static: This creature always advances when able."</t>
   </si>
   <si>
     <t>Activate(M): Create a 1kNum/5Power/5Def Clanker Army summon on any horizontally adjacent tile. You may use this ability any number of times per turn.</t>
@@ -899,10 +949,6 @@
 Pre-Battle: Enemy combatants on this tile get -1 Power until end of combat.</t>
   </si>
   <si>
-    <t>Produce: One Metal
-Command(M): Each of your Clanker units gain +1Pow and +1Def until end of turn.</t>
-  </si>
-  <si>
     <t>Draconic Horn</t>
   </si>
   <si>
@@ -916,47 +962,23 @@
     <t>Lord Kobalte</t>
   </si>
   <si>
+    <t>SWIFMCA</t>
+  </si>
+  <si>
     <t>Dragon</t>
   </si>
   <si>
     <t>Kobalte</t>
-  </si>
-  <si>
-    <t>Filter-Bots</t>
-  </si>
-  <si>
-    <t>MM</t>
-  </si>
-  <si>
-    <t>End: Look at the top three cards of your deck. Put up to two into your discard pile.</t>
   </si>
   <si>
     <t>Static: Cannot be chosen by cards.
 Static: You may pay SWIF rather than pay the cost for Dragon cards.</t>
   </si>
   <si>
-    <t>SWIFMCA</t>
-  </si>
-  <si>
-    <t>SIF</t>
-  </si>
-  <si>
-    <t>IF</t>
-  </si>
-  <si>
-    <t>WIF</t>
-  </si>
-  <si>
-    <t>IFM</t>
-  </si>
-  <si>
-    <t>IFFA</t>
-  </si>
-  <si>
-    <t>IIF</t>
-  </si>
-  <si>
-    <t>SWIF</t>
+    <t>Filter-Bots</t>
+  </si>
+  <si>
+    <t>End: Look at the top three cards of your deck. Put up to two into your discard pile.</t>
   </si>
   <si>
     <t>Draconic Mages</t>
@@ -965,16 +987,6 @@
     <t>Produce: 1 Mana if controlled tile is a resource tile.</t>
   </si>
   <si>
-    <t>Produce: One Food
-Post-Battle: If this unit felled a unit this turn, it gains +1Pow and +1Def.</t>
-  </si>
-  <si>
-    <t>Produce: One resource of a type of occupied tile.</t>
-  </si>
-  <si>
-    <t>Static: You can use Food as though it were Mana to pay for cards and card effects.</t>
-  </si>
-  <si>
     <t>Fungamblers</t>
   </si>
   <si>
@@ -985,6 +997,9 @@
   </si>
   <si>
     <t>Repliclankers</t>
+  </si>
+  <si>
+    <t>MM</t>
   </si>
   <si>
     <t>Repliclankers enters as a copy of a chosen combatant, but as Clanker Warriors with 3k numbers.</t>
@@ -1018,18 +1033,6 @@
     <t>Draconian Warriors</t>
   </si>
   <si>
-    <t>Art Status</t>
-  </si>
-  <si>
-    <t>Outlined</t>
-  </si>
-  <si>
-    <t>Artist</t>
-  </si>
-  <si>
-    <t>Finished</t>
-  </si>
-  <si>
     <t>Impenetrable Hive</t>
   </si>
   <si>
@@ -1043,25 +1046,31 @@
     <t>Phantom</t>
   </si>
   <si>
-    <t>Shouting Ralliers</t>
-  </si>
-  <si>
-    <t>SI</t>
-  </si>
-  <si>
-    <t>Enter: Until the start of your next turn, Kobolds you control get +2 Power.</t>
-  </si>
-  <si>
     <t>Ethereal (Cannot be damaged through combat)
 Static: If the occupied tile has no Slime counters, put a Slime counter on it. Combatants on tiles with slime counters on them don't advance during their owner's turn.</t>
   </si>
   <si>
+    <t>Shouting Ralliers</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>Enter: Until the start of your next turn, Kobolds you control get +2 Power.</t>
+  </si>
+  <si>
     <t>Fight 'til the End</t>
   </si>
   <si>
+    <t>Until end of turn, when a combatant you control dies, combatants you control get +2 Power and +1 Defense until end of turn.</t>
+  </si>
+  <si>
     <t>Rousing Speech</t>
   </si>
   <si>
+    <t>Until end of turn, combatants you control get +1 Power and +3 Numbers</t>
+  </si>
+  <si>
     <t>Natakan Horse</t>
   </si>
   <si>
@@ -1071,15 +1080,6 @@
     <t>You may play combatants on the occupied tile.</t>
   </si>
   <si>
-    <t>Until end of turn, when a combatant you control dies, combatants you control get +2 Power and +1 Defense until end of turn.</t>
-  </si>
-  <si>
-    <t>Until end of turn, combatants you control get +1 Power and +3 Numbers</t>
-  </si>
-  <si>
-    <t>Activate(W): Create a Structure with 1Ft/0Def named Trebuchet on this tile with "Command: One combatant on this tile moves up to 2 tiles forward."</t>
-  </si>
-  <si>
     <t>Scaled Skirmishers</t>
   </si>
   <si>
@@ -1090,10 +1090,6 @@
   </si>
   <si>
     <t>Enter: Return an Insect combatant from your discard to this tile. If either this structure or the combatant leaves the field, the other falls.</t>
-  </si>
-  <si>
-    <t>Post-Battle: Deal 6 damage to each other unit within 1 orthoginal tile and each unit with a Bomb counter on it. Remove all Bomb counters from all units.
-Activate: Put a Bomb counter on a unit on the occupied tile.</t>
   </si>
   <si>
     <t>Swarming Locusts</t>
@@ -1175,13 +1171,10 @@
     <t>WIA</t>
   </si>
   <si>
+    <t>Leviticus</t>
+  </si>
+  <si>
     <t>Static: Enemy combatants have no static abililties.</t>
-  </si>
-  <si>
-    <t>Leviticus</t>
-  </si>
-  <si>
-    <t>Josh Carr</t>
   </si>
   <si>
     <t>Transmutation Mages</t>
@@ -1213,15 +1206,6 @@
   </si>
   <si>
     <t>Outpost</t>
-  </si>
-  <si>
-    <t>Chuck Carr</t>
-  </si>
-  <si>
-    <t>Chuck Carr, Evan Hirt</t>
-  </si>
-  <si>
-    <t>Pillars of Flame</t>
   </si>
   <si>
     <t>Harbinger of Famine</t>
@@ -1266,15 +1250,15 @@
     <t>Counter-Strategy</t>
   </si>
   <si>
+    <t>Put a chosen card planned card into it's owners discard pile.</t>
+  </si>
+  <si>
     <t>Divine Intervention</t>
   </si>
   <si>
     <t>Your combatants cannot fall this turn.</t>
   </si>
   <si>
-    <t>Put a chosen card planned card into it's owners discard pile.</t>
-  </si>
-  <si>
     <t>Raze</t>
   </si>
   <si>
@@ -1299,7 +1283,7 @@
     <t>Evhan, Strategist</t>
   </si>
   <si>
-    <t>SWMM</t>
+    <t>SIFM</t>
   </si>
   <si>
     <t>Static: Kobolds have +X Power, where X is equal to the combined power of other Kobolds diagonally aligned with them.</t>
@@ -1308,37 +1292,37 @@
     <t>Crazed Mechanics</t>
   </si>
   <si>
+    <t>SWM</t>
+  </si>
+  <si>
     <t>Activate: A chosen structure on the occupied tile gains 2 Fortitude.</t>
   </si>
   <si>
     <t>Errica, Coven Conscript</t>
+  </si>
+  <si>
+    <t>WIFA</t>
   </si>
   <si>
     <t>Static: Whenever you play a spell card, produce one Mana.
 Activate(AAAAAA): You win the game.</t>
   </si>
   <si>
-    <t>Lore</t>
-  </si>
-  <si>
     <t>Errica used a crown to communicate with cultists to increase her power and influence. Baoust learned of her collusion and turned her into a human as punishment for turning against her race.</t>
   </si>
   <si>
     <t>Collude</t>
   </si>
   <si>
-    <t>WIFA</t>
-  </si>
-  <si>
-    <t>SIFM</t>
-  </si>
-  <si>
     <t>Each player chooses Knowledge or Power. For each Power vote, you and that player produce one resource of any resource type. For each knowledge vote, you and that player draw a card.</t>
   </si>
   <si>
     <t>Cost of Battle</t>
   </si>
   <si>
+    <t>For each combatant that engaged in combat this turn, it's owner chooses a different resource they own. Each chosen resource decays.</t>
+  </si>
+  <si>
     <t>Rhyan, Assimilated</t>
   </si>
   <si>
@@ -1351,9 +1335,6 @@
     <t>Rhyan rejected his flesh and replaced it with chitin, encouraging centipedes to crawl through his ears and alter his pituitary glands such that he would grow more insect-like.</t>
   </si>
   <si>
-    <t>For each combatant that engaged in combat this turn, it's owner chooses a different resource they own. Each chosen resource decays.</t>
-  </si>
-  <si>
     <t>Spire of Innovation</t>
   </si>
   <si>
@@ -1363,25 +1344,44 @@
     <t>Spore Scrappers</t>
   </si>
   <si>
-    <t>In Progress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calum </t>
-  </si>
-  <si>
-    <t>Ryan Chalmers</t>
-  </si>
-  <si>
-    <t>Zh'Aedinn, in Billowing Smog</t>
-  </si>
-  <si>
-    <t>Zh'Aedinn</t>
-  </si>
-  <si>
     <t>Psychedelic Sam</t>
   </si>
   <si>
     <t>Sam</t>
+  </si>
+  <si>
+    <t>Pillar of Flame</t>
+  </si>
+  <si>
+    <t>Zh'Aedin, in Billowing Smog</t>
+  </si>
+  <si>
+    <t>Zh'Aedin</t>
+  </si>
+  <si>
+    <t>Factory Defense Sentries</t>
+  </si>
+  <si>
+    <t>Range 1
+This unit cannot advance into a tile on an opponent's field.</t>
+  </si>
+  <si>
+    <t>Precon 1</t>
+  </si>
+  <si>
+    <t>Precon 2</t>
+  </si>
+  <si>
+    <t>Card</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Dung Beetle Scavengers</t>
+  </si>
+  <si>
+    <t>Ants insatiable</t>
   </si>
 </sst>
 </file>
@@ -1848,66 +1848,66 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="M1" t="s">
-        <v>315</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>143</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>144</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>145</v>
+        <v>19</v>
       </c>
       <c r="L2" t="s">
-        <v>217</v>
+        <v>20</v>
       </c>
       <c r="P2">
         <f>COUNTIF(L:L, "Common")</f>
@@ -1916,28 +1916,28 @@
     </row>
     <row r="3" spans="1:16" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>157</v>
+        <v>25</v>
       </c>
       <c r="F3">
         <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>150</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I3">
         <v>6</v>
@@ -1946,10 +1946,10 @@
         <v>3</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>229</v>
+        <v>28</v>
       </c>
       <c r="L3" t="s">
-        <v>219</v>
+        <v>29</v>
       </c>
       <c r="M3" s="5"/>
       <c r="P3">
@@ -1959,31 +1959,31 @@
     </row>
     <row r="4" spans="1:16" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>136</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="F4">
         <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="J4">
         <v>9</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>142</v>
+        <v>34</v>
       </c>
       <c r="L4" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
       <c r="P4">
         <f>COUNTIF(L:L, "Rare")</f>
@@ -1992,25 +1992,25 @@
     </row>
     <row r="5" spans="1:16" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="F5">
         <v>5</v>
       </c>
       <c r="G5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H5" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -2019,10 +2019,10 @@
         <v>6</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>113</v>
+        <v>40</v>
       </c>
       <c r="L5" t="s">
-        <v>219</v>
+        <v>29</v>
       </c>
       <c r="P5">
         <f>COUNTIF(L:L, "Secret Rare")</f>
@@ -2031,127 +2031,127 @@
     </row>
     <row r="6" spans="1:16" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>154</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="F6">
         <v>10</v>
       </c>
       <c r="G6" t="s">
-        <v>150</v>
+        <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I6" t="s">
-        <v>152</v>
+        <v>43</v>
       </c>
       <c r="J6">
         <v>2</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>155</v>
+        <v>44</v>
       </c>
       <c r="L6" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="H7" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>170</v>
+        <v>48</v>
       </c>
       <c r="L7" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>151</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="F8">
         <v>10</v>
       </c>
       <c r="G8" t="s">
-        <v>150</v>
+        <v>26</v>
       </c>
       <c r="H8" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I8" t="s">
-        <v>152</v>
+        <v>43</v>
       </c>
       <c r="J8">
         <v>2</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>153</v>
+        <v>51</v>
       </c>
       <c r="L8" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="F9">
         <v>8</v>
       </c>
       <c r="G9" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="H9" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I9">
         <v>3</v>
@@ -2160,21 +2160,21 @@
         <v>2</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="L9" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F10">
         <v>60</v>
@@ -2183,33 +2183,33 @@
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="F11">
         <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="H11" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I11">
         <v>3</v>
@@ -2218,36 +2218,36 @@
         <v>3</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="L11" t="s">
-        <v>217</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="F12">
         <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="H12" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="I12">
         <v>2</v>
@@ -2256,36 +2256,36 @@
         <v>2</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="L12" t="s">
-        <v>217</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="F13">
         <v>5</v>
       </c>
       <c r="G13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H13" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="I13">
         <v>9</v>
@@ -2294,53 +2294,53 @@
         <v>2</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>233</v>
+        <v>70</v>
       </c>
       <c r="L13" t="s">
-        <v>217</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>179</v>
+        <v>71</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="L14" t="s">
-        <v>219</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>201</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="F15">
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>150</v>
+        <v>26</v>
       </c>
       <c r="H15" t="s">
-        <v>202</v>
+        <v>74</v>
       </c>
       <c r="I15">
         <v>3</v>
@@ -2349,56 +2349,56 @@
         <v>3</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="L15" t="s">
-        <v>219</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16" t="s">
+        <v>18</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" t="s">
-        <v>84</v>
-      </c>
-      <c r="H16" t="s">
-        <v>102</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="L16" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="F17">
         <v>24</v>
       </c>
       <c r="G17" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H17" t="s">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="I17">
         <v>4</v>
@@ -2407,33 +2407,33 @@
         <v>10</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="L17" t="s">
-        <v>218</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="F18">
         <v>5</v>
       </c>
       <c r="G18" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I18">
         <v>10</v>
@@ -2442,62 +2442,62 @@
         <v>12</v>
       </c>
       <c r="L18" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>318</v>
+        <v>88</v>
       </c>
       <c r="N18" t="s">
-        <v>379</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E19" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="L19" t="s">
-        <v>219</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>406</v>
+        <v>94</v>
       </c>
       <c r="F20">
         <v>8</v>
       </c>
       <c r="G20" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="H20" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="I20">
         <v>11</v>
@@ -2506,91 +2506,91 @@
         <v>5</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>230</v>
+        <v>96</v>
       </c>
       <c r="L20" t="s">
-        <v>218</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>208</v>
+        <v>98</v>
       </c>
       <c r="F21">
         <v>12</v>
       </c>
       <c r="H21" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="L21" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>316</v>
+        <v>101</v>
       </c>
       <c r="N21" t="s">
-        <v>379</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E22" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L22" t="s">
-        <v>217</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>183</v>
+        <v>105</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>184</v>
+        <v>106</v>
       </c>
       <c r="F23">
         <v>4</v>
       </c>
       <c r="G23" t="s">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="H23" t="s">
-        <v>185</v>
+        <v>108</v>
       </c>
       <c r="I23">
         <v>2</v>
@@ -2599,65 +2599,65 @@
         <v>6</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>186</v>
+        <v>109</v>
       </c>
       <c r="L23" t="s">
-        <v>217</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E24" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="F24">
         <v>3</v>
       </c>
       <c r="H24" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>149</v>
+        <v>112</v>
       </c>
       <c r="L24" t="s">
-        <v>217</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>291</v>
+        <v>114</v>
       </c>
       <c r="F25">
         <v>10</v>
       </c>
       <c r="G25" t="s">
-        <v>150</v>
+        <v>26</v>
       </c>
       <c r="H25" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I25">
         <v>5</v>
@@ -2666,36 +2666,36 @@
         <v>0</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>162</v>
+        <v>115</v>
       </c>
       <c r="L25" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>116</v>
       </c>
       <c r="B26" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C26" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="D26" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>25</v>
+        <v>117</v>
       </c>
       <c r="F26">
         <v>10</v>
       </c>
       <c r="G26" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="H26" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="I26">
         <v>8</v>
@@ -2704,33 +2704,33 @@
         <v>2</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="L26" t="s">
-        <v>218</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>289</v>
+        <v>121</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="H27" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I27">
         <v>6</v>
@@ -2739,36 +2739,36 @@
         <v>5</v>
       </c>
       <c r="L27" t="s">
-        <v>217</v>
+        <v>20</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>318</v>
+        <v>88</v>
       </c>
       <c r="N27" t="s">
-        <v>379</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>20</v>
+        <v>122</v>
       </c>
       <c r="C28" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E28" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="F28">
         <v>2</v>
       </c>
       <c r="G28" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="H28" t="s">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="I28">
         <v>3</v>
@@ -2777,36 +2777,36 @@
         <v>1</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>22</v>
+        <v>124</v>
       </c>
       <c r="L28" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>6</v>
+        <v>125</v>
       </c>
       <c r="B29" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C29" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D29" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="F29">
         <v>3</v>
       </c>
       <c r="G29" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="H29" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I29">
         <v>4</v>
@@ -2815,27 +2815,27 @@
         <v>1</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>234</v>
+        <v>126</v>
       </c>
       <c r="L29" t="s">
-        <v>217</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="C30" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E30" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F30">
         <v>24</v>
@@ -2853,42 +2853,42 @@
         <v>3</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="L30" t="s">
-        <v>219</v>
+        <v>29</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>318</v>
+        <v>88</v>
       </c>
       <c r="N30" t="s">
-        <v>379</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>132</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="C31" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E31" t="s">
-        <v>72</v>
+        <v>134</v>
       </c>
       <c r="F31">
         <v>16</v>
       </c>
       <c r="G31" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H31" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I31">
         <v>8</v>
@@ -2897,36 +2897,36 @@
         <v>4</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="L31" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="72.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="B32" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C32" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E32" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="F32">
         <v>5</v>
       </c>
       <c r="G32" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H32" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="I32">
         <v>17</v>
@@ -2935,36 +2935,36 @@
         <v>5</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>339</v>
+        <v>139</v>
       </c>
       <c r="L32" t="s">
-        <v>217</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>195</v>
+        <v>140</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="C33" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E33" t="s">
-        <v>294</v>
+        <v>141</v>
       </c>
       <c r="F33">
         <v>7</v>
       </c>
       <c r="G33" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="H33" t="s">
-        <v>195</v>
+        <v>140</v>
       </c>
       <c r="I33">
         <v>4</v>
@@ -2973,36 +2973,36 @@
         <v>3</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>196</v>
+        <v>143</v>
       </c>
       <c r="L33" t="s">
-        <v>219</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>55</v>
+        <v>144</v>
       </c>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C34" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E34" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="F34">
         <v>5</v>
       </c>
       <c r="G34" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="H34" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="I34">
         <v>4</v>
@@ -3011,42 +3011,42 @@
         <v>3</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>334</v>
+        <v>145</v>
       </c>
       <c r="L34" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
       <c r="M34" s="8" t="s">
-        <v>318</v>
+        <v>88</v>
       </c>
       <c r="N34" t="s">
-        <v>380</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="C35" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="D35" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E35" t="s">
-        <v>293</v>
+        <v>148</v>
       </c>
       <c r="F35">
         <v>11</v>
       </c>
       <c r="G35" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="H35" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="I35">
         <v>7</v>
@@ -3055,62 +3055,62 @@
         <v>6</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>257</v>
+        <v>150</v>
       </c>
       <c r="L35" t="s">
-        <v>218</v>
+        <v>84</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>318</v>
+        <v>88</v>
       </c>
       <c r="N35" t="s">
-        <v>368</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="B36" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="C36" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="L36" t="s">
-        <v>217</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>49</v>
+        <v>154</v>
       </c>
       <c r="B37" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="C37" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D37" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E37" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="F37">
         <v>6</v>
       </c>
       <c r="G37" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H37" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="I37">
         <v>7</v>
@@ -3119,42 +3119,42 @@
         <v>2</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>194</v>
+        <v>155</v>
       </c>
       <c r="L37" t="s">
-        <v>217</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>69</v>
+        <v>156</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="C38" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E38" t="s">
-        <v>70</v>
+        <v>157</v>
       </c>
       <c r="F38">
         <v>4</v>
       </c>
       <c r="H38" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="J38">
         <v>1</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>242</v>
+        <v>158</v>
       </c>
       <c r="L38" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -3162,10 +3162,10 @@
         <v>159</v>
       </c>
       <c r="C39" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D39" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E39" t="s">
         <v>160</v>
@@ -3174,7 +3174,7 @@
         <v>7</v>
       </c>
       <c r="G39" t="s">
-        <v>150</v>
+        <v>26</v>
       </c>
       <c r="H39" t="s">
         <v>161</v>
@@ -3186,62 +3186,62 @@
         <v>2</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="L39" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
       <c r="M39" s="7" t="s">
-        <v>427</v>
+        <v>163</v>
       </c>
       <c r="N39" t="s">
-        <v>429</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>211</v>
+        <v>165</v>
       </c>
       <c r="C40" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="E40" t="s">
-        <v>221</v>
+        <v>166</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>212</v>
+        <v>167</v>
       </c>
       <c r="L40" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="C41" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D41" t="s">
-        <v>46</v>
+        <v>169</v>
       </c>
       <c r="E41" t="s">
-        <v>292</v>
+        <v>170</v>
       </c>
       <c r="F41">
         <v>8</v>
       </c>
       <c r="G41" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H41" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I41">
         <v>8</v>
@@ -3250,33 +3250,33 @@
         <v>8</v>
       </c>
       <c r="L41" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>171</v>
       </c>
       <c r="B42" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="C42" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D42" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E42" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="F42">
         <v>9</v>
       </c>
       <c r="G42" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H42" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I42">
         <v>3</v>
@@ -3285,36 +3285,36 @@
         <v>6</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>48</v>
+        <v>172</v>
       </c>
       <c r="L42" t="s">
-        <v>217</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>42</v>
+        <v>173</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="C43" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D43" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E43" t="s">
-        <v>290</v>
+        <v>174</v>
       </c>
       <c r="F43">
         <v>10</v>
       </c>
       <c r="G43" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H43" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I43">
         <v>4</v>
@@ -3323,126 +3323,126 @@
         <v>3</v>
       </c>
       <c r="L43" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>90</v>
+        <v>175</v>
       </c>
       <c r="B44" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C44" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D44" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E44" t="s">
-        <v>91</v>
+        <v>176</v>
       </c>
       <c r="F44">
         <v>8</v>
       </c>
       <c r="H44" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="J44">
         <v>0</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>92</v>
+        <v>177</v>
       </c>
       <c r="L44" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>87</v>
+        <v>178</v>
       </c>
       <c r="B45" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C45" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E45" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="F45">
         <v>5</v>
       </c>
       <c r="H45" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="J45">
         <v>9</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>89</v>
+        <v>180</v>
       </c>
       <c r="L45" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>381</v>
+        <v>181</v>
       </c>
       <c r="C46" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D46" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E46" t="s">
-        <v>120</v>
+        <v>182</v>
       </c>
       <c r="H46" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>121</v>
+        <v>183</v>
       </c>
       <c r="L46" t="s">
-        <v>217</v>
+        <v>20</v>
       </c>
       <c r="M46" s="8" t="s">
-        <v>318</v>
+        <v>88</v>
       </c>
       <c r="N46" t="s">
-        <v>379</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>14</v>
+        <v>184</v>
       </c>
       <c r="B47" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C47" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D47" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E47" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="F47">
         <v>3</v>
       </c>
       <c r="G47" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="H47" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I47">
         <v>5</v>
@@ -3451,42 +3451,42 @@
         <v>0</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>88</v>
+        <v>185</v>
       </c>
       <c r="L47" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
       <c r="M47" s="9" t="s">
-        <v>316</v>
+        <v>101</v>
       </c>
       <c r="N47" t="s">
-        <v>379</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>39</v>
+        <v>186</v>
       </c>
       <c r="B48" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C48" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D48" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E48" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="F48">
         <v>3</v>
       </c>
       <c r="G48" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H48" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I48">
         <v>15</v>
@@ -3495,33 +3495,33 @@
         <v>0</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>41</v>
+        <v>187</v>
       </c>
       <c r="L48" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="C49" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E49" t="s">
-        <v>291</v>
+        <v>114</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
       <c r="G49" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H49" t="s">
-        <v>202</v>
+        <v>74</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -3530,88 +3530,88 @@
         <v>1</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>235</v>
+        <v>189</v>
       </c>
       <c r="L49" t="s">
-        <v>217</v>
+        <v>20</v>
       </c>
       <c r="M49" s="9" t="s">
-        <v>316</v>
+        <v>101</v>
       </c>
       <c r="N49" t="s">
-        <v>368</v>
+        <v>151</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C50" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D50" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E50" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
       <c r="H50" t="s">
-        <v>122</v>
+        <v>191</v>
       </c>
       <c r="J50">
         <v>0</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="L50" t="s">
-        <v>217</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>77</v>
+        <v>193</v>
       </c>
       <c r="C51" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>81</v>
+        <v>194</v>
       </c>
       <c r="L51" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="B52" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C52" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="D52" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E52" t="s">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="F52">
         <v>7</v>
       </c>
       <c r="G52" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H52" t="s">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="I52">
         <v>7</v>
@@ -3620,65 +3620,65 @@
         <v>7</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="L52" t="s">
-        <v>218</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>138</v>
+        <v>199</v>
       </c>
       <c r="B53" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="C53" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D53" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E53" t="s">
-        <v>139</v>
+        <v>200</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="H53" t="s">
-        <v>140</v>
+        <v>201</v>
       </c>
       <c r="J53">
         <v>15</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L53" t="s">
-        <v>219</v>
+        <v>29</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>15</v>
+        <v>203</v>
       </c>
       <c r="B54" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C54" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D54" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E54" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="F54">
         <v>5</v>
       </c>
       <c r="G54" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="H54" t="s">
         <v>161</v>
@@ -3690,36 +3690,36 @@
         <v>1</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="L54" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="B55" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="C55" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D55" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E55" t="s">
-        <v>290</v>
+        <v>174</v>
       </c>
       <c r="F55">
         <v>3</v>
       </c>
       <c r="G55" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="H55" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I55">
         <v>4</v>
@@ -3728,71 +3728,71 @@
         <v>0</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="L55" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>318</v>
+        <v>88</v>
       </c>
       <c r="N55" t="s">
-        <v>368</v>
+        <v>151</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>63</v>
+        <v>207</v>
       </c>
       <c r="C56" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D56" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="F56">
         <v>5</v>
       </c>
       <c r="H56" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="J56">
         <v>2</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L56" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>35</v>
+        <v>209</v>
       </c>
       <c r="B57" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C57" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D57" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="F57">
         <v>3</v>
       </c>
       <c r="G57" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="H57" t="s">
-        <v>202</v>
+        <v>74</v>
       </c>
       <c r="I57">
         <v>3</v>
@@ -3801,42 +3801,42 @@
         <v>1</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>299</v>
+        <v>210</v>
       </c>
       <c r="L57" t="s">
-        <v>217</v>
+        <v>20</v>
       </c>
       <c r="M57" s="8" t="s">
-        <v>318</v>
+        <v>88</v>
       </c>
       <c r="N57" t="s">
-        <v>380</v>
+        <v>146</v>
       </c>
     </row>
     <row r="58" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="B58" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C58" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="D58" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>33</v>
+        <v>212</v>
       </c>
       <c r="F58">
         <v>18</v>
       </c>
       <c r="G58" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="H58" t="s">
-        <v>126</v>
+        <v>213</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -3845,65 +3845,65 @@
         <v>12</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="L58" t="s">
-        <v>219</v>
+        <v>29</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>123</v>
+        <v>215</v>
       </c>
       <c r="C59" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D59" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E59" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="H59" t="s">
-        <v>122</v>
+        <v>191</v>
       </c>
       <c r="J59">
         <v>0</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="L59" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="B60" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C60" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="D60" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E60" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="F60">
         <v>16</v>
       </c>
       <c r="G60" t="s">
-        <v>260</v>
+        <v>219</v>
       </c>
       <c r="H60" t="s">
-        <v>174</v>
+        <v>220</v>
       </c>
       <c r="I60">
         <v>2</v>
@@ -3912,39 +3912,39 @@
         <v>2</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L60" t="s">
-        <v>218</v>
+        <v>84</v>
       </c>
       <c r="M60" s="7" t="s">
-        <v>427</v>
+        <v>163</v>
       </c>
       <c r="N60" t="s">
-        <v>428</v>
+        <v>222</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="C61" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="D61" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E61" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="F61">
         <v>2</v>
       </c>
       <c r="G61" t="s">
-        <v>98</v>
+        <v>225</v>
       </c>
       <c r="H61" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="I61">
         <v>1</v>
@@ -3953,24 +3953,24 @@
         <v>8</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="L61" t="s">
-        <v>219</v>
+        <v>29</v>
       </c>
     </row>
     <row r="62" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>171</v>
+        <v>228</v>
       </c>
       <c r="C62" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D62" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E62" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="F62">
         <v>3</v>
@@ -3979,62 +3979,62 @@
         <v>1</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="L62" t="s">
-        <v>219</v>
+        <v>29</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>95</v>
+        <v>230</v>
       </c>
       <c r="C63" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D63" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E63" t="s">
-        <v>58</v>
+        <v>231</v>
       </c>
       <c r="F63">
         <v>10</v>
       </c>
       <c r="H63" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J63">
         <v>8</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>133</v>
+        <v>232</v>
       </c>
       <c r="L63" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>57</v>
+        <v>233</v>
       </c>
       <c r="C64" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D64" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E64" t="s">
-        <v>58</v>
+        <v>231</v>
       </c>
       <c r="F64">
         <v>7</v>
       </c>
       <c r="G64" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="H64" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I64">
         <v>4</v>
@@ -4043,30 +4043,30 @@
         <v>9</v>
       </c>
       <c r="L64" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>200</v>
+        <v>234</v>
       </c>
       <c r="C65" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D65" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E65" t="s">
-        <v>70</v>
+        <v>157</v>
       </c>
       <c r="F65">
         <v>4</v>
       </c>
       <c r="G65" t="s">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="H65" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I65">
         <v>2</v>
@@ -4075,50 +4075,50 @@
         <v>5</v>
       </c>
       <c r="L65" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>80</v>
+        <v>235</v>
       </c>
       <c r="C66" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D66" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>83</v>
+        <v>236</v>
       </c>
       <c r="L66" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="67" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>165</v>
+        <v>237</v>
       </c>
       <c r="B67" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C67" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D67" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E67" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="F67">
         <v>2</v>
       </c>
       <c r="G67" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="H67" t="s">
-        <v>37</v>
+        <v>238</v>
       </c>
       <c r="I67">
         <v>3</v>
@@ -4127,56 +4127,56 @@
         <v>0</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="L67" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="68" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>86</v>
+        <v>240</v>
       </c>
       <c r="C68" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D68" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="E68" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H68" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>104</v>
+        <v>241</v>
       </c>
       <c r="L68" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="69" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>191</v>
+        <v>242</v>
       </c>
       <c r="C69" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D69" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E69" t="s">
-        <v>192</v>
+        <v>243</v>
       </c>
       <c r="F69">
         <v>5</v>
       </c>
       <c r="G69" t="s">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="H69" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I69">
         <v>6</v>
@@ -4185,42 +4185,42 @@
         <v>6</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>193</v>
+        <v>244</v>
       </c>
       <c r="L69" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
       <c r="M69" s="9" t="s">
-        <v>316</v>
+        <v>101</v>
       </c>
       <c r="N69" t="s">
-        <v>379</v>
+        <v>89</v>
       </c>
     </row>
     <row r="70" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>166</v>
+        <v>245</v>
       </c>
       <c r="B70" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C70" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D70" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="E70" t="s">
-        <v>97</v>
+        <v>246</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>98</v>
+        <v>225</v>
       </c>
       <c r="H70" t="s">
-        <v>167</v>
+        <v>247</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -4229,39 +4229,39 @@
         <v>15</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="L70" t="s">
-        <v>217</v>
+        <v>20</v>
       </c>
       <c r="M70" s="8" t="s">
-        <v>318</v>
+        <v>88</v>
       </c>
       <c r="N70" t="s">
-        <v>379</v>
+        <v>89</v>
       </c>
     </row>
     <row r="71" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>198</v>
+        <v>249</v>
       </c>
       <c r="C71" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D71" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E71" t="s">
-        <v>289</v>
+        <v>121</v>
       </c>
       <c r="F71">
         <v>5</v>
       </c>
       <c r="G71" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="H71" t="s">
-        <v>37</v>
+        <v>238</v>
       </c>
       <c r="I71">
         <v>4</v>
@@ -4270,33 +4270,33 @@
         <v>1</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>199</v>
+        <v>250</v>
       </c>
       <c r="L71" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="72" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>197</v>
+        <v>251</v>
       </c>
       <c r="C72" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D72" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E72" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="F72">
         <v>3</v>
       </c>
       <c r="G72" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="H72" t="s">
-        <v>202</v>
+        <v>74</v>
       </c>
       <c r="I72">
         <v>2</v>
@@ -4305,33 +4305,33 @@
         <v>0</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>298</v>
+        <v>252</v>
       </c>
       <c r="L72" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="73" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>430</v>
+        <v>253</v>
       </c>
       <c r="C73" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="D73" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E73" t="s">
-        <v>182</v>
+        <v>254</v>
       </c>
       <c r="F73">
         <v>8</v>
       </c>
       <c r="G73" t="s">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="H73" t="s">
-        <v>431</v>
+        <v>255</v>
       </c>
       <c r="I73">
         <v>6</v>
@@ -4340,10 +4340,10 @@
         <v>11</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="L73" t="s">
-        <v>218</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -4374,69 +4374,69 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="M1" t="s">
-        <v>315</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>317</v>
-      </c>
       <c r="O1" s="3" t="s">
-        <v>412</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>97</v>
+        <v>246</v>
       </c>
       <c r="F2">
         <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>260</v>
+        <v>219</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I2">
         <v>6</v>
@@ -4445,33 +4445,33 @@
         <v>3</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>300</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="F3">
         <v>6</v>
       </c>
       <c r="G3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H3" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="I3">
         <v>8</v>
@@ -4480,33 +4480,33 @@
         <v>5</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="F4">
         <v>10</v>
       </c>
       <c r="G4" t="s">
-        <v>150</v>
+        <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I4">
         <v>6</v>
@@ -4515,79 +4515,79 @@
         <v>1</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="H5" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J6">
         <v>5</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="F7">
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="H7" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I7">
         <v>4</v>
@@ -4596,30 +4596,30 @@
         <v>4</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="F8">
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="H8" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -4628,33 +4628,33 @@
         <v>3</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="F9">
         <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>150</v>
+        <v>26</v>
       </c>
       <c r="H9" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="I9">
         <v>9</v>
@@ -4663,33 +4663,33 @@
         <v>2</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>157</v>
+        <v>25</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>150</v>
+        <v>26</v>
       </c>
       <c r="H10" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -4698,30 +4698,30 @@
         <v>1</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>192</v>
+        <v>243</v>
       </c>
       <c r="F11">
         <v>5</v>
       </c>
       <c r="G11" t="s">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="H11" t="s">
-        <v>226</v>
+        <v>282</v>
       </c>
       <c r="I11">
         <v>4</v>
@@ -4730,21 +4730,21 @@
         <v>6</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="F12">
         <v>10</v>
@@ -4753,56 +4753,56 @@
         <v>0</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="F13">
         <v>6</v>
       </c>
       <c r="H13" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="F14">
         <v>4</v>
       </c>
       <c r="G14" t="s">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="H14" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I14">
         <v>7</v>
@@ -4811,21 +4811,21 @@
         <v>4</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -4834,30 +4834,30 @@
         <v>1</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E16" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="F16">
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="H16" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="I16">
         <v>10</v>
@@ -4866,30 +4866,30 @@
         <v>6</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>184</v>
+        <v>106</v>
       </c>
       <c r="F17">
         <v>3</v>
       </c>
       <c r="G17" t="s">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="H17" t="s">
-        <v>202</v>
+        <v>74</v>
       </c>
       <c r="I17">
         <v>2</v>
@@ -4898,30 +4898,30 @@
         <v>4</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="F18">
         <v>2</v>
       </c>
       <c r="G18" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="H18" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="I18">
         <v>4</v>
@@ -4930,33 +4930,33 @@
         <v>0</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E19" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="F19">
         <v>6</v>
       </c>
       <c r="G19" t="s">
-        <v>260</v>
+        <v>219</v>
       </c>
       <c r="H19" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="I19">
         <v>5</v>
@@ -4965,30 +4965,30 @@
         <v>5</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="F20">
         <v>3</v>
       </c>
       <c r="G20" t="s">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="H20" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -4997,18 +4997,18 @@
         <v>0</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F21">
         <v>60</v>
@@ -5017,30 +5017,30 @@
         <v>0</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E22" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="F22">
         <v>5</v>
       </c>
       <c r="G22" t="s">
-        <v>260</v>
+        <v>219</v>
       </c>
       <c r="H22" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="I22">
         <v>2</v>
@@ -5049,41 +5049,41 @@
         <v>4</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C24" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E24" t="s">
-        <v>291</v>
+        <v>114</v>
       </c>
       <c r="F24">
         <v>5</v>
       </c>
       <c r="G24" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="H24" t="s">
         <v>161</v>
@@ -5095,30 +5095,30 @@
         <v>4</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C25" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="F25">
         <v>7</v>
       </c>
       <c r="G25" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="H25" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I25">
         <v>4</v>
@@ -5129,16 +5129,16 @@
     </row>
     <row r="26" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C26" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E26" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="F26">
         <v>6</v>
@@ -5147,30 +5147,30 @@
         <v>0</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C27" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>97</v>
+        <v>246</v>
       </c>
       <c r="F27">
         <v>3</v>
       </c>
       <c r="G27" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H27" t="s">
-        <v>37</v>
+        <v>238</v>
       </c>
       <c r="I27">
         <v>1</v>
@@ -5179,30 +5179,30 @@
         <v>0</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C28" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E28" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F28">
         <v>3</v>
       </c>
       <c r="G28" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="H28" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I28">
         <v>5</v>
@@ -5211,55 +5211,55 @@
         <v>2</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C29" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C31" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E31" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F31">
         <v>10</v>
       </c>
       <c r="H31" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -5268,7 +5268,7 @@
         <v>2</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -5276,13 +5276,13 @@
         <v>335</v>
       </c>
       <c r="C32" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E32" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="F32">
         <v>3</v>
@@ -5299,10 +5299,10 @@
         <v>336</v>
       </c>
       <c r="C33" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E33" t="s">
         <v>337</v>
@@ -5311,7 +5311,7 @@
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>260</v>
+        <v>219</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -5322,28 +5322,28 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E34" t="s">
-        <v>291</v>
+        <v>114</v>
       </c>
       <c r="F34">
         <v>10</v>
       </c>
       <c r="G34" t="s">
-        <v>150</v>
+        <v>26</v>
       </c>
       <c r="H34" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I34">
         <v>2</v>
@@ -5352,76 +5352,76 @@
         <v>2</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C35" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D35" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E35" t="s">
-        <v>291</v>
+        <v>114</v>
       </c>
       <c r="F35">
         <v>3</v>
       </c>
       <c r="G35" t="s">
-        <v>260</v>
+        <v>219</v>
       </c>
       <c r="J35">
         <v>0</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>344</v>
+      </c>
+      <c r="C36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" t="s">
         <v>345</v>
       </c>
-      <c r="C36" t="s">
-        <v>78</v>
-      </c>
-      <c r="D36" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" t="s">
+      <c r="H36" t="s">
+        <v>18</v>
+      </c>
+      <c r="K36" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="H36" t="s">
-        <v>102</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>347</v>
+      </c>
+      <c r="C37" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" t="s">
         <v>348</v>
-      </c>
-      <c r="C37" t="s">
-        <v>8</v>
-      </c>
-      <c r="D37" t="s">
-        <v>16</v>
-      </c>
-      <c r="E37" t="s">
-        <v>349</v>
       </c>
       <c r="F37">
         <v>5</v>
       </c>
       <c r="G37" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H37" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="I37">
         <v>3</v>
@@ -5430,53 +5430,53 @@
         <v>0</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>350</v>
+      </c>
+      <c r="C38" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" t="s">
+        <v>46</v>
+      </c>
+      <c r="E38" t="s">
+        <v>77</v>
+      </c>
+      <c r="H38" t="s">
+        <v>18</v>
+      </c>
+      <c r="K38" s="1" t="s">
         <v>351</v>
-      </c>
-      <c r="C38" t="s">
-        <v>78</v>
-      </c>
-      <c r="D38" t="s">
-        <v>79</v>
-      </c>
-      <c r="E38" t="s">
-        <v>84</v>
-      </c>
-      <c r="H38" t="s">
-        <v>102</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>352</v>
+      </c>
+      <c r="B39" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" t="s">
         <v>353</v>
-      </c>
-      <c r="B39" t="s">
-        <v>28</v>
-      </c>
-      <c r="C39" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" t="s">
-        <v>16</v>
-      </c>
-      <c r="E39" t="s">
-        <v>354</v>
       </c>
       <c r="F39">
         <v>4</v>
       </c>
       <c r="G39" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="H39" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="I39">
         <v>8</v>
@@ -5485,59 +5485,59 @@
         <v>4</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C40" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D40" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E40" t="s">
-        <v>70</v>
+        <v>157</v>
       </c>
       <c r="F40">
         <v>3</v>
       </c>
       <c r="H40" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="J40">
         <v>0</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>357</v>
+      </c>
+      <c r="B41" t="s">
+        <v>133</v>
+      </c>
+      <c r="C41" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" t="s">
         <v>358</v>
-      </c>
-      <c r="B41" t="s">
-        <v>43</v>
-      </c>
-      <c r="C41" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" t="s">
-        <v>359</v>
       </c>
       <c r="F41">
         <v>5</v>
       </c>
       <c r="G41" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="H41" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="I41">
         <v>8</v>
@@ -5546,21 +5546,21 @@
         <v>3</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B42" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="C42" t="s">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="D42" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F42">
         <v>50</v>
@@ -5569,33 +5569,33 @@
         <v>1</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>363</v>
+      </c>
+      <c r="B43" t="s">
+        <v>58</v>
+      </c>
+      <c r="C43" t="s">
+        <v>80</v>
+      </c>
+      <c r="D43" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" t="s">
         <v>364</v>
-      </c>
-      <c r="B43" t="s">
-        <v>28</v>
-      </c>
-      <c r="C43" t="s">
-        <v>24</v>
-      </c>
-      <c r="D43" t="s">
-        <v>16</v>
-      </c>
-      <c r="E43" t="s">
-        <v>365</v>
       </c>
       <c r="F43">
         <v>5</v>
       </c>
       <c r="G43" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H43" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="I43">
         <v>4</v>
@@ -5609,28 +5609,28 @@
     </row>
     <row r="44" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B44" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C44" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D44" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E44" t="s">
-        <v>144</v>
+        <v>17</v>
       </c>
       <c r="F44">
         <v>4</v>
       </c>
       <c r="G44" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H44" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="I44">
         <v>5</v>
@@ -5639,33 +5639,33 @@
         <v>4</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B45" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="C45" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E45" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F45">
         <v>4</v>
       </c>
       <c r="G45" t="s">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="H45" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="I45">
         <v>14</v>
@@ -5676,82 +5676,82 @@
     </row>
     <row r="46" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C46" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E46" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C47" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D47" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="E47" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C48" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D48" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E48" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="F48">
         <v>5</v>
       </c>
       <c r="H48" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="J48">
         <v>3</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C49" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E49" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="F49">
         <v>40</v>
       </c>
       <c r="G49" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="H49" t="s">
         <v>130</v>
@@ -5763,67 +5763,67 @@
         <v>0</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
     </row>
     <row r="50" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="C50" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D50" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E50" t="s">
-        <v>97</v>
+        <v>246</v>
       </c>
       <c r="H50" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
     </row>
     <row r="51" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C51" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B52" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="C52" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D52" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E52" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="F52">
         <v>6</v>
       </c>
       <c r="G52" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="H52" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I52">
         <v>6</v>
@@ -5832,130 +5832,130 @@
         <v>2</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C53" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D53" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E53" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B54" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D54" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="E54" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B55" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="C55" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D55" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="E55" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B56" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="C56" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D56" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E56" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B57" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="C57" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D57" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="H57" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C58" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D58" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="F58">
         <v>7</v>
       </c>
       <c r="G58" t="s">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="H58" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I58">
         <v>8</v>
@@ -5964,33 +5964,33 @@
         <v>4</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B59" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C59" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="D59" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E59" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="F59">
         <v>7</v>
       </c>
       <c r="G59" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="H59" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="I59">
         <v>5</v>
@@ -5999,33 +5999,33 @@
         <v>5</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="B60" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C60" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D60" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E60" t="s">
-        <v>29</v>
+        <v>404</v>
       </c>
       <c r="F60">
         <v>3</v>
       </c>
       <c r="G60" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="H60" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="I60">
         <v>7</v>
@@ -6034,33 +6034,33 @@
         <v>0</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B61" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C61" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="D61" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E61" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="F61">
         <v>4</v>
       </c>
       <c r="G61" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H61" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="I61">
         <v>12</v>
@@ -6069,67 +6069,67 @@
         <v>7</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B62" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C62" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D62" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E62" t="s">
-        <v>291</v>
+        <v>114</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C63" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D63" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C64" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="D64" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E64" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="F64">
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>150</v>
+        <v>26</v>
       </c>
       <c r="H64" t="s">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="I64">
         <v>10</v>
@@ -6138,30 +6138,30 @@
         <v>4</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C65" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D65" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E65" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="F65">
         <v>12</v>
       </c>
       <c r="H65" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -6172,33 +6172,39 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C66" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D66" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E66" t="s">
-        <v>291</v>
+        <v>114</v>
       </c>
       <c r="G66" t="s">
-        <v>260</v>
+        <v>219</v>
+      </c>
+      <c r="H66" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="C67" t="s">
+        <v>80</v>
+      </c>
+      <c r="D67" t="s">
         <v>24</v>
       </c>
       <c r="G67" t="s">
-        <v>260</v>
+        <v>219</v>
       </c>
       <c r="H67" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -6224,267 +6230,267 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>166</v>
+        <v>245</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>225</v>
       </c>
       <c r="C2" t="s">
-        <v>167</v>
+        <v>247</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>122</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>203</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
         <v>161</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>125</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>184</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>233</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>202</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>132</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>171</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>173</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>186</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -6492,180 +6498,180 @@
         <v>159</v>
       </c>
       <c r="B20" t="s">
-        <v>150</v>
+        <v>26</v>
       </c>
       <c r="C20" t="s">
         <v>161</v>
       </c>
       <c r="D20" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>150</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>154</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>150</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>151</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
-        <v>150</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="B24" t="s">
-        <v>150</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>144</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="C25" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>209</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="C26" t="s">
-        <v>202</v>
+        <v>74</v>
       </c>
       <c r="D26" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>165</v>
+        <v>237</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="C27" t="s">
-        <v>37</v>
+        <v>238</v>
       </c>
       <c r="D27" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="D30" t="s">
-        <v>94</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="B31" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="C31" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="D31" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>116</v>
       </c>
       <c r="B32" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D32" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B33" t="s">
         <v>129</v>
@@ -6674,457 +6680,457 @@
         <v>130</v>
       </c>
       <c r="D33" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>126</v>
+        <v>213</v>
       </c>
       <c r="D34" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C35" t="s">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="D35" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C36" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="D36" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="B37" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="D37" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C38" t="s">
-        <v>174</v>
+        <v>220</v>
       </c>
       <c r="D38" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="B39" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="D39" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>143</v>
+        <v>14</v>
       </c>
       <c r="C40" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="D41" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="C42" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="D42" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>119</v>
+        <v>423</v>
       </c>
       <c r="C43" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>86</v>
+        <v>240</v>
       </c>
       <c r="C44" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="D45" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D46" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="D47" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>77</v>
+        <v>193</v>
       </c>
       <c r="D48" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>80</v>
+        <v>235</v>
       </c>
       <c r="D49" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>136</v>
+        <v>30</v>
       </c>
       <c r="C50" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="D50" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="C51" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="D51" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>69</v>
+        <v>156</v>
       </c>
       <c r="C52" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="D52" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>90</v>
+        <v>175</v>
       </c>
       <c r="C53" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="D53" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>87</v>
+        <v>178</v>
       </c>
       <c r="C54" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="D54" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>63</v>
+        <v>207</v>
       </c>
       <c r="C55" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="D55" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="C56" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D56" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>95</v>
+        <v>230</v>
       </c>
       <c r="C57" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D57" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>138</v>
+        <v>199</v>
       </c>
       <c r="C58" t="s">
-        <v>140</v>
+        <v>201</v>
       </c>
       <c r="D58" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>123</v>
+        <v>215</v>
       </c>
       <c r="C59" t="s">
-        <v>122</v>
+        <v>191</v>
       </c>
       <c r="D59" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>171</v>
+        <v>228</v>
       </c>
       <c r="D60" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>190</v>
+        <v>424</v>
       </c>
       <c r="B61" t="s">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="C61" t="s">
-        <v>189</v>
+        <v>425</v>
       </c>
       <c r="D61" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>179</v>
+        <v>71</v>
       </c>
       <c r="D62" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>183</v>
+        <v>105</v>
       </c>
       <c r="B63" t="s">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="C63" t="s">
-        <v>185</v>
+        <v>108</v>
       </c>
       <c r="D63" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="B64" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="C64" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D64" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>191</v>
+        <v>242</v>
       </c>
       <c r="B65" t="s">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="C65" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D65" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>195</v>
+        <v>140</v>
       </c>
       <c r="B66" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="C66" t="s">
-        <v>195</v>
+        <v>140</v>
       </c>
       <c r="D66" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>197</v>
+        <v>251</v>
       </c>
       <c r="B67" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="C67" t="s">
-        <v>202</v>
+        <v>74</v>
       </c>
       <c r="D67" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>198</v>
+        <v>249</v>
       </c>
       <c r="B68" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="C68" t="s">
-        <v>37</v>
+        <v>238</v>
       </c>
       <c r="D68" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>200</v>
+        <v>234</v>
       </c>
       <c r="B69" t="s">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="C69" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D69" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>201</v>
+        <v>73</v>
       </c>
       <c r="B70" t="s">
-        <v>150</v>
+        <v>26</v>
       </c>
       <c r="C70" t="s">
-        <v>202</v>
+        <v>74</v>
       </c>
       <c r="D70" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C71" t="s">
-        <v>122</v>
+        <v>191</v>
       </c>
       <c r="D71" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>211</v>
+        <v>165</v>
       </c>
       <c r="D72" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -7156,60 +7162,60 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>215</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>213</v>
+        <v>426</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>192</v>
+        <v>243</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="H2" t="s">
-        <v>226</v>
+        <v>282</v>
       </c>
       <c r="I2">
         <v>6</v>
@@ -7218,10 +7224,10 @@
         <v>10</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>214</v>
+        <v>427</v>
       </c>
       <c r="L2" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7246,37 +7252,37 @@
   <sheetData>
     <row r="1" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="10" t="s">
-        <v>224</v>
+        <v>428</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10" t="s">
-        <v>225</v>
+        <v>429</v>
       </c>
       <c r="D1" s="10"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>222</v>
+        <v>430</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>223</v>
+        <v>431</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>222</v>
+        <v>430</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>223</v>
+        <v>431</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>116</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -7286,18 +7292,18 @@
         <v>40</v>
       </c>
       <c r="H3" t="s">
-        <v>151</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -7307,114 +7313,114 @@
         <v>40</v>
       </c>
       <c r="H4" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>209</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>171</v>
+        <v>228</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>227</v>
+        <v>432</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>125</v>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>228</v>
+        <v>433</v>
       </c>
       <c r="D7">
         <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>213</v>
+        <v>426</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="B8">
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>23</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>171</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
       <c r="H9" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="B10">
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>154</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="H10" t="s">
-        <v>6</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="B11">
         <v>3</v>
@@ -7426,109 +7432,109 @@
         <v>3</v>
       </c>
       <c r="H11" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>151</v>
+        <v>49</v>
       </c>
       <c r="B12">
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>154</v>
+        <v>41</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
       <c r="H12" t="s">
-        <v>14</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>203</v>
       </c>
       <c r="B13">
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>151</v>
+        <v>49</v>
       </c>
       <c r="D13">
         <v>3</v>
       </c>
       <c r="H13" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>184</v>
       </c>
       <c r="B14">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>156</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
       <c r="H14" t="s">
-        <v>15</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>233</v>
       </c>
       <c r="B15">
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="D15">
         <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>35</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>213</v>
+        <v>426</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="D16">
         <v>3</v>
       </c>
       <c r="H16" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="B17">
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D17">
         <v>3</v>
       </c>
       <c r="H17" t="s">
-        <v>57</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -7731,14 +7737,8 @@
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2853C30-6322-4EA0-9233-C02855FA666C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="f5235b4c-d799-48fb-911b-9341dfbcb198"/>
   </ds:schemaRefs>
 </ds:datastoreItem>

--- a/Alpha Set List.xlsx
+++ b/Alpha Set List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\apoke\Desktop\Advance!Tactics\Advance-Tactics-Tcgarena\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47DCAE94-7B1A-49FD-BF75-7ADC8598953D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE4F667-79D7-4487-90E7-6218F3B6988C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="1" xr2:uid="{CA094A51-376D-41C2-95CA-6278B694BA34}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{CA094A51-376D-41C2-95CA-6278B694BA34}"/>
   </bookViews>
   <sheets>
     <sheet name="Set1 - Alpha" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="434">
   <si>
     <t>Card Name</t>
   </si>
@@ -4077,6 +4077,12 @@
       <c r="L65" t="s">
         <v>35</v>
       </c>
+      <c r="M65" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="N65" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
@@ -7700,20 +7706,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="f5235b4c-d799-48fb-911b-9341dfbcb198" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="f5235b4c-d799-48fb-911b-9341dfbcb198" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7735,6 +7741,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A915AD6-87DB-4A49-8A2C-415A966F3ADD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2853C30-6322-4EA0-9233-C02855FA666C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -7742,12 +7756,4 @@
     <ds:schemaRef ds:uri="f5235b4c-d799-48fb-911b-9341dfbcb198"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A915AD6-87DB-4A49-8A2C-415A966F3ADD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Alpha Set List.xlsx
+++ b/Alpha Set List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\apoke\Desktop\Advance!Tactics\Advance-Tactics-Tcgarena\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE4F667-79D7-4487-90E7-6218F3B6988C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{35E12D45-7F10-4534-95A3-22A49A69B2B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{CA094A51-376D-41C2-95CA-6278B694BA34}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1365" uniqueCount="431">
   <si>
     <t>Card Name</t>
   </si>
@@ -311,9 +311,6 @@
     <t>Golem</t>
   </si>
   <si>
-    <t>Finished</t>
-  </si>
-  <si>
     <t>Chuck Carr</t>
   </si>
   <si>
@@ -348,9 +345,6 @@
   </si>
   <si>
     <t>Trigger: Flip 2 coins. If either are tails, triggering unit moves backwards 1 tile.</t>
-  </si>
-  <si>
-    <t>Outlined</t>
   </si>
   <si>
     <t>Exhaustive Research</t>
@@ -544,9 +538,6 @@
     <t>Range 2</t>
   </si>
   <si>
-    <t>In Progress</t>
-  </si>
-  <si>
     <t>Ryan Chalmers</t>
   </si>
   <si>
@@ -1006,9 +997,6 @@
   </si>
   <si>
     <t>Zh'Aedinn's Factory</t>
-  </si>
-  <si>
-    <t>Post-Produce: Two random basic resources. If they do, produce one Metal.</t>
   </si>
   <si>
     <t>Fun Gus</t>
@@ -1250,9 +1238,6 @@
     <t>Counter-Strategy</t>
   </si>
   <si>
-    <t>Put a chosen card planned card into it's owners discard pile.</t>
-  </si>
-  <si>
     <t>Divine Intervention</t>
   </si>
   <si>
@@ -1382,13 +1367,19 @@
   </si>
   <si>
     <t>Ants insatiable</t>
+  </si>
+  <si>
+    <t>Post-Produce: Two random basic resources decay. If they do, produce one Metal.</t>
+  </si>
+  <si>
+    <t>Put a chosen planned card into it's owners discard pile.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1413,14 +1404,6 @@
     <font>
       <sz val="20"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1461,11 +1444,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1475,7 +1457,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1486,8 +1467,7 @@
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1840,7 +1820,7 @@
     <col min="8" max="8" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="36.42578125" style="1" customWidth="1"/>
     <col min="12" max="12" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="24" x14ac:dyDescent="0.4">
@@ -1880,10 +1860,7 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1951,7 +1928,6 @@
       <c r="L3" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="5"/>
       <c r="P3">
         <f>COUNTIF(L:L, "Uncommon")</f>
         <v>18</v>
@@ -2321,7 +2297,7 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C15" t="s">
@@ -2353,6 +2329,9 @@
       </c>
       <c r="L15" t="s">
         <v>29</v>
+      </c>
+      <c r="M15" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -2378,7 +2357,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="60.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>79</v>
       </c>
@@ -2413,8 +2392,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
         <v>85</v>
       </c>
       <c r="C18" t="s">
@@ -2444,16 +2423,13 @@
       <c r="L18" t="s">
         <v>35</v>
       </c>
-      <c r="M18" s="8" t="s">
+      <c r="M18" t="s">
         <v>88</v>
       </c>
-      <c r="N18" t="s">
+    </row>
+    <row r="19" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>89</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>90</v>
       </c>
       <c r="B19" t="s">
         <v>58</v>
@@ -2465,18 +2441,18 @@
         <v>24</v>
       </c>
       <c r="E19" t="s">
+        <v>90</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="L19" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="48.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B20" t="s">
         <v>58</v>
@@ -2488,7 +2464,7 @@
         <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F20">
         <v>8</v>
@@ -2497,7 +2473,7 @@
         <v>53</v>
       </c>
       <c r="H20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I20">
         <v>11</v>
@@ -2506,15 +2482,15 @@
         <v>5</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L20" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>97</v>
+    <row r="21" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="B21" t="s">
         <v>58</v>
@@ -2526,33 +2502,30 @@
         <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F21">
         <v>12</v>
       </c>
       <c r="H21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L21" t="s">
         <v>35</v>
       </c>
-      <c r="M21" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="N21" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M21" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
         <v>15</v>
@@ -2561,18 +2534,18 @@
         <v>16</v>
       </c>
       <c r="E22" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s">
         <v>23</v>
@@ -2581,16 +2554,16 @@
         <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F23">
         <v>4</v>
       </c>
       <c r="G23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H23" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I23">
         <v>2</v>
@@ -2599,15 +2572,15 @@
         <v>6</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L23" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C24" t="s">
         <v>31</v>
@@ -2616,7 +2589,7 @@
         <v>24</v>
       </c>
       <c r="E24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F24">
         <v>3</v>
@@ -2628,15 +2601,15 @@
         <v>0</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="L24" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B25" t="s">
         <v>22</v>
@@ -2648,7 +2621,7 @@
         <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F25">
         <v>10</v>
@@ -2666,15 +2639,15 @@
         <v>0</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="L25" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="60.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B26" t="s">
         <v>62</v>
@@ -2686,7 +2659,7 @@
         <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F26">
         <v>10</v>
@@ -2695,7 +2668,7 @@
         <v>64</v>
       </c>
       <c r="H26" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I26">
         <v>8</v>
@@ -2704,15 +2677,15 @@
         <v>2</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L26" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>120</v>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>118</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -2721,7 +2694,7 @@
         <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -2741,16 +2714,13 @@
       <c r="L27" t="s">
         <v>20</v>
       </c>
-      <c r="M27" s="8" t="s">
+      <c r="M27" t="s">
         <v>88</v>
       </c>
-      <c r="N27" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
@@ -2768,7 +2738,7 @@
         <v>64</v>
       </c>
       <c r="H28" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I28">
         <v>3</v>
@@ -2777,15 +2747,15 @@
         <v>1</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="L28" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B29" t="s">
         <v>62</v>
@@ -2815,15 +2785,15 @@
         <v>1</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L29" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>127</v>
+    <row r="30" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>125</v>
       </c>
       <c r="B30" t="s">
         <v>22</v>
@@ -2835,16 +2805,16 @@
         <v>24</v>
       </c>
       <c r="E30" t="s">
+        <v>126</v>
+      </c>
+      <c r="F30">
+        <v>24</v>
+      </c>
+      <c r="G30" t="s">
+        <v>127</v>
+      </c>
+      <c r="H30" t="s">
         <v>128</v>
-      </c>
-      <c r="F30">
-        <v>24</v>
-      </c>
-      <c r="G30" t="s">
-        <v>129</v>
-      </c>
-      <c r="H30" t="s">
-        <v>130</v>
       </c>
       <c r="I30">
         <v>21</v>
@@ -2853,33 +2823,30 @@
         <v>3</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L30" t="s">
         <v>29</v>
       </c>
-      <c r="M30" s="8" t="s">
+      <c r="M30" t="s">
         <v>88</v>
       </c>
-      <c r="N30" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>130</v>
+      </c>
+      <c r="B31" t="s">
+        <v>131</v>
+      </c>
+      <c r="C31" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" t="s">
         <v>132</v>
-      </c>
-      <c r="B31" t="s">
-        <v>133</v>
-      </c>
-      <c r="C31" t="s">
-        <v>23</v>
-      </c>
-      <c r="D31" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" t="s">
-        <v>134</v>
       </c>
       <c r="F31">
         <v>16</v>
@@ -2897,15 +2864,15 @@
         <v>4</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L31" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="72.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="72.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B32" t="s">
         <v>62</v>
@@ -2917,7 +2884,7 @@
         <v>16</v>
       </c>
       <c r="E32" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F32">
         <v>5</v>
@@ -2926,7 +2893,7 @@
         <v>38</v>
       </c>
       <c r="H32" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I32">
         <v>17</v>
@@ -2935,18 +2902,18 @@
         <v>5</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L32" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="48.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B33" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C33" t="s">
         <v>80</v>
@@ -2955,16 +2922,16 @@
         <v>24</v>
       </c>
       <c r="E33" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F33">
         <v>7</v>
       </c>
       <c r="G33" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H33" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I33">
         <v>4</v>
@@ -2973,15 +2940,15 @@
         <v>3</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L33" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>144</v>
+    <row r="34" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
+        <v>142</v>
       </c>
       <c r="B34" t="s">
         <v>58</v>
@@ -3011,24 +2978,21 @@
         <v>3</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L34" t="s">
         <v>35</v>
       </c>
-      <c r="M34" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="N34" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>147</v>
+      <c r="M34" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
+        <v>145</v>
       </c>
       <c r="B35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C35" t="s">
         <v>80</v>
@@ -3037,16 +3001,16 @@
         <v>24</v>
       </c>
       <c r="E35" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F35">
         <v>11</v>
       </c>
       <c r="G35" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H35" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I35">
         <v>7</v>
@@ -3055,21 +3019,18 @@
         <v>6</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="L35" t="s">
         <v>84</v>
       </c>
-      <c r="M35" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="N35" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="M35" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B36" t="s">
         <v>22</v>
@@ -3081,18 +3042,18 @@
         <v>24</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L36" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B37" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C37" t="s">
         <v>23</v>
@@ -3119,18 +3080,18 @@
         <v>2</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="L37" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B38" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C38" t="s">
         <v>31</v>
@@ -3139,7 +3100,7 @@
         <v>24</v>
       </c>
       <c r="E38" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F38">
         <v>4</v>
@@ -3151,15 +3112,15 @@
         <v>1</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="L38" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>159</v>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
+        <v>157</v>
       </c>
       <c r="C39" t="s">
         <v>23</v>
@@ -3168,7 +3129,7 @@
         <v>24</v>
       </c>
       <c r="E39" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F39">
         <v>7</v>
@@ -3177,7 +3138,7 @@
         <v>26</v>
       </c>
       <c r="H39" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I39">
         <v>3</v>
@@ -3186,21 +3147,18 @@
         <v>2</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="L39" t="s">
         <v>35</v>
       </c>
-      <c r="M39" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="N39" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M39" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C40" t="s">
         <v>15</v>
@@ -3209,30 +3167,30 @@
         <v>46</v>
       </c>
       <c r="E40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="L40" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B41" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C41" t="s">
         <v>23</v>
       </c>
       <c r="D41" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E41" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F41">
         <v>8</v>
@@ -3253,12 +3211,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B42" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C42" t="s">
         <v>23</v>
@@ -3285,18 +3243,18 @@
         <v>6</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L42" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B43" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C43" t="s">
         <v>23</v>
@@ -3305,7 +3263,7 @@
         <v>24</v>
       </c>
       <c r="E43" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F43">
         <v>10</v>
@@ -3326,9 +3284,9 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B44" t="s">
         <v>58</v>
@@ -3340,7 +3298,7 @@
         <v>24</v>
       </c>
       <c r="E44" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F44">
         <v>8</v>
@@ -3352,15 +3310,15 @@
         <v>0</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L44" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="48.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B45" t="s">
         <v>58</v>
@@ -3372,7 +3330,7 @@
         <v>24</v>
       </c>
       <c r="E45" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F45">
         <v>5</v>
@@ -3384,15 +3342,15 @@
         <v>9</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="L45" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>181</v>
+    <row r="46" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
+        <v>178</v>
       </c>
       <c r="C46" t="s">
         <v>15</v>
@@ -3401,27 +3359,24 @@
         <v>16</v>
       </c>
       <c r="E46" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H46" t="s">
         <v>18</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="L46" t="s">
         <v>20</v>
       </c>
-      <c r="M46" s="8" t="s">
+      <c r="M46" t="s">
         <v>88</v>
       </c>
-      <c r="N46" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>184</v>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="8" t="s">
+        <v>181</v>
       </c>
       <c r="B47" t="s">
         <v>62</v>
@@ -3433,7 +3388,7 @@
         <v>16</v>
       </c>
       <c r="E47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F47">
         <v>3</v>
@@ -3451,21 +3406,18 @@
         <v>0</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="L47" t="s">
         <v>35</v>
       </c>
-      <c r="M47" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="N47" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="M47" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B48" t="s">
         <v>62</v>
@@ -3495,15 +3447,15 @@
         <v>0</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="L48" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>188</v>
+    <row r="49" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="8" t="s">
+        <v>185</v>
       </c>
       <c r="C49" t="s">
         <v>23</v>
@@ -3512,7 +3464,7 @@
         <v>24</v>
       </c>
       <c r="E49" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F49">
         <v>1</v>
@@ -3530,21 +3482,18 @@
         <v>1</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="L49" t="s">
         <v>20</v>
       </c>
-      <c r="M49" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="N49" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" ht="48.75" x14ac:dyDescent="0.25">
+      <c r="M49" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C50" t="s">
         <v>31</v>
@@ -3553,27 +3502,27 @@
         <v>24</v>
       </c>
       <c r="E50" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
       <c r="H50" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="J50">
         <v>0</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="L50" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C51" t="s">
         <v>15</v>
@@ -3582,15 +3531,15 @@
         <v>46</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="L51" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="48.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B52" t="s">
         <v>62</v>
@@ -3602,7 +3551,7 @@
         <v>24</v>
       </c>
       <c r="E52" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F52">
         <v>7</v>
@@ -3611,7 +3560,7 @@
         <v>38</v>
       </c>
       <c r="H52" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I52">
         <v>7</v>
@@ -3620,15 +3569,15 @@
         <v>7</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="L52" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="48.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B53" t="s">
         <v>22</v>
@@ -3640,27 +3589,27 @@
         <v>24</v>
       </c>
       <c r="E53" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="H53" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="J53">
         <v>15</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="L53" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B54" t="s">
         <v>62</v>
@@ -3681,7 +3630,7 @@
         <v>64</v>
       </c>
       <c r="H54" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I54">
         <v>7</v>
@@ -3690,18 +3639,18 @@
         <v>1</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="L54" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="48.75" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>205</v>
+    <row r="55" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="7" t="s">
+        <v>202</v>
       </c>
       <c r="B55" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C55" t="s">
         <v>23</v>
@@ -3710,13 +3659,13 @@
         <v>24</v>
       </c>
       <c r="E55" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F55">
         <v>3</v>
       </c>
       <c r="G55" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H55" t="s">
         <v>27</v>
@@ -3728,21 +3677,18 @@
         <v>0</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="L55" t="s">
         <v>35</v>
       </c>
-      <c r="M55" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="N55" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="M55" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C56" t="s">
         <v>31</v>
@@ -3751,7 +3697,7 @@
         <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F56">
         <v>5</v>
@@ -3763,15 +3709,15 @@
         <v>2</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="L56" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>209</v>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" s="7" t="s">
+        <v>206</v>
       </c>
       <c r="B57" t="s">
         <v>58</v>
@@ -3801,21 +3747,18 @@
         <v>1</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L57" t="s">
         <v>20</v>
       </c>
-      <c r="M57" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="N57" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="M57" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B58" t="s">
         <v>58</v>
@@ -3827,7 +3770,7 @@
         <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F58">
         <v>18</v>
@@ -3836,7 +3779,7 @@
         <v>87</v>
       </c>
       <c r="H58" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -3845,15 +3788,15 @@
         <v>12</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="L58" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C59" t="s">
         <v>31</v>
@@ -3862,27 +3805,27 @@
         <v>24</v>
       </c>
       <c r="E59" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="H59" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="J59">
         <v>0</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="L59" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>217</v>
+    <row r="60" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="A60" s="6" t="s">
+        <v>214</v>
       </c>
       <c r="B60" t="s">
         <v>62</v>
@@ -3894,16 +3837,16 @@
         <v>24</v>
       </c>
       <c r="E60" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F60">
         <v>16</v>
       </c>
       <c r="G60" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H60" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I60">
         <v>2</v>
@@ -3912,21 +3855,18 @@
         <v>2</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="L60" t="s">
         <v>84</v>
       </c>
-      <c r="M60" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="N60" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="M60" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C61" t="s">
         <v>80</v>
@@ -3935,16 +3875,16 @@
         <v>24</v>
       </c>
       <c r="E61" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F61">
         <v>2</v>
       </c>
       <c r="G61" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H61" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I61">
         <v>1</v>
@@ -3953,15 +3893,15 @@
         <v>8</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L61" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C62" t="s">
         <v>31</v>
@@ -3979,15 +3919,15 @@
         <v>1</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="L62" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C63" t="s">
         <v>31</v>
@@ -3996,27 +3936,27 @@
         <v>24</v>
       </c>
       <c r="E63" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F63">
         <v>10</v>
       </c>
       <c r="H63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J63">
         <v>8</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="L63" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C64" t="s">
         <v>23</v>
@@ -4025,7 +3965,7 @@
         <v>24</v>
       </c>
       <c r="E64" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F64">
         <v>7</v>
@@ -4046,9 +3986,9 @@
         <v>35</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>234</v>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" s="8" t="s">
+        <v>231</v>
       </c>
       <c r="C65" t="s">
         <v>23</v>
@@ -4057,13 +3997,13 @@
         <v>24</v>
       </c>
       <c r="E65" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F65">
         <v>4</v>
       </c>
       <c r="G65" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H65" t="s">
         <v>27</v>
@@ -4077,16 +4017,13 @@
       <c r="L65" t="s">
         <v>35</v>
       </c>
-      <c r="M65" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="N65" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M65" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C66" t="s">
         <v>15</v>
@@ -4095,15 +4032,15 @@
         <v>16</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="L66" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B67" t="s">
         <v>62</v>
@@ -4124,7 +4061,7 @@
         <v>53</v>
       </c>
       <c r="H67" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I67">
         <v>3</v>
@@ -4133,15 +4070,15 @@
         <v>0</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="L67" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C68" t="s">
         <v>15</v>
@@ -4156,15 +4093,15 @@
         <v>18</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="L68" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>242</v>
+    <row r="69" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="A69" s="8" t="s">
+        <v>239</v>
       </c>
       <c r="C69" t="s">
         <v>23</v>
@@ -4173,13 +4110,13 @@
         <v>24</v>
       </c>
       <c r="E69" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F69">
         <v>5</v>
       </c>
       <c r="G69" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H69" t="s">
         <v>27</v>
@@ -4191,21 +4128,18 @@
         <v>6</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="L69" t="s">
         <v>35</v>
       </c>
-      <c r="M69" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="N69" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>245</v>
+      <c r="M69" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="A70" s="7" t="s">
+        <v>242</v>
       </c>
       <c r="B70" t="s">
         <v>62</v>
@@ -4217,16 +4151,16 @@
         <v>46</v>
       </c>
       <c r="E70" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H70" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -4235,21 +4169,18 @@
         <v>15</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="L70" t="s">
         <v>20</v>
       </c>
-      <c r="M70" s="8" t="s">
+      <c r="M70" t="s">
         <v>88</v>
       </c>
-      <c r="N70" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" ht="24.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C71" t="s">
         <v>23</v>
@@ -4258,16 +4189,16 @@
         <v>16</v>
       </c>
       <c r="E71" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F71">
         <v>5</v>
       </c>
       <c r="G71" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H71" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I71">
         <v>4</v>
@@ -4276,15 +4207,15 @@
         <v>1</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="L71" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C72" t="s">
         <v>23</v>
@@ -4299,7 +4230,7 @@
         <v>3</v>
       </c>
       <c r="G72" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H72" t="s">
         <v>74</v>
@@ -4311,15 +4242,15 @@
         <v>0</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="L72" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>253</v>
+    <row r="73" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="A73" s="6" t="s">
+        <v>250</v>
       </c>
       <c r="C73" t="s">
         <v>80</v>
@@ -4328,16 +4259,16 @@
         <v>24</v>
       </c>
       <c r="E73" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F73">
         <v>8</v>
       </c>
       <c r="G73" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H73" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="I73">
         <v>6</v>
@@ -4346,10 +4277,13 @@
         <v>11</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="L73" t="s">
         <v>84</v>
+      </c>
+      <c r="M73" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -4372,7 +4306,7 @@
     <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="36.42578125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="46.85546875" style="6" customWidth="1"/>
+    <col min="15" max="15" width="46.85546875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="24" x14ac:dyDescent="0.4">
@@ -4419,12 +4353,12 @@
         <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C2" t="s">
         <v>23</v>
@@ -4433,13 +4367,13 @@
         <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F2">
         <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H2" t="s">
         <v>27</v>
@@ -4451,12 +4385,12 @@
         <v>3</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
@@ -4468,7 +4402,7 @@
         <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F3">
         <v>6</v>
@@ -4477,7 +4411,7 @@
         <v>38</v>
       </c>
       <c r="H3" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="I3">
         <v>8</v>
@@ -4486,12 +4420,12 @@
         <v>5</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
@@ -4521,12 +4455,12 @@
         <v>1</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -4538,18 +4472,18 @@
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H5" t="s">
         <v>18</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C6" t="s">
         <v>31</v>
@@ -4564,18 +4498,18 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J6">
         <v>5</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
@@ -4602,12 +4536,12 @@
         <v>4</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
@@ -4634,12 +4568,12 @@
         <v>3</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
@@ -4651,7 +4585,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F9">
         <v>10</v>
@@ -4660,7 +4594,7 @@
         <v>26</v>
       </c>
       <c r="H9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I9">
         <v>9</v>
@@ -4669,12 +4603,12 @@
         <v>2</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B10" t="s">
         <v>22</v>
@@ -4695,7 +4629,7 @@
         <v>26</v>
       </c>
       <c r="H10" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -4704,12 +4638,12 @@
         <v>1</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C11" t="s">
         <v>23</v>
@@ -4718,16 +4652,16 @@
         <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F11">
         <v>5</v>
       </c>
       <c r="G11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H11" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="I11">
         <v>4</v>
@@ -4736,12 +4670,12 @@
         <v>6</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
@@ -4750,7 +4684,7 @@
         <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F12">
         <v>10</v>
@@ -4759,12 +4693,12 @@
         <v>0</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
@@ -4773,7 +4707,7 @@
         <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F13">
         <v>6</v>
@@ -4785,12 +4719,12 @@
         <v>0</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
@@ -4799,13 +4733,13 @@
         <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F14">
         <v>4</v>
       </c>
       <c r="G14" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H14" t="s">
         <v>27</v>
@@ -4817,12 +4751,12 @@
         <v>4</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
@@ -4831,7 +4765,7 @@
         <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -4840,12 +4774,12 @@
         <v>1</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C16" t="s">
         <v>80</v>
@@ -4854,16 +4788,16 @@
         <v>24</v>
       </c>
       <c r="E16" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F16">
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H16" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="I16">
         <v>10</v>
@@ -4872,12 +4806,12 @@
         <v>6</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
@@ -4886,13 +4820,13 @@
         <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F17">
         <v>3</v>
       </c>
       <c r="G17" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H17" t="s">
         <v>74</v>
@@ -4904,12 +4838,12 @@
         <v>4</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
@@ -4924,7 +4858,7 @@
         <v>2</v>
       </c>
       <c r="G18" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H18" t="s">
         <v>69</v>
@@ -4936,12 +4870,12 @@
         <v>0</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B19" t="s">
         <v>62</v>
@@ -4959,10 +4893,10 @@
         <v>6</v>
       </c>
       <c r="G19" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H19" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I19">
         <v>5</v>
@@ -4971,12 +4905,12 @@
         <v>5</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C20" t="s">
         <v>23</v>
@@ -4985,13 +4919,13 @@
         <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F20">
         <v>3</v>
       </c>
       <c r="G20" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H20" t="s">
         <v>27</v>
@@ -5003,12 +4937,12 @@
         <v>0</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C21" t="s">
         <v>56</v>
@@ -5023,12 +4957,12 @@
         <v>0</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>312</v>
+        <v>429</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C22" t="s">
         <v>80</v>
@@ -5037,16 +4971,16 @@
         <v>24</v>
       </c>
       <c r="E22" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F22">
         <v>5</v>
       </c>
       <c r="G22" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H22" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="I22">
         <v>2</v>
@@ -5055,12 +4989,12 @@
         <v>4</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C23" t="s">
         <v>23</v>
@@ -5069,12 +5003,12 @@
         <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C24" t="s">
         <v>23</v>
@@ -5083,16 +5017,16 @@
         <v>24</v>
       </c>
       <c r="E24" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F24">
         <v>5</v>
       </c>
       <c r="G24" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H24" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I24">
         <v>4</v>
@@ -5101,12 +5035,12 @@
         <v>4</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C25" t="s">
         <v>23</v>
@@ -5121,7 +5055,7 @@
         <v>7</v>
       </c>
       <c r="G25" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H25" t="s">
         <v>27</v>
@@ -5135,7 +5069,7 @@
     </row>
     <row r="26" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C26" t="s">
         <v>31</v>
@@ -5144,7 +5078,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F26">
         <v>6</v>
@@ -5153,12 +5087,12 @@
         <v>0</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -5167,16 +5101,16 @@
         <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F27">
         <v>3</v>
       </c>
       <c r="G27" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="H27" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I27">
         <v>1</v>
@@ -5185,12 +5119,12 @@
         <v>0</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
@@ -5199,7 +5133,7 @@
         <v>24</v>
       </c>
       <c r="E28" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F28">
         <v>3</v>
@@ -5217,12 +5151,12 @@
         <v>2</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C29" t="s">
         <v>15</v>
@@ -5231,12 +5165,12 @@
         <v>46</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C30" t="s">
         <v>15</v>
@@ -5245,12 +5179,12 @@
         <v>46</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C31" t="s">
         <v>23</v>
@@ -5259,7 +5193,7 @@
         <v>24</v>
       </c>
       <c r="E31" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="F31">
         <v>10</v>
@@ -5274,12 +5208,12 @@
         <v>2</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C32" t="s">
         <v>23</v>
@@ -5302,7 +5236,7 @@
     </row>
     <row r="33" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C33" t="s">
         <v>31</v>
@@ -5311,24 +5245,24 @@
         <v>24</v>
       </c>
       <c r="E33" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B34" t="s">
         <v>22</v>
@@ -5340,7 +5274,7 @@
         <v>24</v>
       </c>
       <c r="E34" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F34">
         <v>10</v>
@@ -5349,7 +5283,7 @@
         <v>26</v>
       </c>
       <c r="H34" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="I34">
         <v>2</v>
@@ -5358,12 +5292,12 @@
         <v>2</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C35" t="s">
         <v>31</v>
@@ -5372,24 +5306,24 @@
         <v>24</v>
       </c>
       <c r="E35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F35">
         <v>3</v>
       </c>
       <c r="G35" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="J35">
         <v>0</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C36" t="s">
         <v>15</v>
@@ -5398,18 +5332,18 @@
         <v>16</v>
       </c>
       <c r="E36" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="H36" t="s">
         <v>18</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C37" t="s">
         <v>23</v>
@@ -5418,7 +5352,7 @@
         <v>24</v>
       </c>
       <c r="E37" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="F37">
         <v>5</v>
@@ -5436,12 +5370,12 @@
         <v>0</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C38" t="s">
         <v>15</v>
@@ -5456,12 +5390,12 @@
         <v>18</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B39" t="s">
         <v>58</v>
@@ -5473,13 +5407,13 @@
         <v>24</v>
       </c>
       <c r="E39" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="F39">
         <v>4</v>
       </c>
       <c r="G39" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H39" t="s">
         <v>69</v>
@@ -5491,12 +5425,12 @@
         <v>4</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C40" t="s">
         <v>31</v>
@@ -5505,7 +5439,7 @@
         <v>24</v>
       </c>
       <c r="E40" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F40">
         <v>3</v>
@@ -5517,15 +5451,15 @@
         <v>0</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B41" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C41" t="s">
         <v>23</v>
@@ -5534,16 +5468,16 @@
         <v>16</v>
       </c>
       <c r="E41" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="F41">
         <v>5</v>
       </c>
       <c r="G41" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H41" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="I41">
         <v>8</v>
@@ -5552,15 +5486,15 @@
         <v>3</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B42" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C42" t="s">
         <v>56</v>
@@ -5575,12 +5509,12 @@
         <v>1</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B43" t="s">
         <v>58</v>
@@ -5592,7 +5526,7 @@
         <v>24</v>
       </c>
       <c r="E43" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="F43">
         <v>5</v>
@@ -5601,7 +5535,7 @@
         <v>38</v>
       </c>
       <c r="H43" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="I43">
         <v>4</v>
@@ -5610,12 +5544,12 @@
         <v>5</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B44" t="s">
         <v>58</v>
@@ -5645,12 +5579,12 @@
         <v>4</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B45" t="s">
         <v>22</v>
@@ -5662,16 +5596,16 @@
         <v>24</v>
       </c>
       <c r="E45" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="F45">
         <v>4</v>
       </c>
       <c r="G45" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H45" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="I45">
         <v>14</v>
@@ -5682,7 +5616,7 @@
     </row>
     <row r="46" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C46" t="s">
         <v>15</v>
@@ -5691,15 +5625,15 @@
         <v>24</v>
       </c>
       <c r="E46" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C47" t="s">
         <v>15</v>
@@ -5708,15 +5642,15 @@
         <v>46</v>
       </c>
       <c r="E47" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C48" t="s">
         <v>31</v>
@@ -5725,7 +5659,7 @@
         <v>24</v>
       </c>
       <c r="E48" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F48">
         <v>5</v>
@@ -5737,12 +5671,12 @@
         <v>3</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C49" t="s">
         <v>80</v>
@@ -5751,16 +5685,16 @@
         <v>24</v>
       </c>
       <c r="E49" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="F49">
         <v>40</v>
       </c>
       <c r="G49" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="H49" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I49">
         <v>5</v>
@@ -5769,12 +5703,12 @@
         <v>0</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="50" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C50" t="s">
         <v>15</v>
@@ -5783,18 +5717,18 @@
         <v>24</v>
       </c>
       <c r="E50" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="H50" t="s">
         <v>18</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="51" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C51" t="s">
         <v>15</v>
@@ -5803,15 +5737,15 @@
         <v>24</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B52" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C52" t="s">
         <v>23</v>
@@ -5820,13 +5754,13 @@
         <v>24</v>
       </c>
       <c r="E52" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F52">
         <v>6</v>
       </c>
       <c r="G52" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H52" t="s">
         <v>27</v>
@@ -5838,12 +5772,12 @@
         <v>2</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C53" t="s">
         <v>15</v>
@@ -5852,15 +5786,15 @@
         <v>24</v>
       </c>
       <c r="E53" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B54" t="s">
         <v>58</v>
@@ -5872,18 +5806,18 @@
         <v>46</v>
       </c>
       <c r="E54" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>390</v>
+        <v>430</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B55" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C55" t="s">
         <v>15</v>
@@ -5892,15 +5826,15 @@
         <v>46</v>
       </c>
       <c r="E55" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B56" t="s">
         <v>22</v>
@@ -5912,18 +5846,18 @@
         <v>16</v>
       </c>
       <c r="E56" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B57" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C57" t="s">
         <v>15</v>
@@ -5932,18 +5866,18 @@
         <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H57" t="s">
         <v>18</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C58" t="s">
         <v>23</v>
@@ -5952,13 +5886,13 @@
         <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="F58">
         <v>7</v>
       </c>
       <c r="G58" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H58" t="s">
         <v>27</v>
@@ -5970,12 +5904,12 @@
         <v>4</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B59" t="s">
         <v>58</v>
@@ -5987,7 +5921,7 @@
         <v>24</v>
       </c>
       <c r="E59" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="F59">
         <v>7</v>
@@ -5996,7 +5930,7 @@
         <v>53</v>
       </c>
       <c r="H59" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I59">
         <v>5</v>
@@ -6005,12 +5939,12 @@
         <v>5</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B60" t="s">
         <v>62</v>
@@ -6022,7 +5956,7 @@
         <v>24</v>
       </c>
       <c r="E60" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="F60">
         <v>3</v>
@@ -6040,12 +5974,12 @@
         <v>0</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="B61" t="s">
         <v>58</v>
@@ -6057,7 +5991,7 @@
         <v>24</v>
       </c>
       <c r="E61" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F61">
         <v>4</v>
@@ -6066,7 +6000,7 @@
         <v>38</v>
       </c>
       <c r="H61" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I61">
         <v>12</v>
@@ -6075,15 +6009,15 @@
         <v>7</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="O61" s="6" t="s">
-        <v>409</v>
+        <v>403</v>
+      </c>
+      <c r="O61" s="5" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="B62" t="s">
         <v>58</v>
@@ -6095,15 +6029,15 @@
         <v>24</v>
       </c>
       <c r="E62" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C63" t="s">
         <v>15</v>
@@ -6112,12 +6046,12 @@
         <v>16</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C64" t="s">
         <v>80</v>
@@ -6126,7 +6060,7 @@
         <v>24</v>
       </c>
       <c r="E64" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="F64">
         <v>15</v>
@@ -6135,7 +6069,7 @@
         <v>26</v>
       </c>
       <c r="H64" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I64">
         <v>10</v>
@@ -6144,15 +6078,15 @@
         <v>4</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="O64" s="6" t="s">
-        <v>417</v>
+        <v>411</v>
+      </c>
+      <c r="O64" s="5" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C65" t="s">
         <v>31</v>
@@ -6161,7 +6095,7 @@
         <v>24</v>
       </c>
       <c r="E65" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="F65">
         <v>12</v>
@@ -6177,8 +6111,8 @@
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="7" t="s">
-        <v>420</v>
+      <c r="A66" s="6" t="s">
+        <v>415</v>
       </c>
       <c r="C66" t="s">
         <v>23</v>
@@ -6187,18 +6121,18 @@
         <v>24</v>
       </c>
       <c r="E66" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G66" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H66" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" s="7" t="s">
-        <v>421</v>
+      <c r="A67" s="6" t="s">
+        <v>416</v>
       </c>
       <c r="C67" t="s">
         <v>80</v>
@@ -6207,10 +6141,10 @@
         <v>24</v>
       </c>
       <c r="G67" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H67" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -6249,13 +6183,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D2" t="s">
         <v>23</v>
@@ -6277,13 +6211,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D4" t="s">
         <v>23</v>
@@ -6291,13 +6225,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D5" t="s">
         <v>23</v>
@@ -6305,7 +6239,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
@@ -6319,7 +6253,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B7" t="s">
         <v>64</v>
@@ -6333,7 +6267,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B8" t="s">
         <v>64</v>
@@ -6361,7 +6295,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B10" t="s">
         <v>87</v>
@@ -6403,7 +6337,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s">
         <v>38</v>
@@ -6417,7 +6351,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B14" t="s">
         <v>38</v>
@@ -6431,7 +6365,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B15" t="s">
         <v>38</v>
@@ -6445,7 +6379,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B16" t="s">
         <v>38</v>
@@ -6459,7 +6393,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B17" t="s">
         <v>38</v>
@@ -6473,7 +6407,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
@@ -6487,7 +6421,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B19" t="s">
         <v>38</v>
@@ -6501,13 +6435,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B20" t="s">
         <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D20" t="s">
         <v>23</v>
@@ -6557,7 +6491,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B24" t="s">
         <v>26</v>
@@ -6571,7 +6505,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B25" t="s">
         <v>53</v>
@@ -6585,7 +6519,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B26" t="s">
         <v>53</v>
@@ -6599,13 +6533,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B27" t="s">
         <v>53</v>
       </c>
       <c r="C27" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D27" t="s">
         <v>23</v>
@@ -6649,13 +6583,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>145</v>
+      </c>
+      <c r="B31" t="s">
+        <v>140</v>
+      </c>
+      <c r="C31" t="s">
         <v>147</v>
-      </c>
-      <c r="B31" t="s">
-        <v>142</v>
-      </c>
-      <c r="C31" t="s">
-        <v>149</v>
       </c>
       <c r="D31" t="s">
         <v>80</v>
@@ -6663,13 +6597,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B32" t="s">
         <v>64</v>
       </c>
       <c r="C32" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D32" t="s">
         <v>80</v>
@@ -6677,13 +6611,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" t="s">
         <v>127</v>
       </c>
-      <c r="B33" t="s">
-        <v>129</v>
-      </c>
       <c r="C33" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D33" t="s">
         <v>80</v>
@@ -6691,13 +6625,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B34" t="s">
         <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D34" t="s">
         <v>80</v>
@@ -6719,13 +6653,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B36" t="s">
         <v>38</v>
       </c>
       <c r="C36" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D36" t="s">
         <v>80</v>
@@ -6733,13 +6667,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B37" t="s">
         <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D37" t="s">
         <v>80</v>
@@ -6747,13 +6681,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B38" t="s">
         <v>38</v>
       </c>
       <c r="C38" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D38" t="s">
         <v>80</v>
@@ -6761,13 +6695,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B39" t="s">
         <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D39" t="s">
         <v>80</v>
@@ -6808,7 +6742,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="C43" t="s">
         <v>18</v>
@@ -6819,7 +6753,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C44" t="s">
         <v>18</v>
@@ -6830,7 +6764,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D45" t="s">
         <v>15</v>
@@ -6838,7 +6772,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D46" t="s">
         <v>15</v>
@@ -6846,7 +6780,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D47" t="s">
         <v>15</v>
@@ -6854,7 +6788,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D48" t="s">
         <v>15</v>
@@ -6862,7 +6796,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D49" t="s">
         <v>15</v>
@@ -6881,7 +6815,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C51" t="s">
         <v>33</v>
@@ -6892,7 +6826,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C52" t="s">
         <v>33</v>
@@ -6903,7 +6837,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C53" t="s">
         <v>33</v>
@@ -6914,7 +6848,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C54" t="s">
         <v>33</v>
@@ -6925,7 +6859,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C55" t="s">
         <v>33</v>
@@ -6936,10 +6870,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C56" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D56" t="s">
         <v>31</v>
@@ -6947,10 +6881,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C57" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D57" t="s">
         <v>31</v>
@@ -6958,10 +6892,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C58" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D58" t="s">
         <v>31</v>
@@ -6969,10 +6903,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C59" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D59" t="s">
         <v>31</v>
@@ -6980,7 +6914,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D60" t="s">
         <v>31</v>
@@ -6988,13 +6922,13 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B61" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C61" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="D61" t="s">
         <v>80</v>
@@ -7010,13 +6944,13 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>103</v>
+      </c>
+      <c r="B63" t="s">
         <v>105</v>
       </c>
-      <c r="B63" t="s">
-        <v>107</v>
-      </c>
       <c r="C63" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D63" t="s">
         <v>23</v>
@@ -7024,10 +6958,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B64" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C64" t="s">
         <v>27</v>
@@ -7038,10 +6972,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B65" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C65" t="s">
         <v>27</v>
@@ -7052,13 +6986,13 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>138</v>
+      </c>
+      <c r="B66" t="s">
         <v>140</v>
       </c>
-      <c r="B66" t="s">
-        <v>142</v>
-      </c>
       <c r="C66" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D66" t="s">
         <v>80</v>
@@ -7066,10 +7000,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B67" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C67" t="s">
         <v>74</v>
@@ -7080,13 +7014,13 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B68" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C68" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D68" t="s">
         <v>23</v>
@@ -7094,10 +7028,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B69" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C69" t="s">
         <v>27</v>
@@ -7122,10 +7056,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C71" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D71" t="s">
         <v>31</v>
@@ -7133,7 +7067,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D72" t="s">
         <v>15</v>
@@ -7203,7 +7137,7 @@
     </row>
     <row r="2" spans="1:12" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C2" t="s">
         <v>23</v>
@@ -7212,16 +7146,16 @@
         <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="I2">
         <v>6</v>
@@ -7230,7 +7164,7 @@
         <v>10</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="L2" t="s">
         <v>35</v>
@@ -7257,38 +7191,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="D1" s="10"/>
+      <c r="A1" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="D1" s="9"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -7303,13 +7237,13 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -7324,13 +7258,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -7341,53 +7275,53 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="D7">
         <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B8">
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -7398,47 +7332,47 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
       <c r="H9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B10">
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="H10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B11">
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D11">
         <v>3</v>
       </c>
       <c r="H11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -7455,12 +7389,12 @@
         <v>3</v>
       </c>
       <c r="H12" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -7472,58 +7406,58 @@
         <v>3</v>
       </c>
       <c r="H13" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B14">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
       <c r="H14" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B15">
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D15">
         <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D16">
         <v>3</v>
       </c>
       <c r="H16" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -7534,13 +7468,13 @@
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D17">
         <v>3</v>
       </c>
       <c r="H17" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -7751,9 +7685,15 @@
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2853C30-6322-4EA0-9233-C02855FA666C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="f5235b4c-d799-48fb-911b-9341dfbcb198"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Alpha Set List.xlsx
+++ b/Alpha Set List.xlsx
@@ -8,19 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\apoke\Desktop\Advance!Tactics\Advance-Tactics-Tcgarena\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{35E12D45-7F10-4534-95A3-22A49A69B2B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{974815FC-44CA-4ADC-8474-C8F377A76CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{CA094A51-376D-41C2-95CA-6278B694BA34}"/>
   </bookViews>
   <sheets>
     <sheet name="Set1 - Alpha" sheetId="1" r:id="rId1"/>
     <sheet name="Set 2" sheetId="5" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
-    <sheet name="Extended Set List" sheetId="2" r:id="rId4"/>
-    <sheet name="PreconLists" sheetId="3" r:id="rId5"/>
+    <sheet name="Set 3" sheetId="7" r:id="rId3"/>
+    <sheet name="Possible Gods" sheetId="8" r:id="rId4"/>
+    <sheet name="Extended Set List" sheetId="2" r:id="rId5"/>
+    <sheet name="PreconLists" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Extended Set List'!$A$69:$K$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Extended Set List'!$A$69:$K$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Set 3'!$A$69:$K$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Set1 - Alpha'!$A$69:$K$69</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1365" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="450">
   <si>
     <t>Card Name</t>
   </si>
@@ -1148,9 +1150,6 @@
   </si>
   <si>
     <t>Palace of Nyalia</t>
-  </si>
-  <si>
-    <t>Static: The first time a Feline advances, it advances twice.</t>
   </si>
   <si>
     <t>Archmage of Denial</t>
@@ -1283,16 +1282,6 @@
     <t>Activate: A chosen structure on the occupied tile gains 2 Fortitude.</t>
   </si>
   <si>
-    <t>Errica, Coven Conscript</t>
-  </si>
-  <si>
-    <t>WIFA</t>
-  </si>
-  <si>
-    <t>Static: Whenever you play a spell card, produce one Mana.
-Activate(AAAAAA): You win the game.</t>
-  </si>
-  <si>
     <t>Errica used a crown to communicate with cultists to increase her power and influence. Baoust learned of her collusion and turned her into a human as punishment for turning against her race.</t>
   </si>
   <si>
@@ -1333,15 +1322,6 @@
   </si>
   <si>
     <t>Sam</t>
-  </si>
-  <si>
-    <t>Pillar of Flame</t>
-  </si>
-  <si>
-    <t>Zh'Aedin, in Billowing Smog</t>
-  </si>
-  <si>
-    <t>Zh'Aedin</t>
   </si>
   <si>
     <t>Factory Defense Sentries</t>
@@ -1373,6 +1353,84 @@
   </si>
   <si>
     <t>Put a chosen planned card into it's owners discard pile.</t>
+  </si>
+  <si>
+    <t>Pre-Combat: Roll a d6. This units gets +X power until end of turn, where X is the result.</t>
+  </si>
+  <si>
+    <t>Produce: Roll a d4. X-1 mana, where X is the result.</t>
+  </si>
+  <si>
+    <t>Nomadic Drakes</t>
+  </si>
+  <si>
+    <t>Whenever you pay one or more Food, you may discard a card. If you do, draw a card.</t>
+  </si>
+  <si>
+    <t>Kathryn Flesher</t>
+  </si>
+  <si>
+    <t>Static: The first time a Feline would advance, it advances twice.</t>
+  </si>
+  <si>
+    <t>Striped Stalwarts</t>
+  </si>
+  <si>
+    <t>FM</t>
+  </si>
+  <si>
+    <t>Ball of Yarn</t>
+  </si>
+  <si>
+    <t>A chosen enemy combatant moves one tile horizontally.</t>
+  </si>
+  <si>
+    <t>Purrformance Enhancers</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Affinities</t>
+  </si>
+  <si>
+    <t>Antipathy</t>
+  </si>
+  <si>
+    <t>Smite</t>
+  </si>
+  <si>
+    <t>Bane</t>
+  </si>
+  <si>
+    <t>Boon</t>
+  </si>
+  <si>
+    <t>Blessing</t>
+  </si>
+  <si>
+    <t>Xanu</t>
+  </si>
+  <si>
+    <t>Life, Prosperity</t>
+  </si>
+  <si>
+    <t>Death</t>
+  </si>
+  <si>
+    <t>Units have +2 Base Numbers/Fortitude</t>
+  </si>
+  <si>
+    <t>For each devoted player, put X +1 Numbers counters on each of that player's armies, Where X is their castle's Fortitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each </t>
+  </si>
+  <si>
+    <t>Geoff Flesher</t>
+  </si>
+  <si>
+    <t>James Patterson, Chuck Carr</t>
   </si>
 </sst>
 </file>
@@ -1409,7 +1467,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1434,6 +1492,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1447,7 +1511,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1463,6 +1527,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1865,7 +1933,7 @@
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
@@ -1885,6 +1953,9 @@
       </c>
       <c r="L2" t="s">
         <v>20</v>
+      </c>
+      <c r="M2" t="s">
+        <v>448</v>
       </c>
       <c r="P2">
         <f>COUNTIF(L:L, "Common")</f>
@@ -2044,7 +2115,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="8" t="s">
         <v>45</v>
       </c>
       <c r="C7" t="s">
@@ -2064,6 +2135,9 @@
       </c>
       <c r="L7" t="s">
         <v>35</v>
+      </c>
+      <c r="M7" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="24.75" x14ac:dyDescent="0.25">
@@ -2143,7 +2217,7 @@
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="6" t="s">
         <v>55</v>
       </c>
       <c r="C10" t="s">
@@ -2160,6 +2234,9 @@
       </c>
       <c r="L10" t="s">
         <v>35</v>
+      </c>
+      <c r="M10" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="24.75" x14ac:dyDescent="0.25">
@@ -2297,7 +2374,7 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="8" t="s">
         <v>73</v>
       </c>
       <c r="C15" t="s">
@@ -2646,7 +2723,7 @@
       </c>
     </row>
     <row r="26" spans="1:13" ht="60.75" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="A26" s="8" t="s">
         <v>114</v>
       </c>
       <c r="B26" t="s">
@@ -2871,7 +2948,7 @@
       </c>
     </row>
     <row r="32" spans="1:13" ht="72.75" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="A32" s="8" t="s">
         <v>134</v>
       </c>
       <c r="B32" t="s">
@@ -3119,7 +3196,7 @@
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="7" t="s">
         <v>157</v>
       </c>
       <c r="C39" t="s">
@@ -3157,7 +3234,7 @@
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="A40" s="8" t="s">
         <v>162</v>
       </c>
       <c r="C40" t="s">
@@ -3174,6 +3251,9 @@
       </c>
       <c r="L40" t="s">
         <v>35</v>
+      </c>
+      <c r="M40" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
@@ -3538,7 +3618,7 @@
       </c>
     </row>
     <row r="52" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="A52" s="7" t="s">
         <v>192</v>
       </c>
       <c r="B52" t="s">
@@ -3573,6 +3653,9 @@
       </c>
       <c r="L52" t="s">
         <v>84</v>
+      </c>
+      <c r="M52" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
@@ -3687,7 +3770,7 @@
       </c>
     </row>
     <row r="56" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="A56" s="8" t="s">
         <v>204</v>
       </c>
       <c r="C56" t="s">
@@ -3713,6 +3796,9 @@
       </c>
       <c r="L56" t="s">
         <v>35</v>
+      </c>
+      <c r="M56" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
@@ -3865,7 +3951,7 @@
       </c>
     </row>
     <row r="61" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="A61" s="8" t="s">
         <v>220</v>
       </c>
       <c r="C61" t="s">
@@ -3900,7 +3986,7 @@
       </c>
     </row>
     <row r="62" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="A62" s="8" t="s">
         <v>225</v>
       </c>
       <c r="C62" t="s">
@@ -3923,6 +4009,9 @@
       </c>
       <c r="L62" t="s">
         <v>29</v>
+      </c>
+      <c r="M62" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
@@ -3954,9 +4043,9 @@
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>230</v>
+    <row r="64" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="A64" s="8" t="s">
+        <v>426</v>
       </c>
       <c r="C64" t="s">
         <v>23</v>
@@ -3965,25 +4054,31 @@
         <v>24</v>
       </c>
       <c r="E64" t="s">
-        <v>228</v>
+        <v>101</v>
       </c>
       <c r="F64">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G64" t="s">
-        <v>87</v>
+        <v>295</v>
       </c>
       <c r="H64" t="s">
-        <v>27</v>
+        <v>121</v>
       </c>
       <c r="I64">
+        <v>1</v>
+      </c>
+      <c r="J64">
         <v>4</v>
       </c>
-      <c r="J64">
-        <v>9</v>
+      <c r="K64" s="1" t="s">
+        <v>427</v>
       </c>
       <c r="L64" t="s">
         <v>35</v>
+      </c>
+      <c r="M64" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
@@ -4100,7 +4195,7 @@
       </c>
     </row>
     <row r="69" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="7" t="s">
         <v>239</v>
       </c>
       <c r="C69" t="s">
@@ -4249,7 +4344,7 @@
       </c>
     </row>
     <row r="73" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="6" t="s">
+      <c r="A73" s="8" t="s">
         <v>250</v>
       </c>
       <c r="C73" t="s">
@@ -4298,10 +4393,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D09819-88AD-4922-89C4-E36F98EAC984}">
-  <dimension ref="A1:O67"/>
+  <dimension ref="A1:O70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
@@ -4957,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
@@ -5509,12 +5604,12 @@
         <v>1</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>358</v>
+        <v>429</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B43" t="s">
         <v>58</v>
@@ -5526,7 +5621,7 @@
         <v>24</v>
       </c>
       <c r="E43" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F43">
         <v>5</v>
@@ -5535,7 +5630,7 @@
         <v>38</v>
       </c>
       <c r="H43" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I43">
         <v>4</v>
@@ -5544,12 +5639,12 @@
         <v>5</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B44" t="s">
         <v>58</v>
@@ -5579,12 +5674,12 @@
         <v>4</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B45" t="s">
         <v>22</v>
@@ -5596,7 +5691,7 @@
         <v>24</v>
       </c>
       <c r="E45" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F45">
         <v>4</v>
@@ -5605,7 +5700,7 @@
         <v>105</v>
       </c>
       <c r="H45" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I45">
         <v>14</v>
@@ -5616,7 +5711,7 @@
     </row>
     <row r="46" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C46" t="s">
         <v>15</v>
@@ -5628,12 +5723,12 @@
         <v>109</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C47" t="s">
         <v>15</v>
@@ -5645,12 +5740,12 @@
         <v>322</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C48" t="s">
         <v>31</v>
@@ -5676,7 +5771,7 @@
     </row>
     <row r="49" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C49" t="s">
         <v>80</v>
@@ -5685,13 +5780,13 @@
         <v>24</v>
       </c>
       <c r="E49" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F49">
         <v>40</v>
       </c>
       <c r="G49" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H49" t="s">
         <v>128</v>
@@ -5703,12 +5798,12 @@
         <v>0</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="50" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C50" t="s">
         <v>15</v>
@@ -5723,12 +5818,12 @@
         <v>18</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="51" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C51" t="s">
         <v>15</v>
@@ -5737,12 +5832,12 @@
         <v>24</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B52" t="s">
         <v>131</v>
@@ -5772,12 +5867,12 @@
         <v>2</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C53" t="s">
         <v>15</v>
@@ -5789,12 +5884,12 @@
         <v>109</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B54" t="s">
         <v>58</v>
@@ -5809,12 +5904,12 @@
         <v>101</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B55" t="s">
         <v>131</v>
@@ -5829,12 +5924,12 @@
         <v>215</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B56" t="s">
         <v>22</v>
@@ -5846,15 +5941,15 @@
         <v>16</v>
       </c>
       <c r="E56" t="s">
+        <v>388</v>
+      </c>
+      <c r="K56" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B57" t="s">
         <v>131</v>
@@ -5872,12 +5967,12 @@
         <v>18</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C58" t="s">
         <v>23</v>
@@ -5886,7 +5981,7 @@
         <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F58">
         <v>7</v>
@@ -5904,12 +5999,12 @@
         <v>4</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B59" t="s">
         <v>58</v>
@@ -5921,7 +6016,7 @@
         <v>24</v>
       </c>
       <c r="E59" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F59">
         <v>7</v>
@@ -5939,12 +6034,12 @@
         <v>5</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B60" t="s">
         <v>62</v>
@@ -5956,7 +6051,7 @@
         <v>24</v>
       </c>
       <c r="E60" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F60">
         <v>3</v>
@@ -5974,7 +6069,7 @@
         <v>0</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="60" x14ac:dyDescent="0.25">
@@ -5985,68 +6080,65 @@
         <v>58</v>
       </c>
       <c r="C61" t="s">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="D61" t="s">
         <v>24</v>
       </c>
       <c r="E61" t="s">
+        <v>112</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="F61">
-        <v>4</v>
-      </c>
-      <c r="G61" t="s">
-        <v>38</v>
-      </c>
-      <c r="H61" t="s">
-        <v>147</v>
-      </c>
-      <c r="I61">
-        <v>12</v>
-      </c>
-      <c r="J61">
-        <v>7</v>
-      </c>
-      <c r="K61" s="1" t="s">
+      <c r="O61" s="5" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>403</v>
-      </c>
-      <c r="O61" s="5" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>405</v>
-      </c>
-      <c r="B62" t="s">
-        <v>58</v>
       </c>
       <c r="C62" t="s">
         <v>15</v>
       </c>
       <c r="D62" t="s">
-        <v>24</v>
-      </c>
-      <c r="E62" t="s">
-        <v>112</v>
+        <v>16</v>
       </c>
       <c r="K62" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>405</v>
+      </c>
+      <c r="C63" t="s">
+        <v>80</v>
+      </c>
+      <c r="D63" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="63" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="F63">
+        <v>15</v>
+      </c>
+      <c r="G63" t="s">
+        <v>26</v>
+      </c>
+      <c r="H63" t="s">
+        <v>194</v>
+      </c>
+      <c r="I63">
+        <v>10</v>
+      </c>
+      <c r="J63">
+        <v>4</v>
+      </c>
+      <c r="K63" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="C63" t="s">
-        <v>15</v>
-      </c>
-      <c r="D63" t="s">
-        <v>16</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="60" x14ac:dyDescent="0.25">
@@ -6054,7 +6146,7 @@
         <v>409</v>
       </c>
       <c r="C64" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="D64" t="s">
         <v>24</v>
@@ -6063,89 +6155,181 @@
         <v>410</v>
       </c>
       <c r="F64">
-        <v>15</v>
-      </c>
-      <c r="G64" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="H64" t="s">
-        <v>194</v>
+        <v>33</v>
       </c>
       <c r="I64">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J64">
-        <v>4</v>
-      </c>
-      <c r="K64" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K64" s="10"/>
+      <c r="O64" s="5" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="A65" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="O64" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>413</v>
-      </c>
       <c r="C65" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D65" t="s">
         <v>24</v>
       </c>
       <c r="E65" t="s">
-        <v>414</v>
+        <v>112</v>
       </c>
       <c r="F65">
-        <v>12</v>
+        <v>8</v>
+      </c>
+      <c r="G65" t="s">
+        <v>216</v>
       </c>
       <c r="H65" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="I65">
         <v>0</v>
       </c>
       <c r="J65">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="6" t="s">
-        <v>415</v>
+        <v>2</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66" s="9" t="s">
+        <v>412</v>
       </c>
       <c r="C66" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="D66" t="s">
         <v>24</v>
       </c>
       <c r="E66" t="s">
-        <v>112</v>
+        <v>258</v>
+      </c>
+      <c r="F66">
+        <v>5</v>
       </c>
       <c r="G66" t="s">
         <v>216</v>
       </c>
       <c r="H66" t="s">
+        <v>413</v>
+      </c>
+      <c r="I66">
+        <v>1</v>
+      </c>
+      <c r="J66">
+        <v>4</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>230</v>
+      </c>
+      <c r="C67" t="s">
+        <v>23</v>
+      </c>
+      <c r="D67" t="s">
+        <v>24</v>
+      </c>
+      <c r="E67" t="s">
+        <v>228</v>
+      </c>
+      <c r="F67">
+        <v>7</v>
+      </c>
+      <c r="G67" t="s">
+        <v>87</v>
+      </c>
+      <c r="H67" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="C67" t="s">
-        <v>80</v>
-      </c>
-      <c r="D67" t="s">
-        <v>24</v>
-      </c>
-      <c r="G67" t="s">
-        <v>216</v>
-      </c>
-      <c r="H67" t="s">
-        <v>417</v>
-      </c>
+      <c r="I67">
+        <v>4</v>
+      </c>
+      <c r="J67">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>430</v>
+      </c>
+      <c r="B68" t="s">
+        <v>131</v>
+      </c>
+      <c r="C68" t="s">
+        <v>23</v>
+      </c>
+      <c r="D68" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68" t="s">
+        <v>431</v>
+      </c>
+      <c r="F68">
+        <v>8</v>
+      </c>
+      <c r="G68" t="s">
+        <v>140</v>
+      </c>
+      <c r="H68" t="s">
+        <v>27</v>
+      </c>
+      <c r="I68">
+        <v>8</v>
+      </c>
+      <c r="J68">
+        <v>6</v>
+      </c>
+      <c r="L68" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>432</v>
+      </c>
+      <c r="C69" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" t="s">
+        <v>24</v>
+      </c>
+      <c r="E69" t="s">
+        <v>344</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>434</v>
+      </c>
+      <c r="C70" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" t="s">
+        <v>24</v>
+      </c>
+      <c r="E70" t="s">
+        <v>354</v>
+      </c>
+      <c r="K70" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6153,924 +6337,350 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E8B7C54-2039-4F68-89DC-F983A17B7C9B}">
-  <dimension ref="A1:F72"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EB4CFA8-C1A3-4F71-BBBE-C310D4E06AAC}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="36.42578125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" ht="24" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K2"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K3"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K4"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K5"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K6"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K7"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K8"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K9"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K10"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K11"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K12"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K13"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K14"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K15"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K16"/>
+    </row>
+    <row r="17" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K17"/>
+    </row>
+    <row r="18" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K18"/>
+    </row>
+    <row r="19" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K19"/>
+    </row>
+    <row r="20" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K20"/>
+    </row>
+    <row r="21" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K21"/>
+    </row>
+    <row r="22" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K22"/>
+    </row>
+    <row r="23" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K23"/>
+    </row>
+    <row r="24" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K24"/>
+    </row>
+    <row r="25" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K25"/>
+    </row>
+    <row r="26" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K26"/>
+    </row>
+    <row r="27" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K27"/>
+    </row>
+    <row r="28" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K28"/>
+    </row>
+    <row r="29" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K29"/>
+    </row>
+    <row r="30" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K30"/>
+    </row>
+    <row r="31" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K31"/>
+    </row>
+    <row r="32" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K32"/>
+    </row>
+    <row r="33" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K33"/>
+    </row>
+    <row r="34" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K34"/>
+    </row>
+    <row r="35" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K35"/>
+    </row>
+    <row r="36" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K36"/>
+    </row>
+    <row r="37" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K37"/>
+    </row>
+    <row r="38" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K38"/>
+    </row>
+    <row r="39" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K39"/>
+    </row>
+    <row r="40" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K40"/>
+    </row>
+    <row r="41" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K41"/>
+    </row>
+    <row r="42" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K42"/>
+    </row>
+    <row r="43" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K43"/>
+    </row>
+    <row r="44" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K44"/>
+    </row>
+    <row r="45" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K45"/>
+    </row>
+    <row r="46" spans="11:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K46"/>
+    </row>
+    <row r="47" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K47"/>
+    </row>
+    <row r="48" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K48"/>
+    </row>
+    <row r="49" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K49"/>
+    </row>
+    <row r="50" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K50"/>
+    </row>
+    <row r="51" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K51"/>
+    </row>
+    <row r="52" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K52"/>
+    </row>
+    <row r="53" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K53"/>
+    </row>
+    <row r="54" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K54"/>
+    </row>
+    <row r="55" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K55"/>
+    </row>
+    <row r="56" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K56"/>
+    </row>
+    <row r="57" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K57"/>
+    </row>
+    <row r="58" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K58"/>
+    </row>
+    <row r="59" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K59"/>
+    </row>
+    <row r="60" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K60"/>
+    </row>
+    <row r="61" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K61"/>
+    </row>
+    <row r="62" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K62"/>
+    </row>
+    <row r="63" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K63"/>
+    </row>
+    <row r="64" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K64"/>
+    </row>
+    <row r="65" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K65"/>
+    </row>
+    <row r="66" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K66"/>
+    </row>
+    <row r="67" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K67"/>
+    </row>
+    <row r="68" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K68"/>
+    </row>
+    <row r="69" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K69"/>
+    </row>
+    <row r="70" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K70"/>
+    </row>
+    <row r="71" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K71"/>
+    </row>
+    <row r="72" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K72"/>
+    </row>
+    <row r="73" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K73"/>
+    </row>
+    <row r="74" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K74"/>
+    </row>
+    <row r="75" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K75"/>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D09EDB3E-A1B0-45D3-BBCE-F2774DC9A7E5}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" customWidth="1"/>
+    <col min="5" max="5" width="28.28515625" customWidth="1"/>
+    <col min="6" max="6" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C1" t="s">
+        <v>437</v>
+      </c>
+      <c r="D1" t="s">
+        <v>438</v>
+      </c>
+      <c r="E1" t="s">
+        <v>439</v>
+      </c>
+      <c r="F1" t="s">
+        <v>440</v>
+      </c>
+      <c r="G1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>242</v>
+        <v>442</v>
       </c>
       <c r="B2" t="s">
-        <v>222</v>
+        <v>443</v>
       </c>
       <c r="C2" t="s">
-        <v>244</v>
+        <v>444</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>200</v>
-      </c>
-      <c r="B5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" t="s">
-        <v>159</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>123</v>
-      </c>
-      <c r="B7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>181</v>
-      </c>
-      <c r="B8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>85</v>
-      </c>
-      <c r="B9" t="s">
-        <v>87</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>230</v>
-      </c>
-      <c r="B10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>67</v>
-      </c>
-      <c r="B12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>152</v>
-      </c>
-      <c r="B13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>185</v>
-      </c>
-      <c r="B14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>130</v>
-      </c>
-      <c r="B15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>165</v>
-      </c>
-      <c r="B16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>168</v>
-      </c>
-      <c r="B17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>170</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>183</v>
-      </c>
-      <c r="B19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>157</v>
-      </c>
-      <c r="B20" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" t="s">
-        <v>159</v>
-      </c>
-      <c r="D20" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" t="s">
-        <v>27</v>
-      </c>
-      <c r="D21" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>111</v>
-      </c>
-      <c r="B24" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" t="s">
-        <v>27</v>
-      </c>
-      <c r="D24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>142</v>
-      </c>
-      <c r="B25" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>206</v>
-      </c>
-      <c r="B26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>234</v>
-      </c>
-      <c r="B27" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" t="s">
-        <v>235</v>
-      </c>
-      <c r="D27" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" t="s">
-        <v>27</v>
-      </c>
-      <c r="D28" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>57</v>
-      </c>
-      <c r="B29" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" t="s">
-        <v>27</v>
-      </c>
-      <c r="D29" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>55</v>
-      </c>
-      <c r="D30" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>145</v>
-      </c>
-      <c r="B31" t="s">
-        <v>140</v>
-      </c>
-      <c r="C31" t="s">
-        <v>147</v>
-      </c>
-      <c r="D31" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>114</v>
-      </c>
-      <c r="B32" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" t="s">
-        <v>116</v>
-      </c>
-      <c r="D32" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>125</v>
-      </c>
-      <c r="B33" t="s">
-        <v>127</v>
-      </c>
-      <c r="C33" t="s">
-        <v>128</v>
-      </c>
-      <c r="D33" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>208</v>
-      </c>
-      <c r="B34" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" t="s">
-        <v>210</v>
-      </c>
-      <c r="D34" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>79</v>
-      </c>
-      <c r="B35" t="s">
-        <v>38</v>
-      </c>
-      <c r="C35" t="s">
-        <v>82</v>
-      </c>
-      <c r="D35" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>134</v>
-      </c>
-      <c r="B36" t="s">
-        <v>38</v>
-      </c>
-      <c r="C36" t="s">
-        <v>136</v>
-      </c>
-      <c r="D36" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>192</v>
-      </c>
-      <c r="B37" t="s">
-        <v>38</v>
-      </c>
-      <c r="C37" t="s">
-        <v>194</v>
-      </c>
-      <c r="D37" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>214</v>
-      </c>
-      <c r="B38" t="s">
-        <v>38</v>
-      </c>
-      <c r="C38" t="s">
-        <v>217</v>
-      </c>
-      <c r="D38" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>92</v>
-      </c>
-      <c r="B39" t="s">
-        <v>53</v>
-      </c>
-      <c r="C39" t="s">
-        <v>94</v>
-      </c>
-      <c r="D39" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>14</v>
-      </c>
-      <c r="C40" t="s">
-        <v>18</v>
-      </c>
-      <c r="D40" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>45</v>
-      </c>
-      <c r="C41" t="s">
-        <v>18</v>
-      </c>
-      <c r="D41" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>76</v>
-      </c>
-      <c r="C42" t="s">
-        <v>18</v>
-      </c>
-      <c r="D42" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>418</v>
-      </c>
-      <c r="C43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D43" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>237</v>
-      </c>
-      <c r="C44" t="s">
-        <v>18</v>
-      </c>
-      <c r="D44" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>89</v>
-      </c>
-      <c r="D45" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>100</v>
-      </c>
-      <c r="D46" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>150</v>
-      </c>
-      <c r="D47" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>190</v>
-      </c>
-      <c r="D48" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>232</v>
-      </c>
-      <c r="D49" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>30</v>
-      </c>
-      <c r="C50" t="s">
-        <v>33</v>
-      </c>
-      <c r="D50" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>108</v>
-      </c>
-      <c r="C51" t="s">
-        <v>33</v>
-      </c>
-      <c r="D51" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>154</v>
-      </c>
-      <c r="C52" t="s">
-        <v>33</v>
-      </c>
-      <c r="D52" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>172</v>
-      </c>
-      <c r="C53" t="s">
-        <v>33</v>
-      </c>
-      <c r="D53" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>175</v>
-      </c>
-      <c r="C54" t="s">
-        <v>33</v>
-      </c>
-      <c r="D54" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>204</v>
-      </c>
-      <c r="C55" t="s">
-        <v>33</v>
-      </c>
-      <c r="D55" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>96</v>
-      </c>
-      <c r="C56" t="s">
-        <v>98</v>
-      </c>
-      <c r="D56" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>227</v>
-      </c>
-      <c r="C57" t="s">
-        <v>98</v>
-      </c>
-      <c r="D57" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>196</v>
-      </c>
-      <c r="C58" t="s">
-        <v>198</v>
-      </c>
-      <c r="D58" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>212</v>
-      </c>
-      <c r="C59" t="s">
-        <v>188</v>
-      </c>
-      <c r="D59" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>225</v>
-      </c>
-      <c r="D60" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>419</v>
-      </c>
-      <c r="B61" t="s">
-        <v>105</v>
-      </c>
-      <c r="C61" t="s">
-        <v>420</v>
-      </c>
-      <c r="D61" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>71</v>
-      </c>
-      <c r="D62" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>103</v>
-      </c>
-      <c r="B63" t="s">
-        <v>105</v>
-      </c>
-      <c r="C63" t="s">
-        <v>106</v>
-      </c>
-      <c r="D63" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>202</v>
-      </c>
-      <c r="B64" t="s">
-        <v>140</v>
-      </c>
-      <c r="C64" t="s">
-        <v>27</v>
-      </c>
-      <c r="D64" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>239</v>
-      </c>
-      <c r="B65" t="s">
-        <v>105</v>
-      </c>
-      <c r="C65" t="s">
-        <v>27</v>
-      </c>
-      <c r="D65" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>138</v>
-      </c>
-      <c r="B66" t="s">
-        <v>140</v>
-      </c>
-      <c r="C66" t="s">
-        <v>138</v>
-      </c>
-      <c r="D66" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>248</v>
-      </c>
-      <c r="B67" t="s">
-        <v>140</v>
-      </c>
-      <c r="C67" t="s">
-        <v>74</v>
-      </c>
-      <c r="D67" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>246</v>
-      </c>
-      <c r="B68" t="s">
-        <v>140</v>
-      </c>
-      <c r="C68" t="s">
-        <v>235</v>
-      </c>
-      <c r="D68" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>231</v>
-      </c>
-      <c r="B69" t="s">
-        <v>105</v>
-      </c>
-      <c r="C69" t="s">
-        <v>27</v>
-      </c>
-      <c r="D69" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>73</v>
-      </c>
-      <c r="B70" t="s">
-        <v>26</v>
-      </c>
-      <c r="C70" t="s">
-        <v>74</v>
-      </c>
-      <c r="D70" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>187</v>
-      </c>
-      <c r="C71" t="s">
-        <v>188</v>
-      </c>
-      <c r="D71" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>162</v>
-      </c>
-      <c r="D72" t="s">
-        <v>15</v>
+        <v>447</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>446</v>
       </c>
     </row>
   </sheetData>
@@ -7078,7 +6688,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDA8A1B9-2DFE-4CB9-932B-BF4909105E3B}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -7137,7 +6747,7 @@
     </row>
     <row r="2" spans="1:12" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="C2" t="s">
         <v>23</v>
@@ -7164,7 +6774,7 @@
         <v>10</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="L2" t="s">
         <v>35</v>
@@ -7179,7 +6789,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCAEE421-A9EF-4A9D-9968-90AE67C938D6}">
   <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7191,27 +6801,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="D1" s="9"/>
+      <c r="A1" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="D1" s="11"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -7281,7 +6891,7 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -7298,13 +6908,13 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="D7">
         <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -7428,7 +7038,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -7445,7 +7055,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="B16">
         <v>3</v>
@@ -7490,6 +7100,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001E1F373BE6E33547A0D98FDEC4389D85" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5da69aaac1bc90c6e03875f228cbb19b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="f5235b4c-d799-48fb-911b-9341dfbcb198" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2d46185ef74ce7664dbfad5565d23765" ns3:_="">
     <xsd:import namespace="f5235b4c-d799-48fb-911b-9341dfbcb198"/>
@@ -7639,15 +7258,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -7657,6 +7267,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A915AD6-87DB-4A49-8A2C-415A966F3ADD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B17DB05-DAA1-4A80-B966-AED12F9FCF5E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7674,26 +7292,18 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A915AD6-87DB-4A49-8A2C-415A966F3ADD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2853C30-6322-4EA0-9233-C02855FA666C}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f5235b4c-d799-48fb-911b-9341dfbcb198"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="f5235b4c-d799-48fb-911b-9341dfbcb198"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Alpha Set List.xlsx
+++ b/Alpha Set List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\apoke\Desktop\Advance!Tactics\Advance-Tactics-Tcgarena\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{974815FC-44CA-4ADC-8474-C8F377A76CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8157E2CD-B0A7-457E-9299-98C1406877E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{CA094A51-376D-41C2-95CA-6278B694BA34}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="451">
   <si>
     <t>Card Name</t>
   </si>
@@ -1431,6 +1431,9 @@
   </si>
   <si>
     <t>James Patterson, Chuck Carr</t>
+  </si>
+  <si>
+    <t>James Patterson, Chuck Carr, Evan Hirt</t>
   </si>
 </sst>
 </file>
@@ -1467,7 +1470,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1498,6 +1501,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1511,7 +1520,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1534,6 +1543,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2435,7 +2445,7 @@
       </c>
     </row>
     <row r="17" spans="1:13" ht="60.75" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" s="12" t="s">
         <v>79</v>
       </c>
       <c r="C17" t="s">
@@ -3234,7 +3244,7 @@
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="7" t="s">
         <v>162</v>
       </c>
       <c r="C40" t="s">
@@ -3770,7 +3780,7 @@
       </c>
     </row>
     <row r="56" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="7" t="s">
         <v>204</v>
       </c>
       <c r="C56" t="s">
@@ -3798,7 +3808,7 @@
         <v>35</v>
       </c>
       <c r="M56" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
@@ -3843,7 +3853,7 @@
       </c>
     </row>
     <row r="58" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="A58" s="12" t="s">
         <v>208</v>
       </c>
       <c r="B58" t="s">
@@ -4172,7 +4182,7 @@
       </c>
     </row>
     <row r="68" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+      <c r="A68" s="8" t="s">
         <v>237</v>
       </c>
       <c r="C68" t="s">
@@ -4344,7 +4354,7 @@
       </c>
     </row>
     <row r="73" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C73" t="s">
@@ -7100,15 +7110,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001E1F373BE6E33547A0D98FDEC4389D85" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5da69aaac1bc90c6e03875f228cbb19b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="f5235b4c-d799-48fb-911b-9341dfbcb198" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2d46185ef74ce7664dbfad5565d23765" ns3:_="">
     <xsd:import namespace="f5235b4c-d799-48fb-911b-9341dfbcb198"/>
@@ -7258,6 +7259,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -7267,14 +7277,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A915AD6-87DB-4A49-8A2C-415A966F3ADD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B17DB05-DAA1-4A80-B966-AED12F9FCF5E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7292,18 +7294,20 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A915AD6-87DB-4A49-8A2C-415A966F3ADD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2853C30-6322-4EA0-9233-C02855FA666C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="f5235b4c-d799-48fb-911b-9341dfbcb198"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Alpha Set List.xlsx
+++ b/Alpha Set List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\apoke\Desktop\Advance!Tactics\Advance-Tactics-Tcgarena\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8157E2CD-B0A7-457E-9299-98C1406877E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30DE6A19-50D2-43F7-8B97-C2B832FAD13F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{CA094A51-376D-41C2-95CA-6278B694BA34}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1163" uniqueCount="451">
   <si>
     <t>Card Name</t>
   </si>
@@ -285,20 +285,7 @@
     <t>A chosen structure falls.</t>
   </si>
   <si>
-    <t>Elaizha, Petromancer</t>
-  </si>
-  <si>
     <t>Champion</t>
-  </si>
-  <si>
-    <t>SSA</t>
-  </si>
-  <si>
-    <t>Elaizha</t>
-  </si>
-  <si>
-    <t>Command(S): Deal damage to target unit equal to this unit's power.
-Command(S): This unit has +10Def until end of turn. You can only activate this ability once per turn.</t>
   </si>
   <si>
     <t>Secret Rare</t>
@@ -1434,6 +1421,19 @@
   </si>
   <si>
     <t>James Patterson, Chuck Carr, Evan Hirt</t>
+  </si>
+  <si>
+    <t>Mt. Yl'lazzha</t>
+  </si>
+  <si>
+    <t>SSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produce: Two of any combination of Stone, Crystal, and/or Metal.
+</t>
+  </si>
+  <si>
+    <t>Elijah Carr</t>
   </si>
 </sst>
 </file>
@@ -1520,7 +1520,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1544,6 +1544,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1965,7 +1966,7 @@
         <v>20</v>
       </c>
       <c r="M2" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="P2">
         <f>COUNTIF(L:L, "Common")</f>
@@ -2147,7 +2148,7 @@
         <v>35</v>
       </c>
       <c r="M7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="24.75" x14ac:dyDescent="0.25">
@@ -2246,7 +2247,7 @@
         <v>35</v>
       </c>
       <c r="M10" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="24.75" x14ac:dyDescent="0.25">
@@ -2418,7 +2419,7 @@
         <v>29</v>
       </c>
       <c r="M15" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -2444,44 +2445,41 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="60.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>79</v>
+    <row r="17" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>447</v>
       </c>
       <c r="C17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" t="s">
+        <v>448</v>
+      </c>
+      <c r="F17">
+        <v>24</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>5</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="L17" t="s">
         <v>80</v>
       </c>
-      <c r="D17" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" t="s">
-        <v>81</v>
-      </c>
-      <c r="F17">
-        <v>24</v>
-      </c>
-      <c r="G17" t="s">
-        <v>38</v>
-      </c>
-      <c r="H17" t="s">
-        <v>82</v>
-      </c>
-      <c r="I17">
-        <v>4</v>
-      </c>
-      <c r="J17">
-        <v>10</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="L17" t="s">
-        <v>84</v>
+      <c r="M17" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
@@ -2490,13 +2488,13 @@
         <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F18">
         <v>5</v>
       </c>
       <c r="G18" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H18" t="s">
         <v>27</v>
@@ -2511,12 +2509,12 @@
         <v>35</v>
       </c>
       <c r="M18" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B19" t="s">
         <v>58</v>
@@ -2528,10 +2526,10 @@
         <v>24</v>
       </c>
       <c r="E19" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="L19" t="s">
         <v>29</v>
@@ -2539,19 +2537,19 @@
     </row>
     <row r="20" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B20" t="s">
         <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
         <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F20">
         <v>8</v>
@@ -2560,7 +2558,7 @@
         <v>53</v>
       </c>
       <c r="H20" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I20">
         <v>11</v>
@@ -2569,15 +2567,15 @@
         <v>5</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L20" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B21" t="s">
         <v>58</v>
@@ -2589,30 +2587,30 @@
         <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F21">
         <v>12</v>
       </c>
       <c r="H21" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="L21" t="s">
         <v>35</v>
       </c>
       <c r="M21" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C22" t="s">
         <v>15</v>
@@ -2621,10 +2619,10 @@
         <v>16</v>
       </c>
       <c r="E22" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="L22" t="s">
         <v>20</v>
@@ -2632,7 +2630,7 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C23" t="s">
         <v>23</v>
@@ -2641,16 +2639,16 @@
         <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F23">
         <v>4</v>
       </c>
       <c r="G23" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H23" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I23">
         <v>2</v>
@@ -2659,7 +2657,7 @@
         <v>6</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L23" t="s">
         <v>20</v>
@@ -2667,7 +2665,7 @@
     </row>
     <row r="24" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s">
         <v>31</v>
@@ -2676,7 +2674,7 @@
         <v>24</v>
       </c>
       <c r="E24" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F24">
         <v>3</v>
@@ -2688,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L24" t="s">
         <v>20</v>
@@ -2696,7 +2694,7 @@
     </row>
     <row r="25" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B25" t="s">
         <v>22</v>
@@ -2708,7 +2706,7 @@
         <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F25">
         <v>10</v>
@@ -2726,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="L25" t="s">
         <v>35</v>
@@ -2734,19 +2732,19 @@
     </row>
     <row r="26" spans="1:13" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B26" t="s">
         <v>62</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D26" t="s">
         <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F26">
         <v>10</v>
@@ -2755,7 +2753,7 @@
         <v>64</v>
       </c>
       <c r="H26" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I26">
         <v>8</v>
@@ -2764,15 +2762,15 @@
         <v>2</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="L26" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -2781,7 +2779,7 @@
         <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -2802,12 +2800,12 @@
         <v>20</v>
       </c>
       <c r="M27" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
@@ -2825,7 +2823,7 @@
         <v>64</v>
       </c>
       <c r="H28" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I28">
         <v>3</v>
@@ -2834,7 +2832,7 @@
         <v>1</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L28" t="s">
         <v>35</v>
@@ -2842,7 +2840,7 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B29" t="s">
         <v>62</v>
@@ -2872,7 +2870,7 @@
         <v>1</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="L29" t="s">
         <v>20</v>
@@ -2880,28 +2878,28 @@
     </row>
     <row r="30" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B30" t="s">
         <v>22</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D30" t="s">
         <v>24</v>
       </c>
       <c r="E30" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F30">
         <v>24</v>
       </c>
       <c r="G30" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H30" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="I30">
         <v>21</v>
@@ -2910,21 +2908,21 @@
         <v>3</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="L30" t="s">
         <v>29</v>
       </c>
       <c r="M30" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B31" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C31" t="s">
         <v>23</v>
@@ -2933,7 +2931,7 @@
         <v>24</v>
       </c>
       <c r="E31" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F31">
         <v>16</v>
@@ -2951,7 +2949,7 @@
         <v>4</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L31" t="s">
         <v>35</v>
@@ -2959,19 +2957,19 @@
     </row>
     <row r="32" spans="1:13" ht="72.75" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B32" t="s">
         <v>62</v>
       </c>
       <c r="C32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D32" t="s">
         <v>16</v>
       </c>
       <c r="E32" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F32">
         <v>5</v>
@@ -2980,7 +2978,7 @@
         <v>38</v>
       </c>
       <c r="H32" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I32">
         <v>17</v>
@@ -2989,7 +2987,7 @@
         <v>5</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="L32" t="s">
         <v>20</v>
@@ -2997,28 +2995,28 @@
     </row>
     <row r="33" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B33" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C33" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D33" t="s">
         <v>24</v>
       </c>
       <c r="E33" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F33">
         <v>7</v>
       </c>
       <c r="G33" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H33" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="I33">
         <v>4</v>
@@ -3027,7 +3025,7 @@
         <v>3</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="L33" t="s">
         <v>29</v>
@@ -3035,7 +3033,7 @@
     </row>
     <row r="34" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B34" t="s">
         <v>58</v>
@@ -3065,39 +3063,39 @@
         <v>3</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="L34" t="s">
         <v>35</v>
       </c>
       <c r="M34" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B35" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C35" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
         <v>24</v>
       </c>
       <c r="E35" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F35">
         <v>11</v>
       </c>
       <c r="G35" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H35" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I35">
         <v>7</v>
@@ -3106,18 +3104,18 @@
         <v>6</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="L35" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="M35" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B36" t="s">
         <v>22</v>
@@ -3129,7 +3127,7 @@
         <v>24</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="L36" t="s">
         <v>20</v>
@@ -3137,10 +3135,10 @@
     </row>
     <row r="37" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B37" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C37" t="s">
         <v>23</v>
@@ -3167,7 +3165,7 @@
         <v>2</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="L37" t="s">
         <v>20</v>
@@ -3175,10 +3173,10 @@
     </row>
     <row r="38" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B38" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C38" t="s">
         <v>31</v>
@@ -3187,7 +3185,7 @@
         <v>24</v>
       </c>
       <c r="E38" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F38">
         <v>4</v>
@@ -3199,7 +3197,7 @@
         <v>1</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="L38" t="s">
         <v>35</v>
@@ -3207,7 +3205,7 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C39" t="s">
         <v>23</v>
@@ -3216,7 +3214,7 @@
         <v>24</v>
       </c>
       <c r="E39" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F39">
         <v>7</v>
@@ -3225,7 +3223,7 @@
         <v>26</v>
       </c>
       <c r="H39" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I39">
         <v>3</v>
@@ -3234,18 +3232,18 @@
         <v>2</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="L39" t="s">
         <v>35</v>
       </c>
       <c r="M39" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C40" t="s">
         <v>15</v>
@@ -3254,33 +3252,33 @@
         <v>46</v>
       </c>
       <c r="E40" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L40" t="s">
         <v>35</v>
       </c>
       <c r="M40" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B41" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C41" t="s">
         <v>23</v>
       </c>
       <c r="D41" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E41" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F41">
         <v>8</v>
@@ -3303,10 +3301,10 @@
     </row>
     <row r="42" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B42" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C42" t="s">
         <v>23</v>
@@ -3333,7 +3331,7 @@
         <v>6</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="L42" t="s">
         <v>20</v>
@@ -3341,10 +3339,10 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B43" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C43" t="s">
         <v>23</v>
@@ -3353,7 +3351,7 @@
         <v>24</v>
       </c>
       <c r="E43" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F43">
         <v>10</v>
@@ -3376,7 +3374,7 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B44" t="s">
         <v>58</v>
@@ -3388,7 +3386,7 @@
         <v>24</v>
       </c>
       <c r="E44" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F44">
         <v>8</v>
@@ -3400,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="L44" t="s">
         <v>35</v>
@@ -3408,7 +3406,7 @@
     </row>
     <row r="45" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B45" t="s">
         <v>58</v>
@@ -3420,7 +3418,7 @@
         <v>24</v>
       </c>
       <c r="E45" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F45">
         <v>5</v>
@@ -3432,7 +3430,7 @@
         <v>9</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="L45" t="s">
         <v>35</v>
@@ -3440,7 +3438,7 @@
     </row>
     <row r="46" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C46" t="s">
         <v>15</v>
@@ -3449,24 +3447,24 @@
         <v>16</v>
       </c>
       <c r="E46" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="H46" t="s">
         <v>18</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="L46" t="s">
         <v>20</v>
       </c>
       <c r="M46" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B47" t="s">
         <v>62</v>
@@ -3478,7 +3476,7 @@
         <v>16</v>
       </c>
       <c r="E47" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F47">
         <v>3</v>
@@ -3496,18 +3494,18 @@
         <v>0</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="L47" t="s">
         <v>35</v>
       </c>
       <c r="M47" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B48" t="s">
         <v>62</v>
@@ -3537,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="L48" t="s">
         <v>35</v>
@@ -3545,7 +3543,7 @@
     </row>
     <row r="49" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C49" t="s">
         <v>23</v>
@@ -3554,7 +3552,7 @@
         <v>24</v>
       </c>
       <c r="E49" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F49">
         <v>1</v>
@@ -3572,18 +3570,18 @@
         <v>1</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="L49" t="s">
         <v>20</v>
       </c>
       <c r="M49" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C50" t="s">
         <v>31</v>
@@ -3592,19 +3590,19 @@
         <v>24</v>
       </c>
       <c r="E50" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
       <c r="H50" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="J50">
         <v>0</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="L50" t="s">
         <v>20</v>
@@ -3612,7 +3610,7 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C51" t="s">
         <v>15</v>
@@ -3621,7 +3619,7 @@
         <v>46</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L51" t="s">
         <v>35</v>
@@ -3629,19 +3627,19 @@
     </row>
     <row r="52" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B52" t="s">
         <v>62</v>
       </c>
       <c r="C52" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D52" t="s">
         <v>24</v>
       </c>
       <c r="E52" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F52">
         <v>7</v>
@@ -3650,7 +3648,7 @@
         <v>38</v>
       </c>
       <c r="H52" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I52">
         <v>7</v>
@@ -3659,18 +3657,18 @@
         <v>7</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L52" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="M52" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B53" t="s">
         <v>22</v>
@@ -3682,19 +3680,19 @@
         <v>24</v>
       </c>
       <c r="E53" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="H53" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="J53">
         <v>15</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="L53" t="s">
         <v>29</v>
@@ -3702,7 +3700,7 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B54" t="s">
         <v>62</v>
@@ -3723,7 +3721,7 @@
         <v>64</v>
       </c>
       <c r="H54" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I54">
         <v>7</v>
@@ -3732,7 +3730,7 @@
         <v>1</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="L54" t="s">
         <v>35</v>
@@ -3740,10 +3738,10 @@
     </row>
     <row r="55" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B55" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C55" t="s">
         <v>23</v>
@@ -3752,13 +3750,13 @@
         <v>24</v>
       </c>
       <c r="E55" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F55">
         <v>3</v>
       </c>
       <c r="G55" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H55" t="s">
         <v>27</v>
@@ -3770,18 +3768,18 @@
         <v>0</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="L55" t="s">
         <v>35</v>
       </c>
       <c r="M55" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C56" t="s">
         <v>31</v>
@@ -3790,7 +3788,7 @@
         <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F56">
         <v>5</v>
@@ -3802,18 +3800,18 @@
         <v>2</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="L56" t="s">
         <v>35</v>
       </c>
       <c r="M56" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B57" t="s">
         <v>58</v>
@@ -3843,39 +3841,39 @@
         <v>1</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L57" t="s">
         <v>20</v>
       </c>
       <c r="M57" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B58" t="s">
         <v>58</v>
       </c>
       <c r="C58" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D58" t="s">
         <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F58">
         <v>18</v>
       </c>
       <c r="G58" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H58" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -3884,7 +3882,7 @@
         <v>12</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="L58" t="s">
         <v>29</v>
@@ -3892,7 +3890,7 @@
     </row>
     <row r="59" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C59" t="s">
         <v>31</v>
@@ -3901,19 +3899,19 @@
         <v>24</v>
       </c>
       <c r="E59" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="H59" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="J59">
         <v>0</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="L59" t="s">
         <v>35</v>
@@ -3921,28 +3919,28 @@
     </row>
     <row r="60" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B60" t="s">
         <v>62</v>
       </c>
       <c r="C60" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D60" t="s">
         <v>24</v>
       </c>
       <c r="E60" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="F60">
         <v>16</v>
       </c>
       <c r="G60" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="H60" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="I60">
         <v>2</v>
@@ -3951,36 +3949,36 @@
         <v>2</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="L60" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="M60" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C61" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D61" t="s">
         <v>24</v>
       </c>
       <c r="E61" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F61">
         <v>2</v>
       </c>
       <c r="G61" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="H61" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="I61">
         <v>1</v>
@@ -3989,7 +3987,7 @@
         <v>8</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="L61" t="s">
         <v>29</v>
@@ -3997,7 +3995,7 @@
     </row>
     <row r="62" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C62" t="s">
         <v>31</v>
@@ -4015,18 +4013,18 @@
         <v>1</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="L62" t="s">
         <v>29</v>
       </c>
       <c r="M62" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C63" t="s">
         <v>31</v>
@@ -4035,19 +4033,19 @@
         <v>24</v>
       </c>
       <c r="E63" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F63">
         <v>10</v>
       </c>
       <c r="H63" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="J63">
         <v>8</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="L63" t="s">
         <v>35</v>
@@ -4055,7 +4053,7 @@
     </row>
     <row r="64" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C64" t="s">
         <v>23</v>
@@ -4064,16 +4062,16 @@
         <v>24</v>
       </c>
       <c r="E64" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F64">
         <v>5</v>
       </c>
       <c r="G64" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="H64" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I64">
         <v>1</v>
@@ -4082,18 +4080,18 @@
         <v>4</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="L64" t="s">
         <v>35</v>
       </c>
       <c r="M64" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C65" t="s">
         <v>23</v>
@@ -4102,13 +4100,13 @@
         <v>24</v>
       </c>
       <c r="E65" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F65">
         <v>4</v>
       </c>
       <c r="G65" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H65" t="s">
         <v>27</v>
@@ -4123,12 +4121,12 @@
         <v>35</v>
       </c>
       <c r="M65" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C66" t="s">
         <v>15</v>
@@ -4137,7 +4135,7 @@
         <v>16</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L66" t="s">
         <v>35</v>
@@ -4145,7 +4143,7 @@
     </row>
     <row r="67" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B67" t="s">
         <v>62</v>
@@ -4166,7 +4164,7 @@
         <v>53</v>
       </c>
       <c r="H67" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="I67">
         <v>3</v>
@@ -4175,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="L67" t="s">
         <v>35</v>
@@ -4183,7 +4181,7 @@
     </row>
     <row r="68" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C68" t="s">
         <v>15</v>
@@ -4198,7 +4196,7 @@
         <v>18</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="L68" t="s">
         <v>35</v>
@@ -4206,7 +4204,7 @@
     </row>
     <row r="69" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C69" t="s">
         <v>23</v>
@@ -4215,13 +4213,13 @@
         <v>24</v>
       </c>
       <c r="E69" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F69">
         <v>5</v>
       </c>
       <c r="G69" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H69" t="s">
         <v>27</v>
@@ -4233,18 +4231,18 @@
         <v>6</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="L69" t="s">
         <v>35</v>
       </c>
       <c r="M69" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B70" t="s">
         <v>62</v>
@@ -4256,16 +4254,16 @@
         <v>46</v>
       </c>
       <c r="E70" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="H70" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -4274,18 +4272,18 @@
         <v>15</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="L70" t="s">
         <v>20</v>
       </c>
       <c r="M70" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C71" t="s">
         <v>23</v>
@@ -4294,16 +4292,16 @@
         <v>16</v>
       </c>
       <c r="E71" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F71">
         <v>5</v>
       </c>
       <c r="G71" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H71" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="I71">
         <v>4</v>
@@ -4312,7 +4310,7 @@
         <v>1</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="L71" t="s">
         <v>35</v>
@@ -4320,7 +4318,7 @@
     </row>
     <row r="72" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C72" t="s">
         <v>23</v>
@@ -4335,7 +4333,7 @@
         <v>3</v>
       </c>
       <c r="G72" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H72" t="s">
         <v>74</v>
@@ -4347,7 +4345,7 @@
         <v>0</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="L72" t="s">
         <v>35</v>
@@ -4355,25 +4353,25 @@
     </row>
     <row r="73" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C73" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D73" t="s">
         <v>24</v>
       </c>
       <c r="E73" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F73">
         <v>8</v>
       </c>
       <c r="G73" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H73" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I73">
         <v>6</v>
@@ -4382,13 +4380,13 @@
         <v>11</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="L73" t="s">
+        <v>80</v>
+      </c>
+      <c r="M73" t="s">
         <v>84</v>
-      </c>
-      <c r="M73" t="s">
-        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -4458,12 +4456,12 @@
         <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C2" t="s">
         <v>23</v>
@@ -4472,13 +4470,13 @@
         <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F2">
         <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="H2" t="s">
         <v>27</v>
@@ -4490,24 +4488,24 @@
         <v>3</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
         <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F3">
         <v>6</v>
@@ -4516,7 +4514,7 @@
         <v>38</v>
       </c>
       <c r="H3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="I3">
         <v>8</v>
@@ -4525,12 +4523,12 @@
         <v>5</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
@@ -4560,12 +4558,12 @@
         <v>1</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -4577,18 +4575,18 @@
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="H5" t="s">
         <v>18</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C6" t="s">
         <v>31</v>
@@ -4603,18 +4601,18 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="J6">
         <v>5</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
@@ -4641,12 +4639,12 @@
         <v>4</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
@@ -4673,12 +4671,12 @@
         <v>3</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
@@ -4690,7 +4688,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F9">
         <v>10</v>
@@ -4699,7 +4697,7 @@
         <v>26</v>
       </c>
       <c r="H9" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="I9">
         <v>9</v>
@@ -4708,18 +4706,18 @@
         <v>2</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B10" t="s">
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
         <v>24</v>
@@ -4734,7 +4732,7 @@
         <v>26</v>
       </c>
       <c r="H10" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -4743,12 +4741,12 @@
         <v>1</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C11" t="s">
         <v>23</v>
@@ -4757,16 +4755,16 @@
         <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F11">
         <v>5</v>
       </c>
       <c r="G11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H11" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="I11">
         <v>4</v>
@@ -4775,12 +4773,12 @@
         <v>6</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
@@ -4789,7 +4787,7 @@
         <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F12">
         <v>10</v>
@@ -4798,12 +4796,12 @@
         <v>0</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
@@ -4812,7 +4810,7 @@
         <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="F13">
         <v>6</v>
@@ -4824,12 +4822,12 @@
         <v>0</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
@@ -4838,13 +4836,13 @@
         <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F14">
         <v>4</v>
       </c>
       <c r="G14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H14" t="s">
         <v>27</v>
@@ -4856,12 +4854,12 @@
         <v>4</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
@@ -4870,7 +4868,7 @@
         <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -4879,30 +4877,30 @@
         <v>1</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D16" t="s">
         <v>24</v>
       </c>
       <c r="E16" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F16">
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="H16" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="I16">
         <v>10</v>
@@ -4911,12 +4909,12 @@
         <v>6</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
@@ -4925,13 +4923,13 @@
         <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F17">
         <v>3</v>
       </c>
       <c r="G17" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H17" t="s">
         <v>74</v>
@@ -4943,12 +4941,12 @@
         <v>4</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
@@ -4963,7 +4961,7 @@
         <v>2</v>
       </c>
       <c r="G18" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="H18" t="s">
         <v>69</v>
@@ -4975,12 +4973,12 @@
         <v>0</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B19" t="s">
         <v>62</v>
@@ -4998,10 +4996,10 @@
         <v>6</v>
       </c>
       <c r="G19" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="H19" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="I19">
         <v>5</v>
@@ -5010,12 +5008,12 @@
         <v>5</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C20" t="s">
         <v>23</v>
@@ -5024,13 +5022,13 @@
         <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="F20">
         <v>3</v>
       </c>
       <c r="G20" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H20" t="s">
         <v>27</v>
@@ -5042,12 +5040,12 @@
         <v>0</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C21" t="s">
         <v>56</v>
@@ -5062,30 +5060,30 @@
         <v>0</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D22" t="s">
         <v>24</v>
       </c>
       <c r="E22" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="F22">
         <v>5</v>
       </c>
       <c r="G22" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="H22" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="I22">
         <v>2</v>
@@ -5094,12 +5092,12 @@
         <v>4</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C23" t="s">
         <v>23</v>
@@ -5108,12 +5106,12 @@
         <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C24" t="s">
         <v>23</v>
@@ -5122,16 +5120,16 @@
         <v>24</v>
       </c>
       <c r="E24" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F24">
         <v>5</v>
       </c>
       <c r="G24" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="H24" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I24">
         <v>4</v>
@@ -5140,12 +5138,12 @@
         <v>4</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C25" t="s">
         <v>23</v>
@@ -5160,7 +5158,7 @@
         <v>7</v>
       </c>
       <c r="G25" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="H25" t="s">
         <v>27</v>
@@ -5174,7 +5172,7 @@
     </row>
     <row r="26" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C26" t="s">
         <v>31</v>
@@ -5183,7 +5181,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F26">
         <v>6</v>
@@ -5192,12 +5190,12 @@
         <v>0</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -5206,16 +5204,16 @@
         <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F27">
         <v>3</v>
       </c>
       <c r="G27" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="H27" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="I27">
         <v>1</v>
@@ -5224,12 +5222,12 @@
         <v>0</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
@@ -5238,7 +5236,7 @@
         <v>24</v>
       </c>
       <c r="E28" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="F28">
         <v>3</v>
@@ -5256,12 +5254,12 @@
         <v>2</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C29" t="s">
         <v>15</v>
@@ -5270,12 +5268,12 @@
         <v>46</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C30" t="s">
         <v>15</v>
@@ -5284,12 +5282,12 @@
         <v>46</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C31" t="s">
         <v>23</v>
@@ -5298,7 +5296,7 @@
         <v>24</v>
       </c>
       <c r="E31" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F31">
         <v>10</v>
@@ -5313,12 +5311,12 @@
         <v>2</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C32" t="s">
         <v>23</v>
@@ -5341,7 +5339,7 @@
     </row>
     <row r="33" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C33" t="s">
         <v>31</v>
@@ -5350,24 +5348,24 @@
         <v>24</v>
       </c>
       <c r="E33" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B34" t="s">
         <v>22</v>
@@ -5379,7 +5377,7 @@
         <v>24</v>
       </c>
       <c r="E34" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F34">
         <v>10</v>
@@ -5388,7 +5386,7 @@
         <v>26</v>
       </c>
       <c r="H34" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="I34">
         <v>2</v>
@@ -5397,12 +5395,12 @@
         <v>2</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C35" t="s">
         <v>31</v>
@@ -5411,24 +5409,24 @@
         <v>24</v>
       </c>
       <c r="E35" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F35">
         <v>3</v>
       </c>
       <c r="G35" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="J35">
         <v>0</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C36" t="s">
         <v>15</v>
@@ -5437,18 +5435,18 @@
         <v>16</v>
       </c>
       <c r="E36" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="H36" t="s">
         <v>18</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C37" t="s">
         <v>23</v>
@@ -5457,7 +5455,7 @@
         <v>24</v>
       </c>
       <c r="E37" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F37">
         <v>5</v>
@@ -5475,12 +5473,12 @@
         <v>0</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C38" t="s">
         <v>15</v>
@@ -5495,12 +5493,12 @@
         <v>18</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B39" t="s">
         <v>58</v>
@@ -5512,13 +5510,13 @@
         <v>24</v>
       </c>
       <c r="E39" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="F39">
         <v>4</v>
       </c>
       <c r="G39" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="H39" t="s">
         <v>69</v>
@@ -5530,12 +5528,12 @@
         <v>4</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C40" t="s">
         <v>31</v>
@@ -5544,7 +5542,7 @@
         <v>24</v>
       </c>
       <c r="E40" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F40">
         <v>3</v>
@@ -5556,15 +5554,15 @@
         <v>0</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B41" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C41" t="s">
         <v>23</v>
@@ -5573,16 +5571,16 @@
         <v>16</v>
       </c>
       <c r="E41" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="F41">
         <v>5</v>
       </c>
       <c r="G41" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H41" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="I41">
         <v>8</v>
@@ -5591,15 +5589,15 @@
         <v>3</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B42" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C42" t="s">
         <v>56</v>
@@ -5614,24 +5612,24 @@
         <v>1</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B43" t="s">
         <v>58</v>
       </c>
       <c r="C43" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D43" t="s">
         <v>24</v>
       </c>
       <c r="E43" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="F43">
         <v>5</v>
@@ -5640,7 +5638,7 @@
         <v>38</v>
       </c>
       <c r="H43" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="I43">
         <v>4</v>
@@ -5649,12 +5647,12 @@
         <v>5</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B44" t="s">
         <v>58</v>
@@ -5684,12 +5682,12 @@
         <v>4</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B45" t="s">
         <v>22</v>
@@ -5701,16 +5699,16 @@
         <v>24</v>
       </c>
       <c r="E45" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="F45">
         <v>4</v>
       </c>
       <c r="G45" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H45" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="I45">
         <v>14</v>
@@ -5721,7 +5719,7 @@
     </row>
     <row r="46" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C46" t="s">
         <v>15</v>
@@ -5730,15 +5728,15 @@
         <v>24</v>
       </c>
       <c r="E46" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C47" t="s">
         <v>15</v>
@@ -5747,15 +5745,15 @@
         <v>46</v>
       </c>
       <c r="E47" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C48" t="s">
         <v>31</v>
@@ -5764,7 +5762,7 @@
         <v>24</v>
       </c>
       <c r="E48" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F48">
         <v>5</v>
@@ -5776,30 +5774,30 @@
         <v>3</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C49" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D49" t="s">
         <v>24</v>
       </c>
       <c r="E49" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="F49">
         <v>40</v>
       </c>
       <c r="G49" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="H49" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="I49">
         <v>5</v>
@@ -5808,12 +5806,12 @@
         <v>0</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="50" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C50" t="s">
         <v>15</v>
@@ -5822,18 +5820,18 @@
         <v>24</v>
       </c>
       <c r="E50" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H50" t="s">
         <v>18</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="51" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C51" t="s">
         <v>15</v>
@@ -5842,15 +5840,15 @@
         <v>24</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B52" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C52" t="s">
         <v>23</v>
@@ -5859,13 +5857,13 @@
         <v>24</v>
       </c>
       <c r="E52" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F52">
         <v>6</v>
       </c>
       <c r="G52" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H52" t="s">
         <v>27</v>
@@ -5877,12 +5875,12 @@
         <v>2</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C53" t="s">
         <v>15</v>
@@ -5891,15 +5889,15 @@
         <v>24</v>
       </c>
       <c r="E53" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="B54" t="s">
         <v>58</v>
@@ -5911,18 +5909,18 @@
         <v>46</v>
       </c>
       <c r="E54" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B55" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C55" t="s">
         <v>15</v>
@@ -5931,15 +5929,15 @@
         <v>46</v>
       </c>
       <c r="E55" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B56" t="s">
         <v>22</v>
@@ -5951,18 +5949,18 @@
         <v>16</v>
       </c>
       <c r="E56" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B57" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C57" t="s">
         <v>15</v>
@@ -5971,18 +5969,18 @@
         <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="H57" t="s">
         <v>18</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C58" t="s">
         <v>23</v>
@@ -5991,13 +5989,13 @@
         <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="F58">
         <v>7</v>
       </c>
       <c r="G58" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H58" t="s">
         <v>27</v>
@@ -6009,24 +6007,24 @@
         <v>4</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B59" t="s">
         <v>58</v>
       </c>
       <c r="C59" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D59" t="s">
         <v>24</v>
       </c>
       <c r="E59" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F59">
         <v>7</v>
@@ -6035,7 +6033,7 @@
         <v>53</v>
       </c>
       <c r="H59" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I59">
         <v>5</v>
@@ -6044,12 +6042,12 @@
         <v>5</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B60" t="s">
         <v>62</v>
@@ -6061,7 +6059,7 @@
         <v>24</v>
       </c>
       <c r="E60" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F60">
         <v>3</v>
@@ -6079,12 +6077,12 @@
         <v>0</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B61" t="s">
         <v>58</v>
@@ -6096,18 +6094,18 @@
         <v>24</v>
       </c>
       <c r="E61" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="O61" s="5" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C62" t="s">
         <v>15</v>
@@ -6116,21 +6114,21 @@
         <v>16</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C63" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D63" t="s">
         <v>24</v>
       </c>
       <c r="E63" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="F63">
         <v>15</v>
@@ -6139,7 +6137,7 @@
         <v>26</v>
       </c>
       <c r="H63" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I63">
         <v>10</v>
@@ -6148,12 +6146,12 @@
         <v>4</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C64" t="s">
         <v>31</v>
@@ -6162,7 +6160,7 @@
         <v>24</v>
       </c>
       <c r="E64" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="F64">
         <v>12</v>
@@ -6178,12 +6176,12 @@
       </c>
       <c r="K64" s="10"/>
       <c r="O64" s="5" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A65" s="9" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C65" t="s">
         <v>23</v>
@@ -6192,13 +6190,13 @@
         <v>24</v>
       </c>
       <c r="E65" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F65">
         <v>8</v>
       </c>
       <c r="G65" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="H65" t="s">
         <v>27</v>
@@ -6210,30 +6208,30 @@
         <v>2</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C66" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D66" t="s">
         <v>24</v>
       </c>
       <c r="E66" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F66">
         <v>5</v>
       </c>
       <c r="G66" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="H66" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="I66">
         <v>1</v>
@@ -6242,12 +6240,12 @@
         <v>4</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C67" t="s">
         <v>23</v>
@@ -6256,13 +6254,13 @@
         <v>24</v>
       </c>
       <c r="E67" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F67">
         <v>7</v>
       </c>
       <c r="G67" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H67" t="s">
         <v>27</v>
@@ -6276,10 +6274,10 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B68" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C68" t="s">
         <v>23</v>
@@ -6288,13 +6286,13 @@
         <v>24</v>
       </c>
       <c r="E68" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="F68">
         <v>8</v>
       </c>
       <c r="G68" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H68" t="s">
         <v>27</v>
@@ -6311,7 +6309,7 @@
     </row>
     <row r="69" spans="1:12" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C69" t="s">
         <v>15</v>
@@ -6320,15 +6318,15 @@
         <v>24</v>
       </c>
       <c r="E69" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C70" t="s">
         <v>15</v>
@@ -6337,7 +6335,7 @@
         <v>24</v>
       </c>
       <c r="E70" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="K70" s="10"/>
     </row>
@@ -6652,45 +6650,45 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D1" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1" t="s">
         <v>435</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
         <v>436</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
         <v>437</v>
-      </c>
-      <c r="D1" t="s">
-        <v>438</v>
-      </c>
-      <c r="E1" t="s">
-        <v>439</v>
-      </c>
-      <c r="F1" t="s">
-        <v>440</v>
-      </c>
-      <c r="G1" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D2" t="s">
+        <v>443</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="B2" t="s">
-        <v>443</v>
-      </c>
-      <c r="C2" t="s">
-        <v>444</v>
-      </c>
-      <c r="D2" t="s">
-        <v>447</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>446</v>
       </c>
     </row>
   </sheetData>
@@ -6757,7 +6755,7 @@
     </row>
     <row r="2" spans="1:12" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C2" t="s">
         <v>23</v>
@@ -6766,16 +6764,16 @@
         <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="I2">
         <v>6</v>
@@ -6784,7 +6782,7 @@
         <v>10</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="L2" t="s">
         <v>35</v>
@@ -6812,37 +6810,37 @@
   <sheetData>
     <row r="1" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="D1" s="11"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -6857,13 +6855,13 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6878,13 +6876,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -6895,53 +6893,53 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="D7">
         <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B8">
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -6952,47 +6950,47 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
       <c r="H9" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B10">
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="H10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B11">
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D11">
         <v>3</v>
       </c>
       <c r="H11" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -7009,12 +7007,12 @@
         <v>3</v>
       </c>
       <c r="H12" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -7026,58 +7024,58 @@
         <v>3</v>
       </c>
       <c r="H13" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B14">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
       <c r="H14" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B15">
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D15">
         <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D16">
         <v>3</v>
       </c>
       <c r="H16" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -7088,13 +7086,13 @@
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D17">
         <v>3</v>
       </c>
       <c r="H17" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/Alpha Set List.xlsx
+++ b/Alpha Set List.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\apoke\Desktop\Advance!Tactics\Advance-Tactics-Tcgarena\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30DE6A19-50D2-43F7-8B97-C2B832FAD13F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{79973F57-B11A-454B-BE74-B03B9AA24C19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{CA094A51-376D-41C2-95CA-6278B694BA34}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Set 3'!$A$69:$K$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Set1 - Alpha'!$A$69:$K$69</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -46,11 +46,186 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1163" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="450">
   <si>
     <t>Card Name</t>
   </si>
   <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Race</t>
+  </si>
+  <si>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>Def</t>
+  </si>
+  <si>
+    <t>Goblin Vanguard</t>
+  </si>
+  <si>
+    <t>Chaotic</t>
+  </si>
+  <si>
+    <t>Army</t>
+  </si>
+  <si>
+    <t>Quick</t>
+  </si>
+  <si>
+    <t>SF</t>
+  </si>
+  <si>
+    <t>Goblin</t>
+  </si>
+  <si>
+    <t>Warriors</t>
+  </si>
+  <si>
+    <t>Effects</t>
+  </si>
+  <si>
+    <t>Ramshackle Cavalry</t>
+  </si>
+  <si>
+    <t>Rudimentry Archers</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>Goblin Giants</t>
+  </si>
+  <si>
+    <t>WI</t>
+  </si>
+  <si>
+    <t>SWI</t>
+  </si>
+  <si>
+    <t>Goblin Prospectors</t>
+  </si>
+  <si>
+    <t>Peasants</t>
+  </si>
+  <si>
+    <t>Static: The tile occupied by this card is a Stone Resource tile.</t>
+  </si>
+  <si>
+    <t>Goblin Chief Bucas</t>
+  </si>
+  <si>
+    <t>Champion</t>
+  </si>
+  <si>
+    <t>SFM</t>
+  </si>
+  <si>
+    <t>Num/Ft</t>
+  </si>
+  <si>
+    <t>Evhan of the Kobold Legion</t>
+  </si>
+  <si>
+    <t>Cunning</t>
+  </si>
+  <si>
+    <t>SWM</t>
+  </si>
+  <si>
+    <t>Kobold</t>
+  </si>
+  <si>
+    <t>Sculptor Konor</t>
+  </si>
+  <si>
+    <t>Golem</t>
+  </si>
+  <si>
+    <t>Static: Once per turn, when one of your Goblins advances, you may have it advance again.
+Static: The first time one of your Goblins would take damage each turn, it instead moves one lane to the right or left, chosen at random.</t>
+  </si>
+  <si>
+    <t>Scavenging Kobolds</t>
+  </si>
+  <si>
+    <t>WF</t>
+  </si>
+  <si>
+    <t>Scouts</t>
+  </si>
+  <si>
+    <t>Crafty Kobolds</t>
+  </si>
+  <si>
+    <t>Reckless Arsonists</t>
+  </si>
+  <si>
+    <t>Human</t>
+  </si>
+  <si>
+    <t>Static: Tiles within 1 orthoginal tile of this card have no resource type.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palador Knights </t>
+  </si>
+  <si>
+    <t>Righteous</t>
+  </si>
+  <si>
+    <t>FI</t>
+  </si>
+  <si>
+    <t>Palador Elites</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normal </t>
+  </si>
+  <si>
+    <t>Palador Frontliners</t>
+  </si>
+  <si>
+    <t>Static: If this unit is behind another friendly combatant, this unit advances.</t>
+  </si>
+  <si>
+    <t>Mages of Palador</t>
+  </si>
+  <si>
+    <t>Mages</t>
+  </si>
+  <si>
+    <t>Crooked Coinswipes</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Criminals</t>
+  </si>
+  <si>
+    <t>Post-Battle: One random resource in your opponent's reserves decays. Produce a resource of the same type.</t>
+  </si>
+  <si>
+    <t>Kobold Contraptionists</t>
+  </si>
+  <si>
+    <t>Architects</t>
+  </si>
+  <si>
+    <t>Stone Legion</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>Enhanced Managolems</t>
+  </si>
+  <si>
     <t>Align</t>
   </si>
   <si>
@@ -60,310 +235,248 @@
     <t>Spd</t>
   </si>
   <si>
-    <t>Cost</t>
-  </si>
-  <si>
-    <t>Num/Ft</t>
-  </si>
-  <si>
-    <t>Race</t>
-  </si>
-  <si>
-    <t>Class</t>
-  </si>
-  <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t>Def</t>
-  </si>
-  <si>
-    <t>Effects</t>
-  </si>
-  <si>
-    <t>Rarity</t>
-  </si>
-  <si>
-    <t>Art Status</t>
-  </si>
-  <si>
-    <t>Artist</t>
+    <t>Sawmill</t>
+  </si>
+  <si>
+    <t>Structure</t>
+  </si>
+  <si>
+    <t>Building</t>
+  </si>
+  <si>
+    <t>Farm</t>
+  </si>
+  <si>
+    <t>SCA</t>
+  </si>
+  <si>
+    <t>WA</t>
+  </si>
+  <si>
+    <t>Mana Well</t>
+  </si>
+  <si>
+    <t>SW</t>
+  </si>
+  <si>
+    <t>Heroic Battalion</t>
+  </si>
+  <si>
+    <t>SFFF</t>
+  </si>
+  <si>
+    <t>Static: If this unit is engaging a Ruthless unit, it has +1 Power.</t>
+  </si>
+  <si>
+    <t>Callous Kobolds</t>
+  </si>
+  <si>
+    <t>Ruthless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Static: This unit can advance while engaged. </t>
+  </si>
+  <si>
+    <t>Retreat</t>
+  </si>
+  <si>
+    <t>Command</t>
+  </si>
+  <si>
+    <t>Rapid</t>
+  </si>
+  <si>
+    <t>Tactical Roll</t>
+  </si>
+  <si>
+    <t>All of your combatants move back 1 tile.</t>
+  </si>
+  <si>
+    <t>Loot the Bodies</t>
+  </si>
+  <si>
+    <t>Move one of your combatants one tile horizontally.</t>
+  </si>
+  <si>
+    <t>AA</t>
+  </si>
+  <si>
+    <t>A chosen structure falls.</t>
+  </si>
+  <si>
+    <t>Teleportation</t>
+  </si>
+  <si>
+    <t>Palador Mage Guild</t>
+  </si>
+  <si>
+    <t>Activate: If unengaged, this unit advances.</t>
+  </si>
+  <si>
+    <t>Produce: One Mana
+Static: Your other Mage units have +1 Power and +1 Defense.
+Activate: One of your mage units gains 2k numbers.</t>
+  </si>
+  <si>
+    <t>Palador Library</t>
+  </si>
+  <si>
+    <t>WII</t>
+  </si>
+  <si>
+    <t>Activate: Draw 1 card.</t>
+  </si>
+  <si>
+    <t>Castle of New Beginnings</t>
+  </si>
+  <si>
+    <t>Castle</t>
+  </si>
+  <si>
+    <t>Stone Barricades</t>
+  </si>
+  <si>
+    <t>Defenses</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Elemental</t>
+  </si>
+  <si>
+    <t>Dark Cultists</t>
+  </si>
+  <si>
+    <t>IA</t>
+  </si>
+  <si>
+    <t>Ball of Fire</t>
+  </si>
+  <si>
+    <t>Spell</t>
+  </si>
+  <si>
+    <t>Earthquake</t>
+  </si>
+  <si>
+    <t>If this command targets a structure, it costs an additional A.
+One chosen unit moves up to 2 tiles orthoganally.</t>
+  </si>
+  <si>
+    <t>Exhaustive Research</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>Discard a card, then draw 2 cards.</t>
+  </si>
+  <si>
+    <t>Static: When this unit advances, combatants within one orthogonal tile move to the occupied tile.</t>
+  </si>
+  <si>
+    <t>Static: Your other armies within 1 orthoginal tile of this card have +3 Power and +1 Defense.</t>
+  </si>
+  <si>
+    <t>SWF</t>
+  </si>
+  <si>
+    <t>Enter: Excavate for a Building card. Put that card into your hand.</t>
+  </si>
+  <si>
+    <t>Architects of Palador</t>
+  </si>
+  <si>
+    <t>Evhan's Wall of Panic</t>
+  </si>
+  <si>
+    <t>Trigger: Flip 2 coins. If either are tails, triggering unit moves backwards 1 tile.</t>
+  </si>
+  <si>
+    <t>Espionage</t>
+  </si>
+  <si>
+    <t>Choose an opponent and look at their hand. They discard 1 chosen card.</t>
+  </si>
+  <si>
+    <t>WAA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Choose a lane. Deal 8 damage to each unit in that lane. </t>
+  </si>
+  <si>
+    <t>Trap</t>
+  </si>
+  <si>
+    <t>Sensitive Spike Shooter</t>
+  </si>
+  <si>
+    <t>Bucas</t>
+  </si>
+  <si>
+    <t>Evhan</t>
+  </si>
+  <si>
+    <t>God</t>
+  </si>
+  <si>
+    <t>Harbinger</t>
+  </si>
+  <si>
+    <t>Harbinger of Death</t>
+  </si>
+  <si>
+    <t>ICCAA</t>
+  </si>
+  <si>
+    <t>Static: Enemy combatants cannot advance forward while on the occupied tile.</t>
+  </si>
+  <si>
+    <t>Can only be played after the combat step.
+If any of your units felled a combatant this turn, draw two cards.</t>
+  </si>
+  <si>
+    <t>Recyclists of the Muck</t>
+  </si>
+  <si>
+    <t>Architect's Guild</t>
+  </si>
+  <si>
+    <t>SSWW</t>
+  </si>
+  <si>
+    <t>Ritual of Annihilation</t>
+  </si>
+  <si>
+    <t>CFAAAA</t>
+  </si>
+  <si>
+    <t>Ritual</t>
+  </si>
+  <si>
+    <t>End: Each other unit within one tile of this unit loses 5kNum/5Ftt.</t>
+  </si>
+  <si>
+    <t>Activate(WW/SS): Put a Building from your hand onto the field in any tile you could normally play one.</t>
   </si>
   <si>
     <t>Ancient Knowledge</t>
   </si>
   <si>
-    <t>Command</t>
-  </si>
-  <si>
-    <t>Quick</t>
-  </si>
-  <si>
     <t>IAA</t>
   </si>
   <si>
-    <t>Spell</t>
-  </si>
-  <si>
     <t>Draw 4 cards.</t>
   </si>
   <si>
-    <t>Uncommon</t>
-  </si>
-  <si>
-    <t>Ants Insatiable</t>
-  </si>
-  <si>
-    <t>Ruthless</t>
-  </si>
-  <si>
-    <t>Army</t>
-  </si>
-  <si>
-    <t>Normal</t>
-  </si>
-  <si>
-    <t>FFF</t>
-  </si>
-  <si>
-    <t>Insect</t>
-  </si>
-  <si>
-    <t>Warriors</t>
-  </si>
-  <si>
-    <t>Static: When this unit deals undefended damage, put that many +1Pow counters on it.</t>
-  </si>
-  <si>
-    <t>Rare</t>
-  </si>
-  <si>
-    <t>Architect's Guild</t>
-  </si>
-  <si>
-    <t>Structure</t>
-  </si>
-  <si>
-    <t>SSWW</t>
-  </si>
-  <si>
-    <t>Building</t>
-  </si>
-  <si>
-    <t>Activate(WW/SS): Put a Building from your hand onto the field in any tile you could normally play one.</t>
-  </si>
-  <si>
-    <t>Common</t>
-  </si>
-  <si>
-    <t>Architects of Palador</t>
-  </si>
-  <si>
-    <t>SWF</t>
-  </si>
-  <si>
-    <t>Human</t>
-  </si>
-  <si>
-    <t>Architects</t>
-  </si>
-  <si>
-    <t>Enter: Excavate for a Building card. Put that card into your hand.</t>
-  </si>
-  <si>
-    <t>Army of Mandibles</t>
-  </si>
-  <si>
-    <t>SF</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>Static: This unit's power is equal to half its numbers, rounded down.</t>
-  </si>
-  <si>
-    <t>Ball of Fire</t>
-  </si>
-  <si>
-    <t>Rapid</t>
-  </si>
-  <si>
-    <t>WA</t>
-  </si>
-  <si>
-    <t>Deal 6 true damage to each unit on a chosen tile. Deal 4 true damage to each unit on each tile one orthoginal tile away  from the chosen tile.</t>
-  </si>
-  <si>
-    <t>Black Colony Guards</t>
-  </si>
-  <si>
-    <t>WF</t>
-  </si>
-  <si>
-    <t>Static: This unit's power is equal the number of your combatants on the field.</t>
-  </si>
-  <si>
-    <t>Callous Kobolds</t>
-  </si>
-  <si>
-    <t>Kobold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Static: This unit can advance while engaged. </t>
-  </si>
-  <si>
-    <t>Castle of New Beginnings</t>
-  </si>
-  <si>
-    <t>Castle</t>
-  </si>
-  <si>
-    <t>Crafty Kobolds</t>
-  </si>
-  <si>
-    <t>Cunning</t>
-  </si>
-  <si>
-    <t>SWI</t>
-  </si>
-  <si>
-    <t>Static: Your other armies within 1 orthoginal tile of this card have +3 Power and +1 Defense.</t>
-  </si>
-  <si>
-    <t>Crooked Coinswipes</t>
-  </si>
-  <si>
-    <t>Chaotic</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>Goblin</t>
-  </si>
-  <si>
-    <t>Criminals</t>
-  </si>
-  <si>
-    <t>Post-Battle: One random resource in your opponent's reserves decays. Produce a resource of the same type.</t>
-  </si>
-  <si>
-    <t>Dark Cultists</t>
-  </si>
-  <si>
-    <t>IA</t>
-  </si>
-  <si>
-    <t>Mages</t>
-  </si>
-  <si>
-    <t>Activate(Sacrifice an Army): This unit gets +1 Power</t>
-  </si>
-  <si>
-    <t>Dig Deeper</t>
-  </si>
-  <si>
-    <t>Produce a resource that shares a type with a resource tile you control.</t>
-  </si>
-  <si>
-    <t>Dung-Beetle Scavengers</t>
-  </si>
-  <si>
-    <t>Scavengers</t>
-  </si>
-  <si>
-    <t>Produce(You have no other units): Two Food</t>
-  </si>
-  <si>
-    <t>Earthquake</t>
-  </si>
-  <si>
-    <t>AA</t>
-  </si>
-  <si>
-    <t>A chosen structure falls.</t>
-  </si>
-  <si>
-    <t>Champion</t>
-  </si>
-  <si>
-    <t>Secret Rare</t>
-  </si>
-  <si>
-    <t>Enhanced Managolems</t>
-  </si>
-  <si>
-    <t>SCA</t>
-  </si>
-  <si>
-    <t>Golem</t>
-  </si>
-  <si>
-    <t>Chuck Carr</t>
-  </si>
-  <si>
-    <t>Espionage</t>
-  </si>
-  <si>
-    <t>FI</t>
-  </si>
-  <si>
-    <t>Choose an opponent and look at their hand. They discard 1 chosen card.</t>
-  </si>
-  <si>
-    <t>Evhan of the Kobold Legion</t>
-  </si>
-  <si>
-    <t>SWMM</t>
-  </si>
-  <si>
-    <t>Evhan</t>
-  </si>
-  <si>
-    <t>Command(Destroy a Kobold): Deal true damage equal to the destroyed Kobold's power to all units on it's previously occupied tile and all castles it was on the backlines of.</t>
-  </si>
-  <si>
-    <t>Evhan's Wall of Panic</t>
-  </si>
-  <si>
-    <t>SMA</t>
-  </si>
-  <si>
-    <t>Defenses</t>
-  </si>
-  <si>
-    <t>Trigger: Flip 2 coins. If either are tails, triggering unit moves backwards 1 tile.</t>
-  </si>
-  <si>
-    <t>Exhaustive Research</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>Discard a card, then draw 2 cards.</t>
-  </si>
-  <si>
-    <t>Factory Units</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>Clanker</t>
-  </si>
-  <si>
-    <t>Workers</t>
-  </si>
-  <si>
-    <t>Produce: One Metal</t>
-  </si>
-  <si>
-    <t>Farm</t>
-  </si>
-  <si>
-    <t>WI</t>
+    <t>John Kaboom</t>
+  </si>
+  <si>
+    <t>WWII</t>
+  </si>
+  <si>
+    <t>Kaboom</t>
   </si>
   <si>
     <t>Produce: One Food
@@ -371,704 +484,574 @@
 Cannot be built on your backlines.</t>
   </si>
   <si>
+    <t>Insect</t>
+  </si>
+  <si>
+    <t>Black Colony Guards</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Static: This unit's power is equal the number of your combatants on the field.</t>
+  </si>
+  <si>
+    <t>Army of Mandibles</t>
+  </si>
+  <si>
+    <t>Static: This unit's power is equal to half its numbers, rounded down.</t>
+  </si>
+  <si>
+    <t>Ants Insatiable</t>
+  </si>
+  <si>
+    <t>FFF</t>
+  </si>
+  <si>
     <t>Gnawing Valkyries</t>
   </si>
   <si>
+    <t>Mud-Spitters</t>
+  </si>
+  <si>
+    <t>SFF</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Static: Cannot be engaged by units on the occupied tile.</t>
+  </si>
+  <si>
+    <t>Rhyan, Loyal to the Mound</t>
+  </si>
+  <si>
+    <t>Rhyan</t>
+  </si>
+  <si>
+    <t>Taunting Dopes</t>
+  </si>
+  <si>
+    <t>Walls of Wind</t>
+  </si>
+  <si>
+    <t>Walls</t>
+  </si>
+  <si>
+    <t>SWFF</t>
+  </si>
+  <si>
+    <t>Deal 6 true damage to each unit on a chosen tile. Deal 4 true damage to each unit on each tile one orthoginal tile away  from the chosen tile.</t>
+  </si>
+  <si>
+    <t>Stash Mound</t>
+  </si>
+  <si>
+    <t>Range 2</t>
+  </si>
+  <si>
+    <t>Shaloom of the Shroom</t>
+  </si>
+  <si>
+    <t>Shaloom</t>
+  </si>
+  <si>
+    <t>Errica</t>
+  </si>
+  <si>
+    <t>Lioness Errica</t>
+  </si>
+  <si>
+    <t>Feline</t>
+  </si>
+  <si>
+    <t>Range 1</t>
+  </si>
+  <si>
+    <t>Dig Deeper</t>
+  </si>
+  <si>
+    <t>Clanker</t>
+  </si>
+  <si>
+    <t>MMM</t>
+  </si>
+  <si>
+    <t>Factory Units</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Workers</t>
+  </si>
+  <si>
+    <t>Produce: One Metal</t>
+  </si>
+  <si>
+    <t>Savannah Cheetahs</t>
+  </si>
+  <si>
+    <t>Static: The first time this unit advances, it advances 2 more times, then put 3 Time counters on this unit. This unit can't advance while it has Time counters on it.</t>
+  </si>
+  <si>
+    <t>Tin Can Clankers</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>Static: When one or more of your opponent's resources decay, produce one Metal.</t>
+  </si>
+  <si>
+    <t>Range 1
+Static: Has +1 Power and +1 Defense for each Mana in your Reserves.</t>
+  </si>
+  <si>
+    <t>King of the Pride</t>
+  </si>
+  <si>
+    <t>Static: Your Felines have +2Pow if they advanced this turn.
+End: If it's your turn, you may have up to 2 Felines advance.</t>
+  </si>
+  <si>
+    <t>Young Hunters</t>
+  </si>
+  <si>
+    <t>White Stalkers</t>
+  </si>
+  <si>
+    <t>Static: Enemy combatants within 1 tile of this unit don't advance during their owner's advance step.</t>
+  </si>
+  <si>
+    <t>Stone-Age Clankers</t>
+  </si>
+  <si>
+    <t>Dung-Beetle Scavengers</t>
+  </si>
+  <si>
+    <t>Scavengers</t>
+  </si>
+  <si>
+    <t>Enter: Put 3 Time counters on this unit.
+End(This unit has no time counters on it): For each unit, deal damage equal to their attack to any target, then deal 5 damage to each castle.</t>
+  </si>
+  <si>
+    <t>Repurposed Battering Ram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hidden
+Trigger: Flip this card face up. Deal 7 damage to each combatant in an othoganally adjacent tile. </t>
+  </si>
+  <si>
+    <t>Hidden
+Trigger: Flip this card face up. Deal 6 damage to each combatant within 2 tiles forward. Produce a Wood, then this unit falls.</t>
+  </si>
+  <si>
+    <t>Produce: One Wood
+Produce(Occupied tile has a Wood resource type):One Wood</t>
+  </si>
+  <si>
+    <t>SMA</t>
+  </si>
+  <si>
+    <t>Produce(You have no other units): Two Food</t>
+  </si>
+  <si>
+    <t>Enter: Put a Time counter on Stash Mound.
+Activate(Destroy Stash Mound, No time counters on Stash Mound): Produce 2 Food.</t>
+  </si>
+  <si>
+    <t>Obscured in Smog</t>
+  </si>
+  <si>
+    <t>A chosen unit gets -3Pow/-1Def until end of turn.</t>
+  </si>
+  <si>
+    <t>Factory Defense Sentries</t>
+  </si>
+  <si>
+    <t>Range 1
+This unit cannot advance into a tile on an opponent's field.</t>
+  </si>
+  <si>
+    <t>Rarity</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>Uncommon</t>
+  </si>
+  <si>
+    <t>Secret Rare</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>Pre-Battle: Roll a d4. Your castle loses that much fortitude and you produce that much Food.</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>Card</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Precon 1</t>
+  </si>
+  <si>
+    <t>Precon 2</t>
+  </si>
+  <si>
+    <t>Defenders</t>
+  </si>
+  <si>
+    <t>Dung Beetle Scavengers</t>
+  </si>
+  <si>
+    <t>Ants insatiable</t>
+  </si>
+  <si>
+    <t>Static: When this unit deals undefended damage, put that many +1Pow counters on it.</t>
+  </si>
+  <si>
+    <t>Command(Destroy a Kobold): Deal true damage equal to the destroyed Kobold's power to all units on it's previously occupied tile and all castles it was on the backlines of.</t>
+  </si>
+  <si>
+    <t>SWFC</t>
+  </si>
+  <si>
+    <t>Static: This unit can advance while engaged.
+Post-Advance: Any other units on the tile this unit advanced from are moved to the occupied tile.</t>
+  </si>
+  <si>
+    <t>Activate(Sacrifice an Army): This unit gets +1 Power</t>
+  </si>
+  <si>
+    <t>Static: Your other goblin units have +1 power.</t>
+  </si>
+  <si>
+    <t>Activate(?): Produce a resource of any basic resource type.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smoke Spirit Atascha </t>
+  </si>
+  <si>
+    <t>WW</t>
+  </si>
+  <si>
+    <t>Atascha</t>
+  </si>
+  <si>
+    <t>Strafe
+Static: Other units on this tile have -2 Power and -2 Defense</t>
+  </si>
+  <si>
+    <t>FA</t>
+  </si>
+  <si>
+    <t>Produce: One mana if there are no combatants on this tile. Otherwise, Two Mana</t>
+  </si>
+  <si>
+    <t>Freaky Fungi</t>
+  </si>
+  <si>
+    <t>The Crooked One</t>
+  </si>
+  <si>
+    <t>WIC</t>
+  </si>
+  <si>
+    <t>Crooked One</t>
+  </si>
+  <si>
+    <t>House-eaters</t>
+  </si>
+  <si>
+    <t>Static: If the occupied tile contains a Building, this unit gains numbers equal to the Building's defense, then building falls.</t>
+  </si>
+  <si>
+    <t>Brainwash</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>Choose a combatant. Gain control of that combatant and change it's direction.</t>
+  </si>
+  <si>
+    <t>Scattershot Sentry</t>
+  </si>
+  <si>
+    <t>Pre-Combat: Deal 5 damage to each enemy unit one tile forward. If you do, deal 3 damage to each enemy unit within one tile horizontally 2 tiles forward.</t>
+  </si>
+  <si>
+    <t>Feisty Grapplers</t>
+  </si>
+  <si>
+    <t>Range 1
+Post-Battle: This unit moves to a tile occupied by a unit it battled this turn.</t>
+  </si>
+  <si>
+    <t>Skittish Kobolds</t>
+  </si>
+  <si>
+    <t>Strafe (This unit can advance horizontally)
+Static: Your other Felines have Strafe.</t>
+  </si>
+  <si>
+    <t>Bombardier Beetles</t>
+  </si>
+  <si>
+    <t>Bombers</t>
+  </si>
+  <si>
+    <t>Fungus</t>
+  </si>
+  <si>
+    <t>Trigger: This unit moves to a random orthoginal tile.</t>
+  </si>
+  <si>
+    <t>Command(F): This unit deals 5 damage to a chosen enemy unit, then deals 2 damage to each other unit within 1 orthoginal tile of the chosen unit.</t>
+  </si>
+  <si>
+    <t>Queen of the Hive</t>
+  </si>
+  <si>
+    <t>Hive Queen</t>
+  </si>
+  <si>
+    <t>Static: Other Insects you own have +X Power, where X is the number of Insects you control.
+Activate(F): Create a 10kNum/1Power/2Def Insect army token on the occupied tile.</t>
+  </si>
+  <si>
+    <t>Bouncer Clankers</t>
+  </si>
+  <si>
+    <t>Post-Battle: Any units dealt damage by Bouncer Clankers this combat move back 1 tile.</t>
+  </si>
+  <si>
+    <t>Enter: For each enemy unit, that unit's controller chooses to deal 10 damage to that unit or deal 5 damage to their castle.</t>
+  </si>
+  <si>
+    <t>Overflowing Mound</t>
+  </si>
+  <si>
+    <t>Assembly Lines</t>
+  </si>
+  <si>
+    <t>WIM</t>
+  </si>
+  <si>
+    <t>Start: Create a 3kNum/3Power/3Def Insect army summon on this tile with "Static: This creature always advances when able."</t>
+  </si>
+  <si>
+    <t>Activate(M): Create a 1kNum/5Power/5Def Clanker Army summon on any horizontally adjacent tile. You may use this ability any number of times per turn.</t>
+  </si>
+  <si>
+    <t>Smog Churners</t>
+  </si>
+  <si>
+    <t>IM</t>
+  </si>
+  <si>
+    <t>Produce: 1 Metal if occupied tile is a resource tile.
+Pre-Battle: Enemy combatants on this tile get -1 Power until end of combat.</t>
+  </si>
+  <si>
+    <t>Produce: One Metal
+Command(M): Each of your Clanker units gain +1Pow and +1Def until end of turn.</t>
+  </si>
+  <si>
+    <t>Draconic Horn</t>
+  </si>
+  <si>
+    <t>SIC</t>
+  </si>
+  <si>
+    <t>Start: Excavate for a Dragon card. Put that card on your frontlines.
+Cannot be built on your backlines.</t>
+  </si>
+  <si>
+    <t>Lord Kobalte</t>
+  </si>
+  <si>
+    <t>Dragon</t>
+  </si>
+  <si>
+    <t>Kobalte</t>
+  </si>
+  <si>
+    <t>Filter-Bots</t>
+  </si>
+  <si>
+    <t>MM</t>
+  </si>
+  <si>
+    <t>End: Look at the top three cards of your deck. Put up to two into your discard pile.</t>
+  </si>
+  <si>
+    <t>Static: Cannot be chosen by cards.
+Static: You may pay SWIF rather than pay the cost for Dragon cards.</t>
+  </si>
+  <si>
+    <t>SWIFMCA</t>
+  </si>
+  <si>
+    <t>SIF</t>
+  </si>
+  <si>
+    <t>IF</t>
+  </si>
+  <si>
     <t>WIF</t>
   </si>
   <si>
-    <t>Static: Cannot be engaged by units on the occupied tile.</t>
-  </si>
-  <si>
-    <t>Goblin Chief Bucas</t>
-  </si>
-  <si>
-    <t>SFM</t>
-  </si>
-  <si>
-    <t>Bucas</t>
-  </si>
-  <si>
-    <t>Static: Once per turn, when one of your Goblins advances, you may have it advance again.
-Static: The first time one of your Goblins would take damage each turn, it instead moves one lane to the right or left, chosen at random.</t>
-  </si>
-  <si>
-    <t>Goblin Giants</t>
-  </si>
-  <si>
-    <t>SIF</t>
-  </si>
-  <si>
-    <t>Goblin Prospectors</t>
-  </si>
-  <si>
-    <t>Peasants</t>
-  </si>
-  <si>
-    <t>Static: The tile occupied by this card is a Stone Resource tile.</t>
-  </si>
-  <si>
-    <t>Goblin Vanguard</t>
-  </si>
-  <si>
-    <t>Static: Your other goblin units have +1 power.</t>
-  </si>
-  <si>
-    <t>Harbinger of Death</t>
-  </si>
-  <si>
-    <t>ICCAA</t>
-  </si>
-  <si>
-    <t>God</t>
-  </si>
-  <si>
-    <t>Harbinger</t>
-  </si>
-  <si>
-    <t>End: Each other unit within one tile of this unit loses 5kNum/5Ftt.</t>
-  </si>
-  <si>
-    <t>Heroic Battalion</t>
-  </si>
-  <si>
-    <t>Righteous</t>
-  </si>
-  <si>
-    <t>SFFF</t>
-  </si>
-  <si>
-    <t>Static: If this unit is engaging a Ruthless unit, it has +1 Power.</t>
-  </si>
-  <si>
-    <t>John Kaboom</t>
-  </si>
-  <si>
-    <t>WWII</t>
-  </si>
-  <si>
-    <t>Kaboom</t>
+    <t>IFM</t>
+  </si>
+  <si>
+    <t>IFFA</t>
+  </si>
+  <si>
+    <t>IIF</t>
+  </si>
+  <si>
+    <t>SWIF</t>
+  </si>
+  <si>
+    <t>Draconic Mages</t>
+  </si>
+  <si>
+    <t>Produce: 1 Mana if controlled tile is a resource tile.</t>
+  </si>
+  <si>
+    <t>Produce: One Food
+Post-Battle: If this unit felled a unit this turn, it gains +1Pow and +1Def.</t>
+  </si>
+  <si>
+    <t>Produce: One resource of a type of occupied tile.</t>
+  </si>
+  <si>
+    <t>Static: You can use Food as though it were Mana to pay for cards and card effects.</t>
+  </si>
+  <si>
+    <t>Fungamblers</t>
+  </si>
+  <si>
+    <t>Rogues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start: Roll 2d6. Choose one result. Your castle gains fortitude equal to the chosen result and each opponent's castle loses fortitude equal to the other result. </t>
+  </si>
+  <si>
+    <t>Repliclankers</t>
+  </si>
+  <si>
+    <t>Repliclankers enters as a copy of a chosen combatant, but as Clanker Warriors with 3k numbers.</t>
+  </si>
+  <si>
+    <t>Zh'Aedinn's Factory</t>
+  </si>
+  <si>
+    <t>Fun Gus</t>
+  </si>
+  <si>
+    <t>Gus</t>
+  </si>
+  <si>
+    <t>Static: Whenever a non-Gus card makes you roll a dice, you may roll a dice. 
+Static: Whenever you roll a 2, produce one Mana</t>
+  </si>
+  <si>
+    <t>Mycelium Rootwalkers</t>
+  </si>
+  <si>
+    <t>WFA</t>
+  </si>
+  <si>
+    <t>Draconian Archers</t>
+  </si>
+  <si>
+    <t>Draconian Warriors</t>
+  </si>
+  <si>
+    <t>Art Status</t>
+  </si>
+  <si>
+    <t>Artist</t>
+  </si>
+  <si>
+    <t>Impenetrable Hive</t>
+  </si>
+  <si>
+    <t>Produce: 1 Food
+Static: Other units on this tile have +2 Defense</t>
+  </si>
+  <si>
+    <t>Ghost Slugs</t>
+  </si>
+  <si>
+    <t>Phantom</t>
+  </si>
+  <si>
+    <t>Shouting Ralliers</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>Enter: Until the start of your next turn, Kobolds you control get +2 Power.</t>
+  </si>
+  <si>
+    <t>Ethereal (Cannot be damaged through combat)
+Static: If the occupied tile has no Slime counters, put a Slime counter on it. Combatants on tiles with slime counters on them don't advance during their owner's turn.</t>
+  </si>
+  <si>
+    <t>Fight 'til the End</t>
+  </si>
+  <si>
+    <t>Rousing Speech</t>
+  </si>
+  <si>
+    <t>Natakan Horse</t>
+  </si>
+  <si>
+    <t>WWI</t>
+  </si>
+  <si>
+    <t>You may play combatants on the occupied tile.</t>
+  </si>
+  <si>
+    <t>Until end of turn, when a combatant you control dies, combatants you control get +2 Power and +1 Defense until end of turn.</t>
+  </si>
+  <si>
+    <t>Until end of turn, combatants you control get +1 Power and +3 Numbers</t>
+  </si>
+  <si>
+    <t>Activate(W): Create a Structure with 1Ft/0Def named Trebuchet on this tile with "Command: One combatant on this tile moves up to 2 tiles forward."</t>
+  </si>
+  <si>
+    <t>Scaled Skirmishers</t>
+  </si>
+  <si>
+    <t>Ophiocordyceps</t>
+  </si>
+  <si>
+    <t>FFI</t>
+  </si>
+  <si>
+    <t>Enter: Return an Insect combatant from your discard to this tile. If either this structure or the combatant leaves the field, the other falls.</t>
   </si>
   <si>
     <t>Post-Battle: Deal 6 damage to each other unit within 1 orthoginal tile and each unit with a Bomb counter on it. Remove all Bomb counters from all units.
 Activate: Put a Bomb counter on a unit on the occupied tile.</t>
   </si>
   <si>
-    <t>King of the Pride</t>
-  </si>
-  <si>
-    <t>IIF</t>
-  </si>
-  <si>
-    <t>Feline</t>
-  </si>
-  <si>
-    <t>Static: Your Felines have +2Pow if they advanced this turn.
-End: If it's your turn, you may have up to 2 Felines advance.</t>
-  </si>
-  <si>
-    <t>Kobold Contraptionists</t>
-  </si>
-  <si>
-    <t>Activate(W): Create a Structure with 1Ft/0Def named Trebuchet on this tile with "Command: One combatant on this tile moves up to 2 tiles forward."</t>
-  </si>
-  <si>
-    <t>Chuck Carr, Evan Hirt</t>
-  </si>
-  <si>
-    <t>Lioness Errica</t>
-  </si>
-  <si>
-    <t>IFFA</t>
-  </si>
-  <si>
-    <t>Errica</t>
-  </si>
-  <si>
-    <t>Strafe (This unit can advance horizontally)
-Static: Your other Felines have Strafe.</t>
-  </si>
-  <si>
-    <t>Josh Carr</t>
-  </si>
-  <si>
-    <t>Loot the Bodies</t>
-  </si>
-  <si>
-    <t>Can only be played after the combat step.
-If any of your units felled a combatant this turn, draw two cards.</t>
-  </si>
-  <si>
-    <t>Mages of Palador</t>
-  </si>
-  <si>
-    <t>Range 1
-Static: Has +1 Power and +1 Defense for each Mana in your Reserves.</t>
-  </si>
-  <si>
-    <t>Mana Well</t>
-  </si>
-  <si>
-    <t>SW</t>
-  </si>
-  <si>
-    <t>Produce: One mana if there are no combatants on this tile. Otherwise, Two Mana</t>
-  </si>
-  <si>
-    <t>Mud-Spitters</t>
-  </si>
-  <si>
-    <t>SFF</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Range 2</t>
-  </si>
-  <si>
-    <t>Ryan Chalmers</t>
-  </si>
-  <si>
-    <t>Obscured in Smog</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>A chosen unit gets -3Pow/-1Def until end of turn.</t>
-  </si>
-  <si>
-    <t>Palador Elites</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Normal </t>
-  </si>
-  <si>
-    <t>IFM</t>
-  </si>
-  <si>
-    <t>Palador Frontliners</t>
-  </si>
-  <si>
-    <t>Static: If this unit is behind another friendly combatant, this unit advances.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palador Knights </t>
-  </si>
-  <si>
-    <t>IF</t>
-  </si>
-  <si>
-    <t>Palador Library</t>
-  </si>
-  <si>
-    <t>WII</t>
-  </si>
-  <si>
-    <t>Activate: Draw 1 card.</t>
-  </si>
-  <si>
-    <t>Palador Mage Guild</t>
-  </si>
-  <si>
-    <t>SWFC</t>
-  </si>
-  <si>
-    <t>Produce: One Mana
-Static: Your other Mage units have +1 Power and +1 Defense.
-Activate: One of your mage units gains 2k numbers.</t>
-  </si>
-  <si>
-    <t>Pillars of Flame</t>
-  </si>
-  <si>
-    <t>WAA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Choose a lane. Deal 8 damage to each unit in that lane. </t>
-  </si>
-  <si>
-    <t>Ramshackle Cavalry</t>
-  </si>
-  <si>
-    <t>Activate: If unengaged, this unit advances.</t>
-  </si>
-  <si>
-    <t>Reckless Arsonists</t>
-  </si>
-  <si>
-    <t>Static: Tiles within 1 orthoginal tile of this card have no resource type.</t>
-  </si>
-  <si>
-    <t>Recyclists of the Muck</t>
-  </si>
-  <si>
-    <t>Activate(?): Produce a resource of any basic resource type.</t>
-  </si>
-  <si>
-    <t>Repurposed Battering Ram</t>
-  </si>
-  <si>
-    <t>Trap</t>
-  </si>
-  <si>
-    <t>Hidden
-Trigger: Flip this card face up. Deal 6 damage to each combatant within 2 tiles forward. Produce a Wood, then this unit falls.</t>
-  </si>
-  <si>
-    <t>Retreat</t>
-  </si>
-  <si>
-    <t>All of your combatants move back 1 tile.</t>
-  </si>
-  <si>
-    <t>Rhyan, Loyal to the Mound</t>
-  </si>
-  <si>
-    <t>SWFF</t>
-  </si>
-  <si>
-    <t>Rhyan</t>
-  </si>
-  <si>
-    <t>Command(F): Create a Insect Army summon with 5kNum/XPow/2Def and "This unit's power is equal to the number of your Insects on the field" on a horizontally adjacent tile.</t>
-  </si>
-  <si>
-    <t>Ritual of Annihilation</t>
-  </si>
-  <si>
-    <t>CFAAAA</t>
-  </si>
-  <si>
-    <t>Ritual</t>
-  </si>
-  <si>
-    <t>Enter: Put 3 Time counters on this unit.
-End(This unit has no time counters on it): For each unit, deal damage equal to their attack to any target, then deal 5 damage to each castle.</t>
-  </si>
-  <si>
-    <t>Rudimentry Archers</t>
-  </si>
-  <si>
-    <t>Range 1</t>
-  </si>
-  <si>
-    <t>Savannah Cheetahs</t>
-  </si>
-  <si>
-    <t>Static: The first time this unit advances, it advances 2 more times, then put 3 Time counters on this unit. This unit can't advance while it has Time counters on it.</t>
-  </si>
-  <si>
-    <t>Sawmill</t>
-  </si>
-  <si>
-    <t>Produce: One Wood
-Produce(Occupied tile has a Wood resource type):One Wood</t>
-  </si>
-  <si>
-    <t>Scavenging Kobolds</t>
-  </si>
-  <si>
-    <t>Produce: One resource of a type of occupied tile.</t>
-  </si>
-  <si>
-    <t>Sculptor Konor</t>
-  </si>
-  <si>
-    <t>SSC</t>
-  </si>
-  <si>
-    <t>Konor</t>
-  </si>
-  <si>
-    <t>Activate: Create a Golem Army summon with 1kNum/3Pow/7Def on this tile.</t>
-  </si>
-  <si>
-    <t>Sensitive Spike Shooter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hidden
-Trigger: Flip this card face up. Deal 7 damage to each combatant in an othoganally adjacent tile. </t>
-  </si>
-  <si>
-    <t>Shaloom of the Shroom</t>
-  </si>
-  <si>
-    <t>FA</t>
-  </si>
-  <si>
-    <t>Fungus</t>
-  </si>
-  <si>
-    <t>Shaloom</t>
-  </si>
-  <si>
-    <t>Pre-Battle: Roll a d4. Your castle loses that much fortitude and you produce that much Food.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calum </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smoke Spirit Atascha </t>
-  </si>
-  <si>
-    <t>WW</t>
-  </si>
-  <si>
-    <t>Elemental</t>
-  </si>
-  <si>
-    <t>Atascha</t>
-  </si>
-  <si>
-    <t>Strafe
-Static: Other units on this tile have -2 Power and -2 Defense</t>
-  </si>
-  <si>
-    <t>Stash Mound</t>
-  </si>
-  <si>
-    <t>Enter: Put a Time counter on Stash Mound.
-Activate(Destroy Stash Mound, No time counters on Stash Mound): Produce 2 Food.</t>
-  </si>
-  <si>
-    <t>Stone Barricades</t>
-  </si>
-  <si>
-    <t>SS</t>
-  </si>
-  <si>
-    <t>Static: Enemy combatants cannot advance forward while on the occupied tile.</t>
-  </si>
-  <si>
-    <t>Stone Legion</t>
-  </si>
-  <si>
-    <t>Stone-Age Clankers</t>
-  </si>
-  <si>
-    <t>Tactical Roll</t>
-  </si>
-  <si>
-    <t>Move one of your combatants one tile horizontally.</t>
-  </si>
-  <si>
-    <t>Taunting Dopes</t>
-  </si>
-  <si>
-    <t>Scouts</t>
-  </si>
-  <si>
-    <t>Static: When this unit advances, combatants within one orthogonal tile move to the occupied tile.</t>
-  </si>
-  <si>
-    <t>Teleportation</t>
-  </si>
-  <si>
-    <t>If this command targets a structure, it costs an additional A.
-One chosen unit moves up to 2 tiles orthoganally.</t>
-  </si>
-  <si>
-    <t>Tin Can Clankers</t>
-  </si>
-  <si>
-    <t>SM</t>
-  </si>
-  <si>
-    <t>Static: When one or more of your opponent's resources decay, produce one Metal.</t>
-  </si>
-  <si>
-    <t>Walls of Wind</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Walls</t>
-  </si>
-  <si>
-    <t>Static: This unit can advance while engaged.
-Post-Advance: Any other units on the tile this unit advanced from are moved to the occupied tile.</t>
-  </si>
-  <si>
-    <t>White Stalkers</t>
-  </si>
-  <si>
-    <t>Static: Enemy combatants within 1 tile of this unit don't advance during their owner's advance step.</t>
-  </si>
-  <si>
-    <t>Young Hunters</t>
-  </si>
-  <si>
-    <t>Produce: One Food
-Post-Battle: If this unit felled a unit this turn, it gains +1Pow and +1Def.</t>
-  </si>
-  <si>
-    <t>Zh'Aedinn, in Billowing Smog</t>
-  </si>
-  <si>
-    <t>MMM</t>
-  </si>
-  <si>
-    <t>Zh'Aedinn</t>
-  </si>
-  <si>
-    <t>Produce: One Metal
-Command(M): Each of your Clanker units gain +1Pow and +1Def until end of turn.</t>
-  </si>
-  <si>
-    <t>Lore</t>
-  </si>
-  <si>
-    <t>Freaky Fungi</t>
-  </si>
-  <si>
-    <t>Static: You can use Food as though it were Mana to pay for cards and card effects.</t>
-  </si>
-  <si>
-    <t>The Crooked One</t>
-  </si>
-  <si>
-    <t>WIC</t>
-  </si>
-  <si>
-    <t>Crooked One</t>
-  </si>
-  <si>
-    <t>Enter: For each enemy unit, that unit's controller chooses to deal 10 damage to that unit or deal 5 damage to their castle.</t>
-  </si>
-  <si>
-    <t>House-eaters</t>
-  </si>
-  <si>
-    <t>Static: If the occupied tile contains a Building, this unit gains numbers equal to the Building's defense, then building falls.</t>
-  </si>
-  <si>
-    <t>Brainwash</t>
-  </si>
-  <si>
-    <t>CA</t>
-  </si>
-  <si>
-    <t>Choose a combatant. Gain control of that combatant and change it's direction.</t>
-  </si>
-  <si>
-    <t>Scattershot Sentry</t>
-  </si>
-  <si>
-    <t>Pre-Combat: Deal 5 damage to each enemy unit one tile forward. If you do, deal 3 damage to each enemy unit within one tile horizontally 2 tiles forward.</t>
-  </si>
-  <si>
-    <t>Feisty Grapplers</t>
-  </si>
-  <si>
-    <t>Range 1
-Post-Battle: This unit moves to a tile occupied by a unit it battled this turn.</t>
-  </si>
-  <si>
-    <t>Skittish Kobolds</t>
-  </si>
-  <si>
-    <t>Trigger: This unit moves to a random orthoginal tile.</t>
-  </si>
-  <si>
-    <t>Bombardier Beetles</t>
-  </si>
-  <si>
-    <t>Bombers</t>
-  </si>
-  <si>
-    <t>Command(F): This unit deals 5 damage to a chosen enemy unit, then deals 2 damage to each other unit within 1 orthoginal tile of the chosen unit.</t>
-  </si>
-  <si>
-    <t>Queen of the Hive</t>
-  </si>
-  <si>
-    <t>Hive Queen</t>
-  </si>
-  <si>
-    <t>Static: Other Insects you own have +X Power, where X is the number of Insects you control.
-Activate(F): Create a 10kNum/1Power/2Def Insect army token on the occupied tile.</t>
-  </si>
-  <si>
-    <t>Bouncer Clankers</t>
-  </si>
-  <si>
-    <t>Defenders</t>
-  </si>
-  <si>
-    <t>Post-Battle: Any units dealt damage by Bouncer Clankers this combat move back 1 tile.</t>
-  </si>
-  <si>
-    <t>Overflowing Mound</t>
-  </si>
-  <si>
-    <t>SWIF</t>
-  </si>
-  <si>
-    <t>Start: Create a 3kNum/3Power/3Def Insect army summon on this tile with "Static: This creature always advances when able."</t>
-  </si>
-  <si>
-    <t>Assembly Lines</t>
-  </si>
-  <si>
-    <t>WIM</t>
-  </si>
-  <si>
-    <t>Activate(M): Create a 1kNum/5Power/5Def Clanker Army summon on any horizontally adjacent tile. You may use this ability any number of times per turn.</t>
-  </si>
-  <si>
-    <t>Smog Churners</t>
-  </si>
-  <si>
-    <t>IM</t>
-  </si>
-  <si>
-    <t>Produce: 1 Metal if occupied tile is a resource tile.
-Pre-Battle: Enemy combatants on this tile get -1 Power until end of combat.</t>
-  </si>
-  <si>
-    <t>Draconic Horn</t>
-  </si>
-  <si>
-    <t>SIC</t>
-  </si>
-  <si>
-    <t>Start: Excavate for a Dragon card. Put that card on your frontlines.
-Cannot be built on your backlines.</t>
-  </si>
-  <si>
-    <t>Lord Kobalte</t>
-  </si>
-  <si>
-    <t>SWIFMCA</t>
-  </si>
-  <si>
-    <t>Dragon</t>
-  </si>
-  <si>
-    <t>Kobalte</t>
-  </si>
-  <si>
-    <t>Static: Cannot be chosen by cards.
-Static: You may pay SWIF rather than pay the cost for Dragon cards.</t>
-  </si>
-  <si>
-    <t>Filter-Bots</t>
-  </si>
-  <si>
-    <t>End: Look at the top three cards of your deck. Put up to two into your discard pile.</t>
-  </si>
-  <si>
-    <t>Draconic Mages</t>
-  </si>
-  <si>
-    <t>Produce: 1 Mana if controlled tile is a resource tile.</t>
-  </si>
-  <si>
-    <t>Fungamblers</t>
-  </si>
-  <si>
-    <t>Rogues</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start: Roll 2d6. Choose one result. Your castle gains fortitude equal to the chosen result and each opponent's castle loses fortitude equal to the other result. </t>
-  </si>
-  <si>
-    <t>Repliclankers</t>
-  </si>
-  <si>
-    <t>MM</t>
-  </si>
-  <si>
-    <t>Repliclankers enters as a copy of a chosen combatant, but as Clanker Warriors with 3k numbers.</t>
-  </si>
-  <si>
-    <t>Zh'Aedinn's Factory</t>
-  </si>
-  <si>
-    <t>Fun Gus</t>
-  </si>
-  <si>
-    <t>Gus</t>
-  </si>
-  <si>
-    <t>Static: Whenever a non-Gus card makes you roll a dice, you may roll a dice. 
-Static: Whenever you roll a 2, produce one Mana</t>
-  </si>
-  <si>
-    <t>Mycelium Rootwalkers</t>
-  </si>
-  <si>
-    <t>WFA</t>
-  </si>
-  <si>
-    <t>Draconian Archers</t>
-  </si>
-  <si>
-    <t>Draconian Warriors</t>
-  </si>
-  <si>
-    <t>Impenetrable Hive</t>
-  </si>
-  <si>
-    <t>Produce: 1 Food
-Static: Other units on this tile have +2 Defense</t>
-  </si>
-  <si>
-    <t>Ghost Slugs</t>
-  </si>
-  <si>
-    <t>Phantom</t>
-  </si>
-  <si>
-    <t>Ethereal (Cannot be damaged through combat)
-Static: If the occupied tile has no Slime counters, put a Slime counter on it. Combatants on tiles with slime counters on them don't advance during their owner's turn.</t>
-  </si>
-  <si>
-    <t>Shouting Ralliers</t>
-  </si>
-  <si>
-    <t>SI</t>
-  </si>
-  <si>
-    <t>Enter: Until the start of your next turn, Kobolds you control get +2 Power.</t>
-  </si>
-  <si>
-    <t>Fight 'til the End</t>
-  </si>
-  <si>
-    <t>Until end of turn, when a combatant you control dies, combatants you control get +2 Power and +1 Defense until end of turn.</t>
-  </si>
-  <si>
-    <t>Rousing Speech</t>
-  </si>
-  <si>
-    <t>Until end of turn, combatants you control get +1 Power and +3 Numbers</t>
-  </si>
-  <si>
-    <t>Natakan Horse</t>
-  </si>
-  <si>
-    <t>WWI</t>
-  </si>
-  <si>
-    <t>You may play combatants on the occupied tile.</t>
-  </si>
-  <si>
-    <t>Scaled Skirmishers</t>
-  </si>
-  <si>
-    <t>Ophiocordyceps</t>
-  </si>
-  <si>
-    <t>FFI</t>
-  </si>
-  <si>
-    <t>Enter: Return an Insect combatant from your discard to this tile. If either this structure or the combatant leaves the field, the other falls.</t>
-  </si>
-  <si>
     <t>Swarming Locusts</t>
   </si>
   <si>
@@ -1145,10 +1128,13 @@
     <t>WIA</t>
   </si>
   <si>
+    <t>Static: Enemy combatants have no static abililties.</t>
+  </si>
+  <si>
     <t>Leviticus</t>
   </si>
   <si>
-    <t>Static: Enemy combatants have no static abililties.</t>
+    <t>Josh Carr</t>
   </si>
   <si>
     <t>Transmutation Mages</t>
@@ -1180,6 +1166,15 @@
   </si>
   <si>
     <t>Outpost</t>
+  </si>
+  <si>
+    <t>Chuck Carr</t>
+  </si>
+  <si>
+    <t>Chuck Carr, Evan Hirt</t>
+  </si>
+  <si>
+    <t>Pillars of Flame</t>
   </si>
   <si>
     <t>Harbinger of Famine</t>
@@ -1254,48 +1249,51 @@
     <t>Evhan, Strategist</t>
   </si>
   <si>
+    <t>SWMM</t>
+  </si>
+  <si>
+    <t>Static: Kobolds have +X Power, where X is equal to the combined power of other Kobolds diagonally aligned with them.</t>
+  </si>
+  <si>
+    <t>Crazed Mechanics</t>
+  </si>
+  <si>
+    <t>Activate: A chosen structure on the occupied tile gains 2 Fortitude.</t>
+  </si>
+  <si>
+    <t>Lore</t>
+  </si>
+  <si>
+    <t>Errica used a crown to communicate with cultists to increase her power and influence. Baoust learned of her collusion and turned her into a human as punishment for turning against her race.</t>
+  </si>
+  <si>
+    <t>Collude</t>
+  </si>
+  <si>
     <t>SIFM</t>
   </si>
   <si>
-    <t>Static: Kobolds have +X Power, where X is equal to the combined power of other Kobolds diagonally aligned with them.</t>
-  </si>
-  <si>
-    <t>Crazed Mechanics</t>
-  </si>
-  <si>
-    <t>SWM</t>
-  </si>
-  <si>
-    <t>Activate: A chosen structure on the occupied tile gains 2 Fortitude.</t>
-  </si>
-  <si>
-    <t>Errica used a crown to communicate with cultists to increase her power and influence. Baoust learned of her collusion and turned her into a human as punishment for turning against her race.</t>
-  </si>
-  <si>
-    <t>Collude</t>
-  </si>
-  <si>
     <t>Each player chooses Knowledge or Power. For each Power vote, you and that player produce one resource of any resource type. For each knowledge vote, you and that player draw a card.</t>
   </si>
   <si>
     <t>Cost of Battle</t>
   </si>
   <si>
+    <t>Rhyan, Assimilated</t>
+  </si>
+  <si>
+    <t>FFC</t>
+  </si>
+  <si>
+    <t>Post-Combat: For each combatant you own that felled a unit this turn, draw a card. For each combatant you own that was felled in combat this turn, produce one Food.</t>
+  </si>
+  <si>
+    <t>Rhyan rejected his flesh and replaced it with chitin, encouraging centipedes to crawl through his ears and alter his pituitary glands such that he would grow more insect-like.</t>
+  </si>
+  <si>
     <t>For each combatant that engaged in combat this turn, it's owner chooses a different resource they own. Each chosen resource decays.</t>
   </si>
   <si>
-    <t>Rhyan, Assimilated</t>
-  </si>
-  <si>
-    <t>FFC</t>
-  </si>
-  <si>
-    <t>Post-Combat: For each combatant you own that felled a unit this turn, draw a card. For each combatant you own that was felled in combat this turn, produce one Food.</t>
-  </si>
-  <si>
-    <t>Rhyan rejected his flesh and replaced it with chitin, encouraging centipedes to crawl through his ears and alter his pituitary glands such that he would grow more insect-like.</t>
-  </si>
-  <si>
     <t>Spire of Innovation</t>
   </si>
   <si>
@@ -1305,37 +1303,24 @@
     <t>Spore Scrappers</t>
   </si>
   <si>
+    <t xml:space="preserve">Calum </t>
+  </si>
+  <si>
+    <t>Ryan Chalmers</t>
+  </si>
+  <si>
+    <t>Zh'Aedinn, in Billowing Smog</t>
+  </si>
+  <si>
+    <t>Zh'Aedinn</t>
+  </si>
+  <si>
     <t>Psychedelic Sam</t>
   </si>
   <si>
     <t>Sam</t>
   </si>
   <si>
-    <t>Factory Defense Sentries</t>
-  </si>
-  <si>
-    <t>Range 1
-This unit cannot advance into a tile on an opponent's field.</t>
-  </si>
-  <si>
-    <t>Precon 1</t>
-  </si>
-  <si>
-    <t>Precon 2</t>
-  </si>
-  <si>
-    <t>Card</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Dung Beetle Scavengers</t>
-  </si>
-  <si>
-    <t>Ants insatiable</t>
-  </si>
-  <si>
     <t>Post-Produce: Two random basic resources decay. If they do, produce one Metal.</t>
   </si>
   <si>
@@ -1357,9 +1342,6 @@
     <t>Kathryn Flesher</t>
   </si>
   <si>
-    <t>Static: The first time a Feline would advance, it advances twice.</t>
-  </si>
-  <si>
     <t>Striped Stalwarts</t>
   </si>
   <si>
@@ -1423,17 +1405,32 @@
     <t>James Patterson, Chuck Carr, Evan Hirt</t>
   </si>
   <si>
-    <t>Mt. Yl'lazzha</t>
+    <t>Repeat the Cycle</t>
+  </si>
+  <si>
+    <t>Immediate</t>
+  </si>
+  <si>
+    <t>Return up to two chosen cards from your discard to your hand.</t>
+  </si>
+  <si>
+    <t>Mt. Ylaizzha</t>
   </si>
   <si>
     <t>SSS</t>
   </si>
   <si>
-    <t xml:space="preserve">Produce: Two of any combination of Stone, Crystal, and/or Metal.
-</t>
-  </si>
-  <si>
-    <t>Elijah Carr</t>
+    <t>Produce: Two of either Stone, Crystal, or Metal.
+Post-Produce: You may discard a card. If you do, draw two cards.</t>
+  </si>
+  <si>
+    <t>Produce a resource of any type.</t>
+  </si>
+  <si>
+    <t>Activate: A chosen Feline unit advances. Usable once per game.</t>
+  </si>
+  <si>
+    <t>Activate(FF): Create a Insect Army summon with 5kNum/XPow/0Def and "This unit's power is equal to the number of your Insects on the field" on a horizontally adjacent tile.</t>
   </si>
 </sst>
 </file>
@@ -1503,7 +1500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7030A0"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1520,7 +1517,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1540,11 +1537,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1560,10 +1556,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1892,7 +1884,7 @@
     <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1907,66 +1899,66 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="K1" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>11</v>
+        <v>204</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>13</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>14</v>
+        <v>136</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>137</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="L2" t="s">
-        <v>20</v>
+        <v>206</v>
       </c>
       <c r="M2" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="P2">
         <f>COUNTIF(L:L, "Common")</f>
@@ -1975,28 +1967,28 @@
     </row>
     <row r="3" spans="1:16" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="F3">
         <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="H3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I3">
         <v>6</v>
@@ -2005,10 +1997,10 @@
         <v>3</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>28</v>
+        <v>218</v>
       </c>
       <c r="L3" t="s">
-        <v>29</v>
+        <v>208</v>
       </c>
       <c r="P3">
         <f>COUNTIF(L:L, "Uncommon")</f>
@@ -2017,31 +2009,31 @@
     </row>
     <row r="4" spans="1:16" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>129</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="F4">
         <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="J4">
         <v>9</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>34</v>
+        <v>135</v>
       </c>
       <c r="L4" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
       <c r="P4">
         <f>COUNTIF(L:L, "Rare")</f>
@@ -2050,25 +2042,25 @@
     </row>
     <row r="5" spans="1:16" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="F5">
         <v>5</v>
       </c>
       <c r="G5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H5" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -2077,10 +2069,10 @@
         <v>6</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="L5" t="s">
-        <v>29</v>
+        <v>208</v>
       </c>
       <c r="P5">
         <f>COUNTIF(L:L, "Secret Rare")</f>
@@ -2089,130 +2081,130 @@
     </row>
     <row r="6" spans="1:16" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>10</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="H6" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I6" t="s">
-        <v>43</v>
+        <v>145</v>
       </c>
       <c r="J6">
         <v>2</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>44</v>
+        <v>148</v>
       </c>
       <c r="L6" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>45</v>
+      <c r="A7" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="H7" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>48</v>
+        <v>162</v>
       </c>
       <c r="L7" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
       <c r="M7" t="s">
-        <v>84</v>
+        <v>364</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>144</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="F8">
         <v>10</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="H8" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I8" t="s">
-        <v>43</v>
+        <v>145</v>
       </c>
       <c r="J8">
         <v>2</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="L8" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="F9">
         <v>8</v>
       </c>
       <c r="G9" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="H9" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I9">
         <v>3</v>
@@ -2221,21 +2213,21 @@
         <v>2</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="L9" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F10">
         <v>60</v>
@@ -2244,36 +2236,36 @@
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
       <c r="M10" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="F11">
         <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="H11" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I11">
         <v>3</v>
@@ -2282,36 +2274,36 @@
         <v>3</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="L11" t="s">
-        <v>20</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="F12">
         <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="H12" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="I12">
         <v>2</v>
@@ -2320,36 +2312,36 @@
         <v>2</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="L12" t="s">
-        <v>20</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="F13">
         <v>5</v>
       </c>
       <c r="G13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H13" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="I13">
         <v>9</v>
@@ -2358,53 +2350,53 @@
         <v>2</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>70</v>
+        <v>222</v>
       </c>
       <c r="L13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="24.75" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>71</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>72</v>
+        <v>447</v>
       </c>
       <c r="L14" t="s">
-        <v>29</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>73</v>
+        <v>190</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="F15">
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="H15" t="s">
-        <v>74</v>
+        <v>191</v>
       </c>
       <c r="I15">
         <v>3</v>
@@ -2413,91 +2405,88 @@
         <v>3</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>75</v>
+        <v>198</v>
       </c>
       <c r="L15" t="s">
-        <v>29</v>
+        <v>208</v>
       </c>
       <c r="M15" t="s">
-        <v>84</v>
+        <v>363</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="C16" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E16" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H16" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="L16" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
-        <v>447</v>
+      <c r="A17" s="11" t="s">
+        <v>444</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F17">
-        <v>24</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G17" t="s">
+        <v>97</v>
       </c>
       <c r="J17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="L17" t="s">
-        <v>80</v>
-      </c>
-      <c r="M17" t="s">
-        <v>450</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="F18">
         <v>5</v>
       </c>
       <c r="G18" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="H18" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I18">
         <v>10</v>
@@ -2506,59 +2495,59 @@
         <v>12</v>
       </c>
       <c r="L18" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
       <c r="M18" t="s">
-        <v>84</v>
+        <v>363</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E19" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="L19" t="s">
-        <v>29</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D20" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E20" t="s">
-        <v>89</v>
+        <v>389</v>
       </c>
       <c r="F20">
         <v>8</v>
       </c>
       <c r="G20" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="H20" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="I20">
         <v>11</v>
@@ -2567,88 +2556,88 @@
         <v>5</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>91</v>
+        <v>219</v>
       </c>
       <c r="L20" t="s">
-        <v>80</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E21" t="s">
-        <v>93</v>
+        <v>197</v>
       </c>
       <c r="F21">
         <v>12</v>
       </c>
       <c r="H21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="L21" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
       <c r="M21" t="s">
-        <v>140</v>
+        <v>364</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C22" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E22" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="L22" t="s">
-        <v>20</v>
+        <v>206</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>99</v>
+        <v>174</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="F23">
         <v>4</v>
       </c>
       <c r="G23" t="s">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="H23" t="s">
-        <v>102</v>
+        <v>176</v>
       </c>
       <c r="I23">
         <v>2</v>
@@ -2657,103 +2646,103 @@
         <v>6</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>103</v>
+        <v>177</v>
       </c>
       <c r="L23" t="s">
-        <v>20</v>
+        <v>206</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="F24">
         <v>3</v>
       </c>
       <c r="H24" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="L24" t="s">
-        <v>20</v>
+        <v>206</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D25" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E25" t="s">
-        <v>108</v>
+        <v>279</v>
       </c>
       <c r="F25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G25" t="s">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="H25" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>109</v>
+        <v>155</v>
       </c>
       <c r="L25" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>111</v>
+        <v>25</v>
       </c>
       <c r="F26">
         <v>10</v>
       </c>
       <c r="G26" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="H26" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="I26">
         <v>8</v>
@@ -2762,33 +2751,33 @@
         <v>2</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>113</v>
+        <v>33</v>
       </c>
       <c r="L26" t="s">
-        <v>80</v>
+        <v>207</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E27" t="s">
-        <v>115</v>
+        <v>277</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="H27" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I27">
         <v>6</v>
@@ -2797,33 +2786,33 @@
         <v>5</v>
       </c>
       <c r="L27" t="s">
-        <v>20</v>
+        <v>206</v>
       </c>
       <c r="M27" t="s">
-        <v>84</v>
+        <v>363</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="C28" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E28" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="F28">
         <v>2</v>
       </c>
       <c r="G28" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="H28" t="s">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="I28">
         <v>3</v>
@@ -2832,36 +2821,36 @@
         <v>1</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>118</v>
+        <v>22</v>
       </c>
       <c r="L28" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="C29" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E29" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="F29">
         <v>3</v>
       </c>
       <c r="G29" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="H29" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I29">
         <v>4</v>
@@ -2870,36 +2859,36 @@
         <v>1</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>120</v>
+        <v>223</v>
       </c>
       <c r="L29" t="s">
-        <v>20</v>
+        <v>206</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B30" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D30" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E30" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F30">
         <v>24</v>
       </c>
       <c r="G30" t="s">
+        <v>122</v>
+      </c>
+      <c r="H30" t="s">
         <v>123</v>
-      </c>
-      <c r="H30" t="s">
-        <v>124</v>
       </c>
       <c r="I30">
         <v>21</v>
@@ -2908,39 +2897,39 @@
         <v>3</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="L30" t="s">
-        <v>29</v>
+        <v>208</v>
       </c>
       <c r="M30" t="s">
-        <v>84</v>
+        <v>363</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B31" t="s">
-        <v>127</v>
+        <v>42</v>
       </c>
       <c r="C31" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D31" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E31" t="s">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="F31">
         <v>16</v>
       </c>
       <c r="G31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H31" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I31">
         <v>8</v>
@@ -2949,36 +2938,36 @@
         <v>4</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="L31" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="72.75" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E32" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="F32">
         <v>5</v>
       </c>
       <c r="G32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H32" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="I32">
         <v>17</v>
@@ -2987,36 +2976,36 @@
         <v>5</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>133</v>
+        <v>324</v>
       </c>
       <c r="L32" t="s">
-        <v>20</v>
+        <v>206</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>134</v>
+        <v>184</v>
       </c>
       <c r="B33" t="s">
-        <v>127</v>
+        <v>42</v>
       </c>
       <c r="C33" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D33" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E33" t="s">
-        <v>135</v>
+        <v>282</v>
       </c>
       <c r="F33">
         <v>7</v>
       </c>
       <c r="G33" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="H33" t="s">
-        <v>134</v>
+        <v>184</v>
       </c>
       <c r="I33">
         <v>4</v>
@@ -3025,36 +3014,36 @@
         <v>3</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>137</v>
+        <v>185</v>
       </c>
       <c r="L33" t="s">
-        <v>29</v>
+        <v>208</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>138</v>
+        <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C34" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D34" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E34" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="F34">
         <v>5</v>
       </c>
       <c r="G34" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="H34" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="I34">
         <v>4</v>
@@ -3063,39 +3052,39 @@
         <v>3</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>139</v>
+        <v>319</v>
       </c>
       <c r="L34" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
       <c r="M34" t="s">
-        <v>140</v>
+        <v>364</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="B35" t="s">
-        <v>127</v>
+        <v>42</v>
       </c>
       <c r="C35" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D35" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E35" t="s">
-        <v>142</v>
+        <v>281</v>
       </c>
       <c r="F35">
         <v>11</v>
       </c>
       <c r="G35" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="H35" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="I35">
         <v>7</v>
@@ -3104,59 +3093,59 @@
         <v>6</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>144</v>
+        <v>245</v>
       </c>
       <c r="L35" t="s">
-        <v>80</v>
+        <v>207</v>
       </c>
       <c r="M35" t="s">
-        <v>145</v>
+        <v>352</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>146</v>
+        <v>81</v>
       </c>
       <c r="B36" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D36" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="L36" t="s">
-        <v>20</v>
+        <v>206</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>148</v>
+        <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>127</v>
+        <v>42</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E37" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="F37">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H37" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="I37">
         <v>7</v>
@@ -3165,65 +3154,65 @@
         <v>2</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="L37" t="s">
-        <v>20</v>
+        <v>206</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>150</v>
+        <v>68</v>
       </c>
       <c r="B38" t="s">
-        <v>127</v>
+        <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D38" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E38" t="s">
-        <v>151</v>
+        <v>69</v>
       </c>
       <c r="F38">
         <v>4</v>
       </c>
       <c r="H38" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="J38">
         <v>1</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>152</v>
+        <v>230</v>
       </c>
       <c r="L38" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C39" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" t="s">
         <v>153</v>
-      </c>
-      <c r="C39" t="s">
-        <v>23</v>
-      </c>
-      <c r="D39" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" t="s">
-        <v>154</v>
       </c>
       <c r="F39">
         <v>7</v>
       </c>
       <c r="G39" t="s">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="H39" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I39">
         <v>3</v>
@@ -3232,884 +3221,869 @@
         <v>2</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="L39" t="s">
+        <v>205</v>
+      </c>
+      <c r="M39" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="C40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" t="s">
+        <v>105</v>
+      </c>
+      <c r="F40">
+        <v>5</v>
+      </c>
+      <c r="G40" t="s">
+        <v>270</v>
+      </c>
+      <c r="H40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+      <c r="J40">
+        <v>4</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="L40" t="s">
+        <v>205</v>
+      </c>
+      <c r="M40" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C41" t="s">
+        <v>77</v>
+      </c>
+      <c r="D41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E41" t="s">
+        <v>210</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="L41" t="s">
+        <v>205</v>
+      </c>
+      <c r="M41" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" t="s">
+        <v>45</v>
+      </c>
+      <c r="E42" t="s">
+        <v>280</v>
+      </c>
+      <c r="F42">
+        <v>8</v>
+      </c>
+      <c r="G42" t="s">
+        <v>39</v>
+      </c>
+      <c r="H42" t="s">
+        <v>12</v>
+      </c>
+      <c r="I42">
+        <v>8</v>
+      </c>
+      <c r="J42">
+        <v>8</v>
+      </c>
+      <c r="L42" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43" t="s">
+        <v>42</v>
+      </c>
+      <c r="C43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" t="s">
         <v>35</v>
       </c>
-      <c r="M39" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C40" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" t="s">
-        <v>46</v>
-      </c>
-      <c r="E40" t="s">
-        <v>159</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="L40" t="s">
-        <v>35</v>
-      </c>
-      <c r="M40" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>161</v>
-      </c>
-      <c r="B41" t="s">
-        <v>127</v>
-      </c>
-      <c r="C41" t="s">
-        <v>23</v>
-      </c>
-      <c r="D41" t="s">
-        <v>162</v>
-      </c>
-      <c r="E41" t="s">
-        <v>163</v>
-      </c>
-      <c r="F41">
-        <v>8</v>
-      </c>
-      <c r="G41" t="s">
-        <v>38</v>
-      </c>
-      <c r="H41" t="s">
-        <v>27</v>
-      </c>
-      <c r="I41">
-        <v>8</v>
-      </c>
-      <c r="J41">
-        <v>8</v>
-      </c>
-      <c r="L41" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>164</v>
-      </c>
-      <c r="B42" t="s">
-        <v>127</v>
-      </c>
-      <c r="C42" t="s">
-        <v>23</v>
-      </c>
-      <c r="D42" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" t="s">
-        <v>50</v>
-      </c>
-      <c r="F42">
-        <v>9</v>
-      </c>
-      <c r="G42" t="s">
-        <v>38</v>
-      </c>
-      <c r="H42" t="s">
-        <v>27</v>
-      </c>
-      <c r="I42">
-        <v>3</v>
-      </c>
-      <c r="J42">
+      <c r="F43">
         <v>6</v>
       </c>
-      <c r="K42" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="L42" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>166</v>
-      </c>
-      <c r="B43" t="s">
-        <v>127</v>
-      </c>
-      <c r="C43" t="s">
-        <v>23</v>
-      </c>
-      <c r="D43" t="s">
-        <v>24</v>
-      </c>
-      <c r="E43" t="s">
-        <v>167</v>
-      </c>
-      <c r="F43">
-        <v>10</v>
-      </c>
       <c r="G43" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H43" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I43">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J43">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="L43" t="s">
-        <v>35</v>
+        <v>206</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>168</v>
+        <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="C44" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D44" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E44" t="s">
-        <v>169</v>
+        <v>278</v>
       </c>
       <c r="F44">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="G44" t="s">
+        <v>39</v>
       </c>
       <c r="H44" t="s">
-        <v>33</v>
+        <v>12</v>
+      </c>
+      <c r="I44">
+        <v>4</v>
       </c>
       <c r="J44">
+        <v>3</v>
+      </c>
+      <c r="L44" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>89</v>
+      </c>
+      <c r="B45" t="s">
+        <v>28</v>
+      </c>
+      <c r="C45" t="s">
+        <v>63</v>
+      </c>
+      <c r="D45" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" t="s">
+        <v>90</v>
+      </c>
+      <c r="F45">
+        <v>8</v>
+      </c>
+      <c r="H45" t="s">
+        <v>64</v>
+      </c>
+      <c r="J45">
         <v>0</v>
       </c>
-      <c r="K44" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="L44" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>171</v>
-      </c>
-      <c r="B45" t="s">
-        <v>58</v>
-      </c>
-      <c r="C45" t="s">
-        <v>31</v>
-      </c>
-      <c r="D45" t="s">
-        <v>24</v>
-      </c>
-      <c r="E45" t="s">
-        <v>172</v>
-      </c>
-      <c r="F45">
+      <c r="K45" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L45" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>86</v>
+      </c>
+      <c r="B46" t="s">
+        <v>28</v>
+      </c>
+      <c r="C46" t="s">
+        <v>63</v>
+      </c>
+      <c r="D46" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" t="s">
+        <v>220</v>
+      </c>
+      <c r="F46">
         <v>5</v>
       </c>
-      <c r="H45" t="s">
-        <v>33</v>
-      </c>
-      <c r="J45">
+      <c r="H46" t="s">
+        <v>64</v>
+      </c>
+      <c r="J46">
         <v>9</v>
       </c>
-      <c r="K45" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="L45" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="C46" t="s">
-        <v>15</v>
-      </c>
-      <c r="D46" t="s">
-        <v>16</v>
-      </c>
-      <c r="E46" t="s">
-        <v>175</v>
-      </c>
-      <c r="H46" t="s">
+      <c r="K46" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L46" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="C47" t="s">
+        <v>77</v>
+      </c>
+      <c r="D47" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" t="s">
+        <v>116</v>
+      </c>
+      <c r="H47" t="s">
+        <v>101</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="L47" t="s">
+        <v>206</v>
+      </c>
+      <c r="M47" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B48" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48" t="s">
         <v>18</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="L46" t="s">
-        <v>20</v>
-      </c>
-      <c r="M46" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="B47" t="s">
-        <v>62</v>
-      </c>
-      <c r="C47" t="s">
-        <v>23</v>
-      </c>
-      <c r="D47" t="s">
-        <v>16</v>
-      </c>
-      <c r="E47" t="s">
-        <v>105</v>
-      </c>
-      <c r="F47">
-        <v>3</v>
-      </c>
-      <c r="G47" t="s">
-        <v>64</v>
-      </c>
-      <c r="H47" t="s">
-        <v>27</v>
-      </c>
-      <c r="I47">
-        <v>5</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="L47" t="s">
-        <v>35</v>
-      </c>
-      <c r="M47" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>179</v>
-      </c>
-      <c r="B48" t="s">
-        <v>62</v>
-      </c>
-      <c r="C48" t="s">
-        <v>23</v>
-      </c>
-      <c r="D48" t="s">
-        <v>24</v>
-      </c>
-      <c r="E48" t="s">
-        <v>59</v>
       </c>
       <c r="F48">
         <v>3</v>
       </c>
       <c r="G48" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="H48" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I48">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J48">
         <v>0</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>180</v>
+        <v>87</v>
       </c>
       <c r="L48" t="s">
-        <v>35</v>
+        <v>205</v>
+      </c>
+      <c r="M48" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="8" t="s">
-        <v>181</v>
+      <c r="A49" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" t="s">
+        <v>7</v>
       </c>
       <c r="C49" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E49" t="s">
-        <v>108</v>
+        <v>19</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G49" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H49" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="I49">
+        <v>15</v>
+      </c>
+      <c r="J49">
         <v>0</v>
       </c>
-      <c r="J49">
-        <v>1</v>
-      </c>
       <c r="K49" s="1" t="s">
-        <v>182</v>
+        <v>40</v>
       </c>
       <c r="L49" t="s">
-        <v>20</v>
-      </c>
-      <c r="M49" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>183</v>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="8" t="s">
+        <v>128</v>
       </c>
       <c r="C50" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D50" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E50" t="s">
-        <v>105</v>
+        <v>279</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
+      <c r="G50" t="s">
+        <v>39</v>
+      </c>
       <c r="H50" t="s">
-        <v>184</v>
+        <v>191</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
       </c>
       <c r="J50">
+        <v>1</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="L50" t="s">
+        <v>206</v>
+      </c>
+      <c r="M50" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>193</v>
+      </c>
+      <c r="C51" t="s">
+        <v>63</v>
+      </c>
+      <c r="D51" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51" t="s">
+        <v>18</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="H51" t="s">
+        <v>118</v>
+      </c>
+      <c r="J51">
         <v>0</v>
       </c>
-      <c r="K50" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="L50" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>186</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="K51" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="L51" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>76</v>
+      </c>
+      <c r="C52" t="s">
+        <v>77</v>
+      </c>
+      <c r="D52" t="s">
+        <v>78</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L52" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="B53" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D53" t="s">
+        <v>16</v>
+      </c>
+      <c r="E53" t="s">
+        <v>161</v>
+      </c>
+      <c r="F53">
+        <v>5</v>
+      </c>
+      <c r="G53" t="s">
+        <v>39</v>
+      </c>
+      <c r="H53" t="s">
+        <v>157</v>
+      </c>
+      <c r="I53">
+        <v>7</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="L53" t="s">
+        <v>207</v>
+      </c>
+      <c r="M53" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>131</v>
+      </c>
+      <c r="B54" t="s">
+        <v>74</v>
+      </c>
+      <c r="C54" t="s">
+        <v>63</v>
+      </c>
+      <c r="D54" t="s">
+        <v>16</v>
+      </c>
+      <c r="E54" t="s">
+        <v>132</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="H54" t="s">
+        <v>133</v>
+      </c>
+      <c r="J54">
         <v>15</v>
       </c>
-      <c r="D51" t="s">
-        <v>46</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="L51" t="s">
+      <c r="K54" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="L54" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" t="s">
+        <v>16</v>
+      </c>
+      <c r="E55" t="s">
+        <v>19</v>
+      </c>
+      <c r="F55">
+        <v>5</v>
+      </c>
+      <c r="G55" t="s">
+        <v>11</v>
+      </c>
+      <c r="H55" t="s">
+        <v>154</v>
+      </c>
+      <c r="I55">
+        <v>7</v>
+      </c>
+      <c r="J55">
+        <v>1</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="L55" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
+      <c r="A56" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="B56" t="s">
+        <v>42</v>
+      </c>
+      <c r="C56" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" t="s">
+        <v>16</v>
+      </c>
+      <c r="E56" t="s">
+        <v>278</v>
+      </c>
+      <c r="F56">
+        <v>3</v>
+      </c>
+      <c r="G56" t="s">
+        <v>169</v>
+      </c>
+      <c r="H56" t="s">
+        <v>12</v>
+      </c>
+      <c r="I56">
+        <v>4</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="L56" t="s">
+        <v>205</v>
+      </c>
+      <c r="M56" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C57" t="s">
+        <v>63</v>
+      </c>
+      <c r="D57" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" t="s">
+        <v>18</v>
+      </c>
+      <c r="F57">
+        <v>5</v>
+      </c>
+      <c r="H57" t="s">
+        <v>64</v>
+      </c>
+      <c r="J57">
+        <v>2</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="L57" t="s">
+        <v>205</v>
+      </c>
+      <c r="M57" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B58" t="s">
+        <v>28</v>
+      </c>
+      <c r="C58" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="52" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="B52" t="s">
-        <v>62</v>
-      </c>
-      <c r="C52" t="s">
-        <v>79</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="F58">
+        <v>3</v>
+      </c>
+      <c r="G58" t="s">
+        <v>30</v>
+      </c>
+      <c r="H58" t="s">
+        <v>191</v>
+      </c>
+      <c r="I58">
+        <v>3</v>
+      </c>
+      <c r="J58">
+        <v>1</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="L58" t="s">
+        <v>206</v>
+      </c>
+      <c r="M58" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="C59" t="s">
+        <v>77</v>
+      </c>
+      <c r="D59" t="s">
+        <v>442</v>
+      </c>
+      <c r="E59" t="s">
+        <v>43</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L59" t="s">
+        <v>208</v>
+      </c>
+      <c r="M59" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>119</v>
+      </c>
+      <c r="C60" t="s">
+        <v>63</v>
+      </c>
+      <c r="D60" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" t="s">
+        <v>18</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="H60" t="s">
+        <v>118</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="L60" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="A61" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" t="s">
         <v>24</v>
       </c>
-      <c r="E52" t="s">
-        <v>189</v>
-      </c>
-      <c r="F52">
-        <v>7</v>
-      </c>
-      <c r="G52" t="s">
-        <v>38</v>
-      </c>
-      <c r="H52" t="s">
-        <v>190</v>
-      </c>
-      <c r="I52">
-        <v>7</v>
-      </c>
-      <c r="J52">
-        <v>7</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="L52" t="s">
-        <v>80</v>
-      </c>
-      <c r="M52" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>192</v>
-      </c>
-      <c r="B53" t="s">
-        <v>22</v>
-      </c>
-      <c r="C53" t="s">
-        <v>31</v>
-      </c>
-      <c r="D53" t="s">
-        <v>24</v>
-      </c>
-      <c r="E53" t="s">
-        <v>193</v>
-      </c>
-      <c r="F53">
-        <v>1</v>
-      </c>
-      <c r="H53" t="s">
-        <v>194</v>
-      </c>
-      <c r="J53">
-        <v>15</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="L53" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>196</v>
-      </c>
-      <c r="B54" t="s">
-        <v>62</v>
-      </c>
-      <c r="C54" t="s">
-        <v>23</v>
-      </c>
-      <c r="D54" t="s">
-        <v>24</v>
-      </c>
-      <c r="E54" t="s">
-        <v>59</v>
-      </c>
-      <c r="F54">
-        <v>5</v>
-      </c>
-      <c r="G54" t="s">
-        <v>64</v>
-      </c>
-      <c r="H54" t="s">
-        <v>155</v>
-      </c>
-      <c r="I54">
-        <v>7</v>
-      </c>
-      <c r="J54">
-        <v>1</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="L54" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" ht="48.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="B55" t="s">
-        <v>127</v>
-      </c>
-      <c r="C55" t="s">
-        <v>23</v>
-      </c>
-      <c r="D55" t="s">
-        <v>24</v>
-      </c>
-      <c r="E55" t="s">
-        <v>167</v>
-      </c>
-      <c r="F55">
-        <v>3</v>
-      </c>
-      <c r="G55" t="s">
-        <v>136</v>
-      </c>
-      <c r="H55" t="s">
-        <v>27</v>
-      </c>
-      <c r="I55">
-        <v>4</v>
-      </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="L55" t="s">
-        <v>35</v>
-      </c>
-      <c r="M55" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="C56" t="s">
-        <v>31</v>
-      </c>
-      <c r="D56" t="s">
-        <v>24</v>
-      </c>
-      <c r="E56" t="s">
-        <v>105</v>
-      </c>
-      <c r="F56">
-        <v>5</v>
-      </c>
-      <c r="H56" t="s">
-        <v>33</v>
-      </c>
-      <c r="J56">
+      <c r="D61" t="s">
+        <v>16</v>
+      </c>
+      <c r="E61" t="s">
+        <v>229</v>
+      </c>
+      <c r="F61">
+        <v>16</v>
+      </c>
+      <c r="G61" t="s">
+        <v>248</v>
+      </c>
+      <c r="H61" t="s">
+        <v>166</v>
+      </c>
+      <c r="I61">
         <v>2</v>
       </c>
-      <c r="K56" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="L56" t="s">
-        <v>35</v>
-      </c>
-      <c r="M56" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A57" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="B57" t="s">
-        <v>58</v>
-      </c>
-      <c r="C57" t="s">
-        <v>23</v>
-      </c>
-      <c r="D57" t="s">
-        <v>24</v>
-      </c>
-      <c r="E57" t="s">
-        <v>50</v>
-      </c>
-      <c r="F57">
-        <v>3</v>
-      </c>
-      <c r="G57" t="s">
-        <v>53</v>
-      </c>
-      <c r="H57" t="s">
-        <v>74</v>
-      </c>
-      <c r="I57">
-        <v>3</v>
-      </c>
-      <c r="J57">
-        <v>1</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="L57" t="s">
-        <v>20</v>
-      </c>
-      <c r="M57" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="B58" t="s">
-        <v>58</v>
-      </c>
-      <c r="C58" t="s">
-        <v>79</v>
-      </c>
-      <c r="D58" t="s">
-        <v>24</v>
-      </c>
-      <c r="E58" t="s">
-        <v>205</v>
-      </c>
-      <c r="F58">
-        <v>18</v>
-      </c>
-      <c r="G58" t="s">
-        <v>83</v>
-      </c>
-      <c r="H58" t="s">
-        <v>206</v>
-      </c>
-      <c r="I58">
-        <v>0</v>
-      </c>
-      <c r="J58">
-        <v>12</v>
-      </c>
-      <c r="K58" s="1" t="s">
+      <c r="J61">
+        <v>2</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="L61" t="s">
         <v>207</v>
       </c>
-      <c r="L58" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>208</v>
-      </c>
-      <c r="C59" t="s">
-        <v>31</v>
-      </c>
-      <c r="D59" t="s">
-        <v>24</v>
-      </c>
-      <c r="E59" t="s">
-        <v>105</v>
-      </c>
-      <c r="F59">
-        <v>1</v>
-      </c>
-      <c r="H59" t="s">
-        <v>184</v>
-      </c>
-      <c r="J59">
-        <v>0</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="L59" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="B60" t="s">
-        <v>62</v>
-      </c>
-      <c r="C60" t="s">
-        <v>79</v>
-      </c>
-      <c r="D60" t="s">
-        <v>24</v>
-      </c>
-      <c r="E60" t="s">
-        <v>211</v>
-      </c>
-      <c r="F60">
-        <v>16</v>
-      </c>
-      <c r="G60" t="s">
-        <v>212</v>
-      </c>
-      <c r="H60" t="s">
-        <v>213</v>
-      </c>
-      <c r="I60">
-        <v>2</v>
-      </c>
-      <c r="J60">
-        <v>2</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="L60" t="s">
-        <v>80</v>
-      </c>
-      <c r="M60" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="C61" t="s">
-        <v>79</v>
-      </c>
-      <c r="D61" t="s">
-        <v>24</v>
-      </c>
-      <c r="E61" t="s">
-        <v>217</v>
-      </c>
-      <c r="F61">
-        <v>2</v>
-      </c>
-      <c r="G61" t="s">
-        <v>218</v>
-      </c>
-      <c r="H61" t="s">
-        <v>219</v>
-      </c>
-      <c r="I61">
-        <v>1</v>
-      </c>
-      <c r="J61">
-        <v>8</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="L61" t="s">
-        <v>29</v>
+      <c r="M61" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C62" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D62" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E62" t="s">
-        <v>37</v>
+        <v>226</v>
       </c>
       <c r="F62">
+        <v>2</v>
+      </c>
+      <c r="G62" t="s">
+        <v>97</v>
+      </c>
+      <c r="H62" t="s">
+        <v>227</v>
+      </c>
+      <c r="I62">
+        <v>1</v>
+      </c>
+      <c r="J62">
+        <v>8</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="L62" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="A63" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C63" t="s">
+        <v>63</v>
+      </c>
+      <c r="D63" t="s">
+        <v>16</v>
+      </c>
+      <c r="E63" t="s">
+        <v>109</v>
+      </c>
+      <c r="F63">
         <v>3</v>
       </c>
-      <c r="J62">
+      <c r="J63">
         <v>1</v>
       </c>
-      <c r="K62" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="L62" t="s">
-        <v>29</v>
-      </c>
-      <c r="M62" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>223</v>
-      </c>
-      <c r="C63" t="s">
-        <v>31</v>
-      </c>
-      <c r="D63" t="s">
-        <v>24</v>
-      </c>
-      <c r="E63" t="s">
-        <v>224</v>
-      </c>
-      <c r="F63">
+      <c r="K63" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="L63" t="s">
+        <v>208</v>
+      </c>
+      <c r="M63" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>94</v>
+      </c>
+      <c r="C64" t="s">
+        <v>63</v>
+      </c>
+      <c r="D64" t="s">
+        <v>16</v>
+      </c>
+      <c r="E64" t="s">
+        <v>57</v>
+      </c>
+      <c r="F64">
         <v>10</v>
       </c>
-      <c r="H63" t="s">
-        <v>94</v>
-      </c>
-      <c r="J63">
-        <v>8</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="L63" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="A64" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="C64" t="s">
-        <v>23</v>
-      </c>
-      <c r="D64" t="s">
-        <v>24</v>
-      </c>
-      <c r="E64" t="s">
-        <v>97</v>
-      </c>
-      <c r="F64">
-        <v>5</v>
-      </c>
-      <c r="G64" t="s">
-        <v>291</v>
-      </c>
       <c r="H64" t="s">
-        <v>117</v>
-      </c>
-      <c r="I64">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="J64">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>423</v>
+        <v>126</v>
       </c>
       <c r="L64" t="s">
-        <v>35</v>
-      </c>
-      <c r="M64" t="s">
-        <v>424</v>
+        <v>205</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A65" s="8" t="s">
-        <v>227</v>
+      <c r="A65" s="7" t="s">
+        <v>189</v>
       </c>
       <c r="C65" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D65" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E65" t="s">
-        <v>151</v>
+        <v>69</v>
       </c>
       <c r="F65">
         <v>4</v>
       </c>
       <c r="G65" t="s">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="H65" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I65">
         <v>2</v>
@@ -4118,53 +4092,53 @@
         <v>5</v>
       </c>
       <c r="L65" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
       <c r="M65" t="s">
-        <v>84</v>
+        <v>363</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>228</v>
+        <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D66" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>229</v>
+        <v>82</v>
       </c>
       <c r="L66" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>230</v>
+        <v>158</v>
       </c>
       <c r="B67" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="C67" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D67" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E67" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="F67">
         <v>2</v>
       </c>
       <c r="G67" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="H67" t="s">
-        <v>231</v>
+        <v>36</v>
       </c>
       <c r="I67">
         <v>3</v>
@@ -4173,56 +4147,56 @@
         <v>0</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>232</v>
+        <v>107</v>
       </c>
       <c r="L67" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
-        <v>233</v>
+        <v>85</v>
       </c>
       <c r="C68" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D68" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="E68" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H68" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>234</v>
+        <v>103</v>
       </c>
       <c r="L68" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>235</v>
+        <v>180</v>
       </c>
       <c r="C69" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D69" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E69" t="s">
-        <v>236</v>
+        <v>181</v>
       </c>
       <c r="F69">
         <v>5</v>
       </c>
       <c r="G69" t="s">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="H69" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I69">
         <v>6</v>
@@ -4231,39 +4205,39 @@
         <v>6</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>237</v>
+        <v>182</v>
       </c>
       <c r="L69" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
       <c r="M69" t="s">
-        <v>84</v>
+        <v>363</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>238</v>
+        <v>159</v>
       </c>
       <c r="B70" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="C70" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D70" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="E70" t="s">
-        <v>239</v>
+        <v>96</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>218</v>
+        <v>97</v>
       </c>
       <c r="H70" t="s">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -4272,36 +4246,36 @@
         <v>15</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="L70" t="s">
-        <v>20</v>
+        <v>206</v>
       </c>
       <c r="M70" t="s">
-        <v>84</v>
+        <v>363</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>242</v>
+        <v>187</v>
       </c>
       <c r="C71" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D71" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E71" t="s">
-        <v>115</v>
+        <v>277</v>
       </c>
       <c r="F71">
         <v>5</v>
       </c>
       <c r="G71" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="H71" t="s">
-        <v>231</v>
+        <v>36</v>
       </c>
       <c r="I71">
         <v>4</v>
@@ -4310,33 +4284,33 @@
         <v>1</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>243</v>
+        <v>188</v>
       </c>
       <c r="L71" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>244</v>
+        <v>186</v>
       </c>
       <c r="C72" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D72" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E72" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="F72">
         <v>3</v>
       </c>
       <c r="G72" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="H72" t="s">
-        <v>74</v>
+        <v>191</v>
       </c>
       <c r="I72">
         <v>2</v>
@@ -4345,33 +4319,33 @@
         <v>0</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>245</v>
+        <v>286</v>
       </c>
       <c r="L72" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>246</v>
+        <v>409</v>
       </c>
       <c r="C73" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D73" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E73" t="s">
-        <v>247</v>
+        <v>173</v>
       </c>
       <c r="F73">
         <v>8</v>
       </c>
       <c r="G73" t="s">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="H73" t="s">
-        <v>248</v>
+        <v>410</v>
       </c>
       <c r="I73">
         <v>6</v>
@@ -4380,17 +4354,17 @@
         <v>11</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="L73" t="s">
-        <v>80</v>
+        <v>207</v>
       </c>
       <c r="M73" t="s">
-        <v>84</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L73">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M73">
     <sortCondition ref="A2:A73"/>
   </sortState>
   <printOptions gridLines="1"/>
@@ -4404,7 +4378,7 @@
   <dimension ref="A1:O70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
@@ -4417,69 +4391,69 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="K1" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>11</v>
+        <v>204</v>
       </c>
       <c r="M1" t="s">
-        <v>12</v>
+        <v>302</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>13</v>
+        <v>303</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>250</v>
+        <v>393</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>239</v>
+        <v>96</v>
       </c>
       <c r="F2">
         <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I2">
         <v>6</v>
@@ -4488,33 +4462,33 @@
         <v>3</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>252</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>254</v>
+        <v>233</v>
       </c>
       <c r="F3">
         <v>6</v>
       </c>
       <c r="G3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H3" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="I3">
         <v>8</v>
@@ -4528,28 +4502,28 @@
     </row>
     <row r="4" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="F4">
         <v>10</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I4">
         <v>6</v>
@@ -4558,79 +4532,79 @@
         <v>1</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>258</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="H5" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>261</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J6">
         <v>5</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="F7">
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="H7" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I7">
         <v>4</v>
@@ -4639,30 +4613,30 @@
         <v>4</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="F8">
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -4671,33 +4645,33 @@
         <v>3</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="F9">
         <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="H9" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="I9">
         <v>9</v>
@@ -4706,33 +4680,33 @@
         <v>2</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="H10" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -4741,30 +4715,30 @@
         <v>1</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>236</v>
+        <v>181</v>
       </c>
       <c r="F11">
         <v>5</v>
       </c>
       <c r="G11" t="s">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="H11" t="s">
-        <v>275</v>
+        <v>215</v>
       </c>
       <c r="I11">
         <v>4</v>
@@ -4773,21 +4747,21 @@
         <v>6</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>276</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F12">
         <v>10</v>
@@ -4796,56 +4770,56 @@
         <v>0</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="F13">
         <v>6</v>
       </c>
       <c r="H13" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>282</v>
+        <v>261</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="F14">
         <v>4</v>
       </c>
       <c r="G14" t="s">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="H14" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I14">
         <v>7</v>
@@ -4854,21 +4828,21 @@
         <v>4</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -4877,30 +4851,30 @@
         <v>1</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E16" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="F16">
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="H16" t="s">
-        <v>292</v>
+        <v>271</v>
       </c>
       <c r="I16">
         <v>10</v>
@@ -4909,30 +4883,30 @@
         <v>6</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>293</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>294</v>
+        <v>272</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="F17">
         <v>3</v>
       </c>
       <c r="G17" t="s">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="H17" t="s">
-        <v>74</v>
+        <v>191</v>
       </c>
       <c r="I17">
         <v>2</v>
@@ -4941,30 +4915,30 @@
         <v>4</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="F18">
         <v>2</v>
       </c>
       <c r="G18" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="H18" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="I18">
         <v>4</v>
@@ -4973,33 +4947,33 @@
         <v>0</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E19" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="F19">
         <v>6</v>
       </c>
       <c r="G19" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="H19" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="I19">
         <v>5</v>
@@ -5008,30 +4982,30 @@
         <v>5</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E20" t="s">
-        <v>302</v>
+        <v>273</v>
       </c>
       <c r="F20">
         <v>3</v>
       </c>
       <c r="G20" t="s">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="H20" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -5040,18 +5014,18 @@
         <v>0</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F21">
         <v>60</v>
@@ -5060,30 +5034,30 @@
         <v>0</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D22" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E22" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="F22">
         <v>5</v>
       </c>
       <c r="G22" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="H22" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="I22">
         <v>2</v>
@@ -5092,44 +5066,44 @@
         <v>4</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C24" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>108</v>
+        <v>279</v>
       </c>
       <c r="F24">
         <v>5</v>
       </c>
       <c r="G24" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="H24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I24">
         <v>4</v>
@@ -5138,30 +5112,30 @@
         <v>4</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="C25" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D25" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E25" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="F25">
         <v>7</v>
       </c>
       <c r="G25" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="H25" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I25">
         <v>4</v>
@@ -5172,16 +5146,16 @@
     </row>
     <row r="26" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C26" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D26" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="F26">
         <v>6</v>
@@ -5190,30 +5164,30 @@
         <v>0</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="C27" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E27" t="s">
-        <v>239</v>
+        <v>96</v>
       </c>
       <c r="F27">
         <v>3</v>
       </c>
       <c r="G27" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="H27" t="s">
-        <v>231</v>
+        <v>36</v>
       </c>
       <c r="I27">
         <v>1</v>
@@ -5222,30 +5196,30 @@
         <v>0</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="C28" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E28" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="F28">
         <v>3</v>
       </c>
       <c r="G28" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="H28" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I28">
         <v>5</v>
@@ -5254,55 +5228,55 @@
         <v>2</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D29" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="C30" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D30" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="C31" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D31" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E31" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="F31">
         <v>10</v>
       </c>
       <c r="H31" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -5311,21 +5285,21 @@
         <v>2</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="C32" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D32" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E32" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="F32">
         <v>3</v>
@@ -5339,54 +5313,54 @@
     </row>
     <row r="33" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="C33" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D33" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E33" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B34" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D34" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E34" t="s">
-        <v>108</v>
+        <v>279</v>
       </c>
       <c r="F34">
         <v>10</v>
       </c>
       <c r="G34" t="s">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="H34" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="I34">
         <v>2</v>
@@ -5395,76 +5369,76 @@
         <v>2</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="60.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="C35" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D35" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E35" t="s">
-        <v>108</v>
+        <v>279</v>
       </c>
       <c r="F35">
         <v>3</v>
       </c>
       <c r="G35" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="J35">
         <v>0</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C36" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="H36" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E37" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="F37">
         <v>5</v>
       </c>
       <c r="G37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H37" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="I37">
         <v>3</v>
@@ -5473,53 +5447,53 @@
         <v>0</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C38" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D38" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="E38" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H38" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C39" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D39" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E39" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="F39">
         <v>4</v>
       </c>
       <c r="G39" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="H39" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="I39">
         <v>8</v>
@@ -5528,59 +5502,59 @@
         <v>4</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="C40" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D40" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E40" t="s">
-        <v>151</v>
+        <v>69</v>
       </c>
       <c r="F40">
         <v>3</v>
       </c>
       <c r="H40" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="J40">
         <v>0</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="B41" t="s">
-        <v>127</v>
+        <v>42</v>
       </c>
       <c r="C41" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D41" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E41" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="F41">
         <v>5</v>
       </c>
       <c r="G41" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="H41" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="I41">
         <v>8</v>
@@ -5589,21 +5563,21 @@
         <v>3</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B42" t="s">
-        <v>127</v>
+        <v>42</v>
       </c>
       <c r="C42" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D42" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F42">
         <v>50</v>
@@ -5612,33 +5586,33 @@
         <v>1</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>425</v>
+        <v>448</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C43" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D43" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E43" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="F43">
         <v>5</v>
       </c>
       <c r="G43" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H43" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="I43">
         <v>4</v>
@@ -5647,33 +5621,33 @@
         <v>5</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B44" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D44" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E44" t="s">
-        <v>17</v>
+        <v>137</v>
       </c>
       <c r="F44">
         <v>4</v>
       </c>
       <c r="G44" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H44" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="I44">
         <v>5</v>
@@ -5682,33 +5656,33 @@
         <v>4</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B45" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D45" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E45" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="F45">
         <v>4</v>
       </c>
       <c r="G45" t="s">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="H45" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="I45">
         <v>14</v>
@@ -5719,85 +5693,85 @@
     </row>
     <row r="46" spans="1:11" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="C46" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D46" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E46" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C47" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D47" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="E47" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C48" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D48" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E48" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F48">
         <v>5</v>
       </c>
       <c r="H48" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="J48">
         <v>3</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C49" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D49" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E49" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F49">
         <v>40</v>
       </c>
       <c r="G49" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="H49" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I49">
         <v>5</v>
@@ -5806,67 +5780,67 @@
         <v>0</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="50" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C50" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D50" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E50" t="s">
-        <v>239</v>
+        <v>96</v>
       </c>
       <c r="H50" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="51" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C51" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D51" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B52" t="s">
-        <v>127</v>
+        <v>42</v>
       </c>
       <c r="C52" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D52" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E52" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="F52">
         <v>6</v>
       </c>
       <c r="G52" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="H52" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I52">
         <v>6</v>
@@ -5875,130 +5849,130 @@
         <v>2</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C53" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D53" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E53" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C54" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D54" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="E54" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B55" t="s">
-        <v>127</v>
+        <v>42</v>
       </c>
       <c r="C55" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D55" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="E55" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>381</v>
+      </c>
+      <c r="B56" t="s">
+        <v>74</v>
+      </c>
+      <c r="C56" t="s">
+        <v>77</v>
+      </c>
+      <c r="D56" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" t="s">
+        <v>382</v>
+      </c>
+      <c r="K56" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="B56" t="s">
-        <v>22</v>
-      </c>
-      <c r="C56" t="s">
-        <v>15</v>
-      </c>
-      <c r="D56" t="s">
-        <v>16</v>
-      </c>
-      <c r="E56" t="s">
-        <v>384</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B57" t="s">
-        <v>127</v>
+        <v>42</v>
       </c>
       <c r="C57" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D57" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E57" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="H57" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C58" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D58" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E58" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F58">
         <v>7</v>
       </c>
       <c r="G58" t="s">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="H58" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I58">
         <v>8</v>
@@ -6007,33 +5981,33 @@
         <v>4</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B59" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C59" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D59" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E59" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="F59">
         <v>7</v>
       </c>
       <c r="G59" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="H59" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="I59">
         <v>5</v>
@@ -6042,33 +6016,33 @@
         <v>5</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B60" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D60" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E60" t="s">
-        <v>394</v>
+        <v>29</v>
       </c>
       <c r="F60">
         <v>3</v>
       </c>
       <c r="G60" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="H60" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="I60">
         <v>7</v>
@@ -6077,67 +6051,67 @@
         <v>0</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>395</v>
+      </c>
+      <c r="B61" t="s">
+        <v>28</v>
+      </c>
+      <c r="C61" t="s">
+        <v>77</v>
+      </c>
+      <c r="D61" t="s">
+        <v>16</v>
+      </c>
+      <c r="E61" t="s">
+        <v>279</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B61" t="s">
-        <v>58</v>
-      </c>
-      <c r="C61" t="s">
-        <v>15</v>
-      </c>
-      <c r="D61" t="s">
-        <v>24</v>
-      </c>
-      <c r="E61" t="s">
-        <v>108</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="O61" s="5" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C62" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D62" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="48.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C63" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D63" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E63" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F63">
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="H63" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="I63">
         <v>10</v>
@@ -6146,27 +6120,27 @@
         <v>4</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>404</v>
+      </c>
+      <c r="C64" t="s">
+        <v>63</v>
+      </c>
+      <c r="D64" t="s">
+        <v>16</v>
+      </c>
+      <c r="E64" t="s">
         <v>405</v>
-      </c>
-      <c r="C64" t="s">
-        <v>31</v>
-      </c>
-      <c r="D64" t="s">
-        <v>24</v>
-      </c>
-      <c r="E64" t="s">
-        <v>406</v>
       </c>
       <c r="F64">
         <v>12</v>
       </c>
       <c r="H64" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -6176,30 +6150,30 @@
       </c>
       <c r="K64" s="10"/>
       <c r="O64" s="5" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A65" s="9" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C65" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D65" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E65" t="s">
-        <v>108</v>
+        <v>279</v>
       </c>
       <c r="F65">
         <v>8</v>
       </c>
       <c r="G65" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="H65" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -6208,30 +6182,30 @@
         <v>2</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C66" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D66" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E66" t="s">
-        <v>254</v>
+        <v>233</v>
       </c>
       <c r="F66">
         <v>5</v>
       </c>
       <c r="G66" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="H66" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="I66">
         <v>1</v>
@@ -6240,30 +6214,30 @@
         <v>4</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>226</v>
+        <v>56</v>
       </c>
       <c r="C67" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D67" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E67" t="s">
-        <v>224</v>
+        <v>57</v>
       </c>
       <c r="F67">
         <v>7</v>
       </c>
       <c r="G67" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="H67" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I67">
         <v>4</v>
@@ -6274,28 +6248,28 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="B68" t="s">
-        <v>127</v>
+        <v>42</v>
       </c>
       <c r="C68" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D68" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E68" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="F68">
         <v>8</v>
       </c>
       <c r="G68" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="H68" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I68">
         <v>8</v>
@@ -6304,38 +6278,38 @@
         <v>6</v>
       </c>
       <c r="L68" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C69" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D69" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E69" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C70" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D70" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E70" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="K70" s="10"/>
     </row>
@@ -6360,7 +6334,6 @@
     <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="36.42578125" style="1" customWidth="1"/>
     <col min="12" max="12" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.85546875" bestFit="1" customWidth="1"/>
@@ -6371,40 +6344,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="K1" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>11</v>
+        <v>204</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>13</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -6641,54 +6614,54 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="28.85546875" customWidth="1"/>
     <col min="5" max="5" width="28.28515625" customWidth="1"/>
-    <col min="6" max="6" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="28.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C1" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1" t="s">
+        <v>428</v>
+      </c>
+      <c r="E1" t="s">
+        <v>429</v>
+      </c>
+      <c r="F1" t="s">
+        <v>430</v>
+      </c>
+      <c r="G1" t="s">
         <v>431</v>
-      </c>
-      <c r="B1" t="s">
-        <v>432</v>
-      </c>
-      <c r="C1" t="s">
-        <v>433</v>
-      </c>
-      <c r="D1" t="s">
-        <v>434</v>
-      </c>
-      <c r="E1" t="s">
-        <v>435</v>
-      </c>
-      <c r="F1" t="s">
-        <v>436</v>
-      </c>
-      <c r="G1" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="B2" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="C2" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="D2" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
     </row>
   </sheetData>
@@ -6720,60 +6693,60 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="K1" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>11</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>410</v>
+        <v>202</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>236</v>
+        <v>181</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="H2" t="s">
-        <v>275</v>
+        <v>215</v>
       </c>
       <c r="I2">
         <v>6</v>
@@ -6782,10 +6755,10 @@
         <v>10</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>411</v>
+        <v>203</v>
       </c>
       <c r="L2" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6809,38 +6782,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="11" t="s">
-        <v>412</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11" t="s">
-        <v>413</v>
-      </c>
-      <c r="D1" s="11"/>
+      <c r="A1" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="D1" s="12"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>414</v>
+        <v>211</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>415</v>
+        <v>212</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>414</v>
+        <v>211</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>415</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -6850,18 +6823,18 @@
         <v>40</v>
       </c>
       <c r="H3" t="s">
-        <v>49</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>210</v>
+        <v>165</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6871,228 +6844,228 @@
         <v>40</v>
       </c>
       <c r="H4" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>202</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>221</v>
+        <v>163</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>204</v>
+        <v>31</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>416</v>
+        <v>216</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>417</v>
+        <v>217</v>
       </c>
       <c r="D7">
         <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>410</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>164</v>
+        <v>46</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
       <c r="H9" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="B10">
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>148</v>
+        <v>48</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="H10" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B11">
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D11">
         <v>3</v>
       </c>
       <c r="H11" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>144</v>
       </c>
       <c r="B12">
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
       <c r="H12" t="s">
-        <v>177</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>196</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>144</v>
       </c>
       <c r="D13">
         <v>3</v>
       </c>
       <c r="H13" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>177</v>
+        <v>14</v>
       </c>
       <c r="B14">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>150</v>
+        <v>68</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
       <c r="H14" t="s">
-        <v>196</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>230</v>
+        <v>158</v>
       </c>
       <c r="B15">
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>181</v>
+        <v>128</v>
       </c>
       <c r="D15">
         <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>202</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>410</v>
+        <v>202</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="D16">
         <v>3</v>
       </c>
       <c r="H16" t="s">
-        <v>204</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="B17">
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D17">
         <v>3</v>
       </c>
       <c r="H17" t="s">
-        <v>226</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -7108,6 +7081,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="f5235b4c-d799-48fb-911b-9341dfbcb198" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001E1F373BE6E33547A0D98FDEC4389D85" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5da69aaac1bc90c6e03875f228cbb19b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="f5235b4c-d799-48fb-911b-9341dfbcb198" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2d46185ef74ce7664dbfad5565d23765" ns3:_="">
     <xsd:import namespace="f5235b4c-d799-48fb-911b-9341dfbcb198"/>
@@ -7257,24 +7247,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2853C30-6322-4EA0-9233-C02855FA666C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="f5235b4c-d799-48fb-911b-9341dfbcb198"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="f5235b4c-d799-48fb-911b-9341dfbcb198" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A915AD6-87DB-4A49-8A2C-415A966F3ADD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B17DB05-DAA1-4A80-B966-AED12F9FCF5E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7290,22 +7287,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A915AD6-87DB-4A49-8A2C-415A966F3ADD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2853C30-6322-4EA0-9233-C02855FA666C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f5235b4c-d799-48fb-911b-9341dfbcb198"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>